--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -650,7 +650,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Карточка формы — в её файле в папке obrazcy: у отчёта лист «Описание», у бланка последние страницы. В образце бланка подсвечены значения, которые подставляет система; числа образцов — для иллюстрации.</t>
+          <t>Образцы — только у отчётов: файл отчёта в папке obrazcy, листы «Образец» и «Описание» (карточка). У бланков файла образца нет. Числа образцов — для иллюстрации.</t>
         </is>
       </c>
     </row>
@@ -3139,9 +3139,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-29.docx</t>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -3199,9 +3199,9 @@
           <t>старая система «Претензия»</t>
         </is>
       </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-30.docx</t>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -3255,9 +3255,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-31.docx</t>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -3311,9 +3311,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-32.docx</t>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -3367,9 +3367,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-33.docx</t>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -3423,9 +3423,9 @@
           <t>старая система «Акт сверки»</t>
         </is>
       </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-34.docx</t>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -3483,9 +3483,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J68" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-34.docx</t>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -3539,9 +3539,9 @@
           <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-35.docx</t>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr"/>
@@ -3591,9 +3591,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-36.docx</t>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr"/>
@@ -3643,9 +3643,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-37.docx</t>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr"/>
@@ -3695,9 +3695,9 @@
           <t>старая система «Доо талап»</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-38.docx</t>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -3751,9 +3751,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-39.docx</t>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr"/>
@@ -3803,9 +3803,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J74" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-40.docx</t>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -3859,9 +3859,9 @@
           <t>старая система, распечатка «Реестр погашений»</t>
         </is>
       </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-41.docx</t>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3915,9 +3915,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J76" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-41.docx</t>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3975,9 +3975,9 @@
           <t>старая система, выгрузка графика</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-42.docx</t>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -4031,9 +4031,9 @@
           <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-43.docx</t>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr"/>
@@ -4083,9 +4083,9 @@
           <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-44.docx</t>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -4139,9 +4139,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-45.docx</t>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K80" s="13" t="inlineStr">
@@ -4195,9 +4195,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-46.docx</t>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -4251,9 +4251,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-48.docx</t>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K82" s="13" t="inlineStr">
@@ -4307,9 +4307,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-49.docx</t>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
@@ -4363,9 +4363,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-50.docx</t>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K84" s="13" t="inlineStr">
@@ -4419,9 +4419,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-51.docx</t>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K85" s="13" t="inlineStr">
@@ -4475,9 +4475,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-52.docx</t>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr"/>
@@ -4527,9 +4527,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-60.docx</t>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
@@ -4583,9 +4583,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-61.docx</t>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr"/>
@@ -4635,9 +4635,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-62.docx</t>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
@@ -4691,9 +4691,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-63.docx</t>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr"/>
@@ -4743,9 +4743,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-64.docx</t>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K91" s="13" t="inlineStr">
@@ -4799,9 +4799,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-65.docx</t>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr"/>
@@ -4851,9 +4851,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-66.docx</t>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr"/>
@@ -4903,9 +4903,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-67.docx</t>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr"/>
@@ -4955,9 +4955,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-68.docx</t>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr"/>
@@ -5007,9 +5007,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-69.docx</t>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr"/>
@@ -5059,9 +5059,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-70.docx</t>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr"/>
@@ -5111,9 +5111,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-71.docx</t>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr"/>
@@ -5163,9 +5163,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-72.docx</t>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr"/>
@@ -5215,9 +5215,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J100" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-73.docx</t>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr"/>
@@ -5267,9 +5267,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-74.docx</t>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr"/>
@@ -5319,9 +5319,9 @@
           <t>Методика №16, прил. 1</t>
         </is>
       </c>
-      <c r="J102" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-75.docx</t>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr"/>
@@ -5371,9 +5371,9 @@
           <t>Методика №16, прил. 2</t>
         </is>
       </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-76.docx</t>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr"/>
@@ -5423,9 +5423,9 @@
           <t>Методика №16, прил. 3</t>
         </is>
       </c>
-      <c r="J104" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-77.docx</t>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr"/>
@@ -5475,9 +5475,9 @@
           <t>Методика №16, прил. 4</t>
         </is>
       </c>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-78.docx</t>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr"/>
@@ -5527,9 +5527,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J106" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-79.docx</t>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr"/>
@@ -5579,9 +5579,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-80.docx</t>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
@@ -5639,9 +5639,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-81.docx</t>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
@@ -5695,9 +5695,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-82.docx</t>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
@@ -5751,9 +5751,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-83.docx</t>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
@@ -5807,9 +5807,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-84.docx</t>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
@@ -5867,9 +5867,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-85.docx</t>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
@@ -5923,9 +5923,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-86.docx</t>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
@@ -5979,9 +5979,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-87.docx</t>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
@@ -6035,9 +6035,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-88.docx</t>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr"/>
@@ -6087,9 +6087,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J116" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-89.docx</t>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
@@ -6143,9 +6143,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
@@ -6203,9 +6203,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J118" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J118" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
@@ -6259,9 +6259,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J119" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J119" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
@@ -6315,9 +6315,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J120" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J120" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
@@ -6371,9 +6371,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J121" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J121" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
@@ -6427,9 +6427,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J122" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J122" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K122" s="13" t="inlineStr">
@@ -6483,9 +6483,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J123" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J123" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -6539,9 +6539,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J124" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J124" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K124" s="13" t="inlineStr">
@@ -6595,9 +6595,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J125" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
@@ -6651,9 +6651,9 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J126" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-90.docx</t>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K126" s="13" t="inlineStr">
@@ -6829,71 +6829,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6931,7 +6866,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Перечень на дату заморозки: ____________. Проверка — на контрольном наборе (лист «Контрольный набор»). Строка сдана, если готовая форма совпадает с карточкой (файл образца, лист «Описание» или последняя страница) и выполнены все правила проверки. Числа образцов — для иллюстрации.</t>
+          <t>Перечень на дату заморозки: ____________. Проверка — на контрольном наборе (лист «Контрольный набор»). Строка сдана, если готовая форма совпадает с карточкой (у отчёта — файл образца, лист «Описание») и выполнены все правила проверки. Числа образцов — для иллюстрации.</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Просроченная задолженность по состоянию на 1-е число</t>
+          <t>Просроченная задолженность по состоянию на дату</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -775,7 +775,7 @@
       <c r="K18" s="7" t="inlineStr"/>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Ежемесячно до 15-го, данные на 1-е число</t>
+          <t>Для комитета — на 1-е число, ежемесячно до 15-го</t>
         </is>
       </c>
     </row>
@@ -6933,16 +6933,21 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Просроченная задолженность по состоянию на 1-е число</t>
+          <t>Просроченная задолженность по состоянию на дату</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО по «Просроченная задолженность» = сумма просроченной задолженности по карточкам кредитов набора на дату отчёта: 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19).
-2. «Кредитов с просрочкой» у подразделения = число его кредитов, у которых дней просрочки не меньше заданного; в ИТОГО — 7.
-3. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025).
-4. КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.
-5. Подытог подразделения и заёмщика и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. ИТОГО: «Просроченная задолженность» = 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19); «Остаток основного долга» = 13 170 000,00 сом.
+2. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 7.
+3. У КЗ-02 (г. Бишкек) две строки: область и район.
+4. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025).
+5. Категория риска: средний — КЗ-02, 03, 09; высокий — КЗ-04, 05, 10, 19 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).
+6. Группа = группе заёмщика в контрольном наборе.
+7. Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».
+8. КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.
+9. Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.
+10. Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -188,6 +188,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6938,21 +6939,23 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО: «Просроченная задолженность» = 4 560 750,00 сом по 7 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19); «Остаток основного долга» = 13 170 000,00 сом.
-2. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 7.
-3. У КЗ-02 (г. Бишкек) две строки: область и район.
-4. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025).
-5. Категория риска: средний — КЗ-02, 03, 09; высокий — КЗ-04, 05, 10, 19 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).
-6. Группа = группе заёмщика в контрольном наборе.
-7. Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».
-8. КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.
-9. Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.
-10. Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
+          <t>1. ИТОГО: «Просроченная задолженность» = 10 328 815,00 сом по 12 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23 и три кредита КЗ-21); «Остаток основного долга» = 41 417 000,00 сом.
+2. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 12.
+3. У КЗ-02 (г. Бишкек) и КЗ-22 (г. Ош) по две строки: область и район.
+4. Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в USD (курс 87,50000)» или «в EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90 000,00 USD = 7 875 000,00 сом, просрочка 20 250,00 USD = 1 771 875,00 сом; КЗ-22: остаток 48 000,00 EUR = 4 872 000,00 сом, просрочка 10 460,00 EUR = 1 061 690,00 сом.
+5. Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500 000,00, просрочка 2 934 500,00 сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.
+6. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245.
+7. Категория риска: средний — КЗ-02, 03, 09, 22, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).
+8. Группа = группе заёмщика в контрольном наборе.
+9. Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».
+10. КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.
+11. Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.
+12. Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-02, КЗ-03</t>
+          <t>весь набор; особо: КЗ-02, КЗ-03, КЗ-21, КЗ-22, КЗ-23</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -10716,7 +10719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10744,7 +10747,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Приёмка идёт на контрольном наборе: 20 заёмщиков, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по трём подразделениям и пяти кураторам, кредиты — в сомах, один — в долларах США. Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
+          <t>Приёмка идёт на контрольном наборе: 23 заёмщика, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по подразделениям и пяти кураторам; кредиты — в сомах, четыре — в иностранной валюте (три в долларах США, один в евро). Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
         </is>
       </c>
     </row>
@@ -12102,24 +12105,290 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-21</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Чуйская обл., Кеминский р-н</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Асанов А. К.</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>№ 19-3/061 от 11.04.2019</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I26" s="14" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>ставка 7 %; просрочка 190 дней: основная сумма 20 000,00 USD, проценты 6 300,00 USD, штрафы 900,00 USD; остаток в сомах по курсу 87,50 на 30.09.2026 — 10 500 000,00</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Три кредита с просрочкой, один в долларах США: извещение о внесудебном обращении взыскания на залог по валютному, претензии по двум в сомах</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>ФО-01</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>№ 22-3/014 от 18.03.2022</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>ставка 12,5 %; просрочка 120 дней: основная сумма 400 000,00, проценты 96 000,00, штрафы 12 400,00</t>
+        </is>
+      </c>
+      <c r="L27" s="16" t="n"/>
+      <c r="M27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>№ 24-3/105 от 02.12.2024</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I28" s="14" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>ставка 10 %; просрочка 35 дней только по процентам и штрафам: проценты 45 000,00, штрафы 1 100,00</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="n"/>
+      <c r="M28" s="15" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-22</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>г. Ош</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Асанов А. К.</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>№ 21-1/207 от 15.11.2021</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>48000</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>ставка 6 %; просрочка 62 дня: основная сумма 8 000,00 EUR, проценты 2 160,00 EUR, штрафы 300,00 EUR; остаток в сомах по курсу 101,50 на 30.09.2026 — 4 872 000,00</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Кредит в евро с просрочкой 62 дня, первичная претензия</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>ФО-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-23</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ОсОО «Кербен-Жибек»</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Джалал-Абадская обл., Ноокенский р-н</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>№ 20-5/118 от 23.06.2020</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>150000</v>
+      </c>
+      <c r="I30" s="14" t="n">
+        <v>90000</v>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>ставка 7 %; просрочка 245 дней: основная сумма 15 000,00 USD, проценты 4 050,00 USD, штрафы 1 200,00 USD; остаток в сомах по курсу 87,50 на 30.09.2026 — 7 875 000,00</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Кредит в долларах США с просрочкой 245 дней, исковое заявление в суд</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>ФО-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-06, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="17">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="L26:L28"/>
+    <mergeCell ref="M26:M28"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="A32:M32"/>
     <mergeCell ref="L5:L6"/>
+    <mergeCell ref="D26:D28"/>
+    <mergeCell ref="C26:C28"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="E26:E28"/>
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 38 (из них заготовок внешних форм: 4), видов отчётов: 6. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Задолженность — свод по портфелю</t>
+          <t>Задолженность по состоянию на дату</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по задолженности»; «20gruppa.xls»; «report-temp.xls» (от разработчиков)</t>
+          <t>старая система «Отчет по задолженности»; «20gruppa.xls»; «report-temp.xls» (выгрузка старой системы)</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
@@ -832,61 +832,61 @@
       <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Набор колонок выбирает пользователь: в образцах варианты из 17 и 9 колонок</t>
+          <t>В старой системе — «Информация по задолженности»</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>ФО-02</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные за период»</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>ФО-03</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Расчёты</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>образцы практики по областям</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>«ТАЛАС ПОГАШЕННЫЕ.xls»</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-02.xlsx</t>
-        </is>
-      </c>
-      <c r="K20" s="10" t="inlineStr"/>
-      <c r="L20" s="10" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-03.xlsx</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -894,12 +894,12 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>ФО-03</t>
+          <t>ФО-04</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+          <t>Погашения за период</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -924,125 +924,129 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-03.xlsx</t>
+          <t>obrazcy/ФО-04.xlsx</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Погашения за период</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>вид «Собрано за месяц»</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-04.xlsx</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>ФО-04</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>вид «Собрано за месяц»</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>ФО-05</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Графики погашения</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-04.xlsx</t>
-        </is>
-      </c>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по графикам»</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-05.xlsx</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n">
@@ -1050,12 +1054,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-05</t>
+          <t>ФО-06</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>План-прогноз поступлений</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1065,7 +1069,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1080,23 +1084,23 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по графикам»</t>
+          <t>старая система «Отчет по плану»</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-05.xlsx</t>
+          <t>obrazcy/ФО-06.xlsx</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr"/>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-06</t>
+          <t>ФО-07</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>Начисления процентов и штрафов</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1121,7 +1125,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1136,25 +1140,21 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
+          <t>оф. ТЗ ¶101; ТЗ 18</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по плану»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-06.xlsx</t>
+          <t>obrazcy/ФО-07.xlsx</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
-        </is>
-      </c>
+      <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-07</t>
+          <t>ФО-08</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Освоение и транши</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Транши</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18</t>
+          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1202,11 +1202,15 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-07.xlsx</t>
+          <t>obrazcy/ФО-08.xlsx</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1214,12 +1218,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1229,7 +1233,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Транши</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1244,7 +1248,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
+          <t>оф. ТЗ ¶419–427</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1254,15 +1258,11 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-08.xlsx</t>
+          <t>obrazcy/ФО-09.xlsx</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶419–427</t>
+          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
@@ -1310,119 +1310,119 @@
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-09.xlsx</t>
+          <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr"/>
       <c r="L28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>вид «Влияние реструктуризации: условия до и после»</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶87</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J29" s="9" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Списание задолженности</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-10.xlsx</t>
-        </is>
-      </c>
-      <c r="K30" s="10" t="inlineStr"/>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
-        </is>
-      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по списанию»</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-11.xlsx</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ФО-11</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по списанию»</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-11.xlsx</t>
+          <t>obrazcy/ФО-12.xlsx</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr"/>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1512,21 +1512,25 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-12.xlsx</t>
+          <t>obrazcy/ФО-13.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1534,12 +1538,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1549,7 +1553,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1564,25 +1568,21 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1620,21 +1620,25 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1642,12 +1646,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1672,25 +1676,21 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-16.xlsx</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1728,77 +1728,77 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -1905,56 +1905,60 @@
       <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" s="10" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-18.xlsx</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -1962,12 +1966,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1977,7 +1981,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -1992,17 +1996,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-18.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2018,12 +2022,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2033,7 +2037,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2048,17 +2052,17 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2074,12 +2078,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2104,25 +2108,21 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -2170,115 +2170,115 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr"/>
-      <c r="L46" s="10" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-26.xlsx</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-26.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2534,11 +2534,15 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2546,12 +2550,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2561,7 +2565,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2576,7 +2580,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2586,15 +2590,11 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2642,11 +2642,15 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -2654,12 +2658,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2669,12 +2673,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2684,7 +2688,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2694,13 +2698,13 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2714,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2725,12 +2729,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2740,7 +2744,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2750,15 +2754,11 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-58.xlsx</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2806,11 +2806,19 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr"/>
+          <t>obrazcy/ФО-59.xlsx</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2818,12 +2826,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2833,12 +2841,12 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2848,7 +2856,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -2856,21 +2864,17 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-59.xlsx</t>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -2878,12 +2882,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2898,7 +2902,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2934,12 +2938,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2954,7 +2958,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2990,12 +2994,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3010,7 +3014,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3046,12 +3050,12 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3061,12 +3065,12 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -3076,24 +3080,20 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -6829,7 +6829,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6939,23 +6939,24 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО: «Просроченная задолженность» = 10 328 815,00 сом по 12 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23 и три кредита КЗ-21); «Остаток основного долга» = 41 417 000,00 сом.
-2. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 12.
+          <t>1. ИТОГО: «Просроченная задолженность» = 10 347,215 тыс. сом по 13 кредитам (КЗ-02, 03, 04, 05, 09, 10, 19, 22, 23, 24 и три кредита КЗ-21); «Остаток основного долга» = 41 417,000 тыс. сом.
+2. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке (заёмщик — его кредитов, район — его заёмщиков и т. д.), ИТОГО — сумма департаментов; «Кредитов с просрочкой» = число кредитов разреза, в ИТОГО — 13.
 3. У КЗ-02 (г. Бишкек) и КЗ-22 (г. Ош) по две строки: область и район.
-4. Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в USD (курс 87,50000)» или «в EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90 000,00 USD = 7 875 000,00 сом, просрочка 20 250,00 USD = 1 771 875,00 сом; КЗ-22: остаток 48 000,00 EUR = 4 872 000,00 сом, просрочка 10 460,00 EUR = 1 061 690,00 сом.
-5. Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500 000,00, просрочка 2 934 500,00 сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.
-6. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245.
-7. Категория риска: средний — КЗ-02, 03, 09, 22, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).
+4. Валютный кредит — в сомах по курсу на 30.09.2026 (USD 87,50000, EUR 101,50000); под ним курсивом строка «в тыс. USD (курс 87,50000)» или «в тыс. EUR (курс 101,50000)» с суммами в валюте договора, в итоги она не входит. КЗ-23: остаток 90,000 тыс. USD = 7 875,000 тыс. сом, просрочка 20,250 тыс. USD = 1 771,875 тыс. сом; КЗ-22: остаток 48,000 тыс. EUR = 4 872,000 тыс. сом, просрочка 10,460 тыс. EUR = 1 061,690 тыс. сом.
+5. Заёмщик с несколькими кредитами — КЗ-21 (USD и два в сомах): строка заёмщика — 3 кредита, остаток 15 500,000, просрочка 2 934,500 тыс. сом (валютный кредит — в сомах), категория — худшая (высокий), дни — наибольшие (190); кредиты под ним по убыванию дней — 190, 120, 35. У № 24-3/105 просрочены только проценты и штрафы, просроченная основная сумма — 0,00.
+6. Дни просрочки на 01.10.2026: КЗ-02 — 20, КЗ-03 — 75, КЗ-09 — 95, КЗ-19 — 190, КЗ-04 — 212, КЗ-10 — 260, КЗ-05 — 409 (считается от 18.08.2025); КЗ-21 — 190, 120, 35; КЗ-22 — 62; КЗ-23 — 245; КЗ-24 — 31.
+7. Категория риска: средний — КЗ-02, 03, 09, 22, 24, КЗ-21 № 22-3/014 и № 24-3/105; высокий — КЗ-04, 05, 10, 19, 23, КЗ-21 № 19-3/061 (Порядок №41 п. 11: 1–180 дней — средний, более 180 — высокий).
 8. Группа = группе заёмщика в контрольном наборе.
 9. Стадия взыскания: КЗ-05 — «Соглашение о добровольном исполнении № 3, 10.09.2026»; КЗ-19 — «мер нет».
 10. КЗ-01 (платит по графику) и КЗ-15 (кредит погашен) в отчёте на 01.10.2026 не показаны.
 11. Строка заёмщика есть и при одном кредите; в районе заёмщики — по убыванию дней.
-12. Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
+12. КЗ-24: основная сумма и проценты погашены, просрочены только штрафы 18,400 тыс. сом — кредит в отчёте есть, остаток основного долга 0,00, дни просрочки 31.
+13. Отбор «Отдел развития регионов», категория «средний» на 01.10.2026: только ИТОГО с нулями и под таблицей «Кредитов с просрочкой от 1 дня на 01.10.2026 нет.»</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-02, КЗ-03, КЗ-21, КЗ-22, КЗ-23</t>
+          <t>весь набор; особо: КЗ-02, КЗ-03, КЗ-21, КЗ-22, КЗ-23, КЗ-24</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
@@ -6975,24 +6976,26 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Задолженность — свод по портфелю</t>
+          <t>Задолженность по состоянию на дату</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО по «по основной сумме» (остаток) = сумма остатков основного долга по карточкам кредитов набора на дату отчёта: 39 482,500 тыс. сом (17 кредитов; кредит КЗ-11 в долларах — 55 000,00 USD по курсу 87,50 = 4 812,500).
-2. ИТОГО по «Просроченная задолженность» = 4 560,750 тыс. сом по 7 кредитам набора (КЗ-02, 03, 04, 05, 09, 10, 19).
-3. «Всего остаток» по кредиту = остаток основной суммы + проценты + штрафы; «Просроченная задолженность» не больше «Всего остаток».
-4. Подытог области, района и заёмщика = сумма строк ниже по каждой числовой колонке; число кредитов в ИТОГО = числу кредитов набора с остатком (17).
-5. КЗ-01 показан с двумя кредитами и просрочкой 0,000; у КЗ-02, КЗ-03, КЗ-04, КЗ-05, КЗ-09, КЗ-10, КЗ-19 просрочка больше нуля.
-6. Валютный кредит КЗ-11 включён в итоги в сомах по курсу на дату отчёта; в строке кредита указана валюта USD.
-7. При выборе краткого набора числа в общих колонках совпадают с полным.
-8. Закрытые кредиты (КЗ-08, КЗ-15, КЗ-16, КЗ-18) в отчёте не показаны: остаток равен нулю.</t>
+          <t>1. ИТОГО: заёмщиков 20, кредитов 23 — все кредиты набора, у которых на 01.10.2026 основная сумма + проценты + штрафы больше нуля.
+2. ИТОГО «по основной сумме» (остаток) = 67 729,500 тыс. сом; «Просроченная задолженность» = 10 347,215 тыс. сом — равна ИТОГО ФО-01 на ту же дату.
+3. «Всего остаток» по кредиту = основная сумма + проценты + штрафы; «Просроченная задолженность» не больше «Всего остаток».
+4. Строка разреза = сумма строк на уровень ниже по каждой суммовой колонке; «Кредитов» — число кредитов разреза, «Заёмщиков» — число разных заёмщиков.
+5. Валютные кредиты КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): сумма по договору, получено, остаток, просрочка — по курсу на 30.09.2026; погашено — по курсу дня платежей (КЗ-11: 48,200 тыс. USD = 4 268,350 тыс. сом). Под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)», в итоги не входит.
+6. КЗ-24: основная сумма и проценты погашены, неоплаченные штрафы 18,400 тыс. сом — кредит в отчёте есть, остаток по основной сумме 0,00.
+7. КЗ-21 — одна строка заёмщика (3 кредита), кредиты по дате договора: 11.04.2019, 18.03.2022, 02.12.2024; КЗ-01 — 15.04.2021, 11.03.2022.
+8. У г. Бишкек (КЗ-02, КЗ-11) и г. Ош (КЗ-22) по две строки: область и район.
+9. Закрытые кредиты КЗ-08, КЗ-15, КЗ-16, КЗ-18 в отчёте не показаны.
+10. Отбор «только с просрочкой»: остаются кредиты из ФО-01 на ту же дату (13), итог просрочки тот же.</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>весь набор; особо: КЗ-24</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
@@ -7002,53 +7005,20 @@
       <c r="J6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>ФО-02</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные за период»</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>1. Каждый кредит отчёта имеет остаток 0 на конец периода и дату полного погашения внутри периода.
-2. КЗ-15 за сентябрь 2026 показан: кредит погашен 18.09.2026.
-3. Кредиты с ненулевым остатком и погашенные в другом периоде в отчёте не показаны (КЗ-01 не показан).
-4. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
-      <c r="J7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>ФО-03</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>1. Остаток по основной сумме в последней строке = остатку основной суммы по карточке кредита на дату расчёта (КЗ-05: 2 100 000,00).
 2. Остаток по основной сумме каждой строки = остаток предыдущей + получено − фактическое погашение.
@@ -7059,32 +7029,32 @@
 7. Блок «Всего на дату расчёта»: остаток = подлежит погашению всего − фактически погашено по каждой из трёх строк; просроченные суммы равны колонкам последней строки.</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-05</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Погашения за период</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Всего погашено» = сумма платежей реестра платежей с датой в периоде.
 2. «Всего погашено» платежа = сумма его разнесения по основной сумме, процентам, накопленным процентам и штрафам.
@@ -7096,32 +7066,32 @@
 8. Списание задолженности (КЗ-08) в отчёте не показывается: это не погашение.</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-01</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>вид «Собрано за месяц»</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Собрано всего» = сумма «Всего погашено» ФО-04 за тот же месяц.
 2. «Собрано всего» = основная сумма + проценты + накопленные проценты + штрафы в каждой строке.
@@ -7131,32 +7101,32 @@
 6. У КЗ-01 два платежа за месяц (по кредитам № 21-3/117 и № 22-2/031): «Платежей» у заёмщика — 2.</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr"/>
-      <c r="G10" s="10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr"/>
-      <c r="I10" s="10" t="inlineStr"/>
-      <c r="J10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>ФО-05</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Графики погашения</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>1. Строки кредита в отчёте = строки вкладки «График» действующей версии графика в карточке кредита (КЗ-01, оба кредита).
 2. «Всего по графику» = основная сумма + проценты + накопленные проценты + накопленные штрафы в каждой строке.
@@ -7167,32 +7137,32 @@
 7. Платежи по КЗ-01 приходятся на 15-е (кредит № 21-3/117) и 11-е (кредит № 22-2/031) числа каждого месяца.</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>ФО-06</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>План-прогноз поступлений</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>1. «Всего за год» = сумма четырёх кварталов = основная сумма + проценты + штрафы; «Итого за квартал» = сумма трёх месяцев.
 2. Для кредита группы 1.1 (КЗ-01, оба кредита) план по месяцам = платежам действующего графика этого месяца (основная сумма + проценты); сентябрь: 170 625,00 по кредиту № 21-3/117 и 112 500,00 по № 22-2/031.
@@ -7203,32 +7173,32 @@
 7. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке; по набору показаны все кредиты с остатком на 01.10.2026 (17).</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-01, КЗ-13</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>ФО-07</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Начисления процентов и штрафов</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>1. Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (ФО-03) с датой в периоде.
 2. «С начала года» ≥ «за период» по каждой колонке.
@@ -7238,9 +7208,43 @@
 6. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ФО-08</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Освоение и транши</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита, вкладка «Состав»; „Освоений, шт.“ = число этих освоений.
+2. „Неосвоенный остаток“ = „Сумма“ − „Освоено“ в каждой строке; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-12 (№ 24-2/088 от 12.03.2024): договор 4 000 000,00; два транша — 1 500 000,00 от 20.03.2024 и 1 000 000,00 от 25.06.2024; освоено 2 500 000,00; неосвоенный остаток 1 500 000,00 показан строкой «Не распределено по траншам».
+4. „Плата за неосвоенный остаток начислена“ по кредиту = значению вкладки «Расчёты» кредита на дату отчёта.
+5. Кредит без траншей (КЗ-14, КЗ-17) показан одной строкой; освоено равно сумме фактов освоения, КЗ-17 — 1 500 000,00 от 15.09.2026.</t>
+        </is>
+      </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -7255,26 +7259,26 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита, вкладка «Состав»; „Освоений, шт.“ = число этих освоений.
-2. „Неосвоенный остаток“ = „Сумма“ − „Освоено“ в каждой строке; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-12 (№ 24-2/088 от 12.03.2024): договор 4 000 000,00; два транша — 1 500 000,00 от 20.03.2024 и 1 000 000,00 от 25.06.2024; освоено 2 500 000,00; неосвоенный остаток 1 500 000,00 показан строкой «Не распределено по траншам».
-4. „Плата за неосвоенный остаток начислена“ по кредиту = значению вкладки «Расчёты» кредита на дату отчёта.
-5. Кредит без траншей (КЗ-14, КЗ-17) показан одной строкой; освоено равно сумме фактов освоения, КЗ-17 — 1 500 000,00 от 15.09.2026.</t>
+          <t>1. Условия действующей версии по кредиту = вкладке «Условия» карточки кредита на дату состояния.
+2. У каждого кредита ровно одна действующая версия на дату; периоды версий не пересекаются и не имеют разрывов.
+3. У КЗ-06 после реструктуризации две версии: первая заменена 07.09.2026, вторая действует с 08.09.2026 по доп. соглашению № 2; ставка 12,5 % → 10 %.
+4. У КЗ-01 по каждому из двух кредитов (№ 21-3/117 и № 22-2/031) одна версия; её дата начала совпадает с датой договора.
+5. Число версий в ИТОГО = сумме версий по кредитам (4).</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-01, КЗ-06</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -7289,26 +7293,25 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1. Условия действующей версии по кредиту = вкладке «Условия» карточки кредита на дату состояния.
-2. У каждого кредита ровно одна действующая версия на дату; периоды версий не пересекаются и не имеют разрывов.
-3. У КЗ-06 после реструктуризации две версии: первая заменена 07.09.2026, вторая действует с 08.09.2026 по доп. соглашению № 2; ставка 12,5 % → 10 %.
-4. У КЗ-01 по каждому из двух кредитов (№ 21-3/117 и № 22-2/031) одна версия; её дата начала совпадает с датой договора.
-5. Число версий в ИТОГО = сумме версий по кредитам (4).</t>
+          <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
+2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
+3. КЗ-06: одно обращение, кредит № 20-2/090 (1 800 000,00), обращение от 15.07.2026, закрыто с исходом „Одобрена“ 28.08.2026 (решение уполномоченного органа); дополнительное соглашение № 2 от 08.09.2026; срок стадии и просрочка пусты.
+4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-06</t>
+          <t>КЗ-02, КЗ-06</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -7318,53 +7321,20 @@
       <c r="J15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
-2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
-3. КЗ-06: одно обращение, кредит № 20-2/090 (1 800 000,00), обращение от 15.07.2026, закрыто с исходом „Одобрена“ 28.08.2026 (решение уполномоченного органа); дополнительное соглашение № 2 от 08.09.2026; срок стадии и просрочка пусты.
-4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-02, КЗ-06</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>вид «Влияние реструктуризации: условия до и после»</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>1. Значения „До“ и „После“ по кредиту = расчёт реструктуризации по этому кредиту (бланк ФО-80) на дату соглашения.
 2. „Изменение процентов к уплате“ = „После“ − „До“ в каждой строке кредита; подытоги и ИТОГО равны сумме строк ниже.
@@ -7372,32 +7342,32 @@
 4. Подытог заёмщика КЗ-06 равен его единственному кредиту; кредит, по которому обращение не дошло до вступления соглашения в силу, в отчёте не показан.</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="10" t="inlineStr"/>
-      <c r="J17" s="10" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>ФО-11</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Списание задолженности</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>1. Сумма списания по кредиту = сумме списания в карточке кредита (вкладка «Списание»).
 2. «Всего» = основная сумма + проценты + штрафы в каждой строке.
@@ -7406,9 +7376,42 @@
 5. Списание не входит в «Погашения за период» (ФО-04).</t>
         </is>
       </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-08</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>ФО-12</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Перевод долга</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
+2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
+3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
+4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>КЗ-08</t>
+          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -7423,25 +7426,26 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
-2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
-3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
-4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
+2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
+3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
+4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
+5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-12, КЗ-13</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -7456,49 +7460,15 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
-2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
-3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
-4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
-5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12, КЗ-13</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>ФО-14</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Залоговое обеспечение — предметы</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7508,32 +7478,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7543,9 +7513,43 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
+2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
+3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
+4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
+5. Все даты снятия попадают в период отчёта.</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-15</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
@@ -7560,49 +7564,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
-2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
-3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
-4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
-5. Все даты снятия попадают в период отчёта.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7612,32 +7582,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7645,9 +7615,43 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>вид «Претензии по областям за период»</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
+2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
+3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
+4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
+5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+        </is>
+      </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7667,21 +7671,20 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
-2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
-3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
-4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
-5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
@@ -7691,53 +7694,20 @@
       <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7746,32 +7716,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7781,32 +7751,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7816,9 +7786,43 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ФО-24</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Классификация — движение по группам платёжеспособности</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
+2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
+3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
+4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
+5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -7833,26 +7837,26 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
-2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
-3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
-4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
-5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
+2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
+3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
+4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
+5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-19</t>
+          <t>весь набор</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -7862,54 +7866,20 @@
       <c r="J31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
-2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
-3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
-4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
-5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7918,32 +7888,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7952,6 +7922,40 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>ФО-27</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Средняя просрочка по департаментам</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
+2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
+3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
+4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
+5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -7969,21 +7973,20 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
-2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
-3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
-4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
-5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -8003,25 +8006,26 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
+2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
+3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
+4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
+5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -8036,26 +8040,26 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
-2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
-3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
-4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
-5. Подытог по состоянию и источнику = сумма строк ниже.</t>
+          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
+2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
+3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
+4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
+5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-11</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -8070,49 +8074,15 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
-2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
-3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
-4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
-5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-11</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-54</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>План-факт погашений</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8122,9 +8092,43 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01, КЗ-02</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>ФО-55</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Заявки по программам и статусам</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
+2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
+3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
+4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
+5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-02</t>
+          <t>КЗ-17, КЗ-18</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8139,26 +8143,25 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
-2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
-3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
-4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
-5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17, КЗ-18</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -8173,48 +8176,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>ФО-57</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Данные для расчёта ОКУ на дату</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8224,9 +8194,43 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>ФО-58</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Изменения статусов кредитов за период</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
+2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
+3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
+4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
+5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -8241,49 +8245,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
-2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
-3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
-4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
-5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>ФО-59</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный риск портфеля</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8293,9 +8263,41 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>ФО-91</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
@@ -8310,12 +8312,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8342,12 +8344,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8374,12 +8376,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -8406,24 +8408,28 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
+          <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
+2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
+3. КЗ-16: «Всего погашено» 6 810,000 тыс. сом = платежи до 2026 года 2 560,000 + задолженность 4 250,000, погашенная имуществом 20.03.2026; доплата сверх долга (550,000) в погашение не входит.
+4. КЗ-08 (списан 17.09.2026), КЗ-07 (долг переведён 09.09.2026), КЗ-18 (расторгнут, средства не получены) в отчёте не показаны.
+5. Отбор «способ погашения: имуществом» за 01.01.2026–30.09.2026 — только КЗ-16.
+6. Строка разреза = сумма строк на уровень ниже; число погашенных кредитов по месяцам и кураторам совпадает с видом ФО-25 «Погашенные заёмщики: месяц × куратор».
+7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Состав — по образцу заказчика</t>
+          <t>КЗ-15, КЗ-16</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -10719,7 +10725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10747,7 +10753,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Приёмка идёт на контрольном наборе: 23 заёмщика, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по подразделениям и пяти кураторам; кредиты — в сомах, четыре — в иностранной валюте (три в долларах США, один в евро). Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
+          <t>Приёмка идёт на контрольном наборе: 24 заёмщика, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по подразделениям и пяти кураторам; кредиты — в сомах, четыре — в иностранной валюте (три в долларах США, один в евро). Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11754,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Ошская обл., г. Ош</t>
+          <t>г. Ош</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -11794,7 +11800,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>ФО-02|Погашенные, ФО-04|Собрано, ФО-16, ФО-25|Погашенные, ФО-34|Акт сверки о полном, ФО-58, ФО-90|О снятии запрета</t>
+          <t>ФО-95, ФО-04|Собрано, ФО-16, ФО-25|Погашенные, ФО-34|Акт сверки о полном, ФО-58, ФО-90|О снятии запрета</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11853,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>задолженность 4 250 000,00 погашена 20.03.2026 имуществом стоимостью 4 800 000,00 (переход права); имущество продано в рассрочку по договору от 04.05.2026, покупатель нарушил договор</t>
+          <t>до 2026 года платежами погашено 2 560 000,00 (основная сумма 1 100 000,00, проценты 1 460 000,00); задолженность 4 250 000,00 погашена 20.03.2026 имуществом стоимостью 4 800 000,00 (переход права); имущество продано в рассрочку по договору от 04.05.2026, покупатель нарушил договор</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -11857,7 +11863,7 @@
       </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
-          <t>ФО-17, ФО-47, ФО-48, ФО-49, ФО-50, ФО-51</t>
+          <t>ФО-17, ФО-47, ФО-48, ФО-49, ФО-50, ФО-51, ФО-95</t>
         </is>
       </c>
     </row>
@@ -12364,8 +12370,71 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-24</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>КФХ «Ак-Суу»</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Иссык-Кульская обл., Ак-Суйский р-н</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>Департамент регионального развития</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Жумабаев Р. С.</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>№ 20-6/027 от 12.05.2020</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>KGS</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>кредит АПК, ставка 5 %, срок возврата 12.05.2026; основная сумма и проценты погашены 14.08.2026 с опозданием; неоплаченные штрафы 18 400,00, срок уплаты по претензии — 31.08.2026, просрочка 31 день</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Основной долг и проценты погашены, остались неоплаченные штрафы: кредит остаётся в задолженности и в просрочке</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>ФО-01, ФО-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-06, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
         </is>
@@ -12380,7 +12449,7 @@
     <mergeCell ref="L26:L28"/>
     <mergeCell ref="M26:M28"/>
     <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A33:M33"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="D26:D28"/>
     <mergeCell ref="C26:C28"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$127</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$114</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 38 (из них заготовок внешних форм: 4), видов отчётов: 6. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 6. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ФО-03</t>
+          <t>ФО-04</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+          <t>Погашения за период</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -872,125 +872,129 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Детальный расчет»; «1.pdf», «chakanges/*.pdf» (тело)</t>
+          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-03.xlsx</t>
+          <t>obrazcy/ФО-04.xlsx</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Погашения за период</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>вид «Собрано за месяц»</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 6 пп. 1; старая система</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по погашениям»; «Сейсултан.xlsx» (лист «Информация по погашениям»)</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-04.xlsx</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>ФО-04</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>вид «Собрано за месяц»</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ФО-05</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Графики погашения</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-04.xlsx</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по графикам»</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-05.xlsx</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -998,12 +1002,12 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-05</t>
+          <t>ФО-06</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>План-прогноз поступлений</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1013,7 +1017,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1028,23 +1032,23 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶102, ¶418, ¶872–874; старая система</t>
+          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по графикам»</t>
+          <t>старая система «Отчет по плану»</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-05.xlsx</t>
+          <t>obrazcy/ФО-06.xlsx</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1058,12 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>ФО-06</t>
+          <t>ФО-07</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>Начисления процентов и штрафов</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1069,7 +1073,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1084,25 +1088,21 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489; Методика №17 пп. 1.1–2.3; старая система</t>
+          <t>оф. ТЗ ¶101; ТЗ 18</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по плану»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-06.xlsx</t>
+          <t>obrazcy/ФО-07.xlsx</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr">
-        <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
-        </is>
-      </c>
+      <c r="L24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>ФО-07</t>
+          <t>ФО-08</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Освоение и транши</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Транши</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶101; ТЗ 18</t>
+          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -1150,11 +1150,15 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-07.xlsx</t>
+          <t>obrazcy/ФО-08.xlsx</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n">
@@ -1162,12 +1166,12 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1177,7 +1181,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Транши</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1192,7 +1196,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶446, ¶648–650, ¶870; Методика №16 п. 11 пп. 1; ТЗ 06</t>
+          <t>оф. ТЗ ¶419–427</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -1202,15 +1206,11 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-08.xlsx</t>
+          <t>obrazcy/ФО-09.xlsx</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶419–427</t>
+          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -1258,119 +1258,119 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-09.xlsx</t>
+          <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>вид «Влияние реструктуризации: условия до и после»</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶87</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J28" s="9" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr"/>
+      <c r="K28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Списание задолженности</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶87</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-10.xlsx</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
-        </is>
-      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по списанию»</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-11.xlsx</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>ФО-11</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1408,17 +1408,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по списанию»</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-11.xlsx</t>
+          <t>obrazcy/ФО-12.xlsx</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr"/>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1460,21 +1460,25 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-12.xlsx</t>
+          <t>obrazcy/ФО-13.xlsx</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1482,12 +1486,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1497,7 +1501,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1512,25 +1516,21 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1568,21 +1568,25 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1590,12 +1594,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1620,25 +1624,21 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-16.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1676,77 +1676,77 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1853,56 +1853,60 @@
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-18.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1910,12 +1914,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1925,7 +1929,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-18.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -1966,12 +1970,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -1996,17 +2000,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2022,12 +2026,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2037,7 +2041,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2052,25 +2056,21 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2118,115 +2118,115 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-26.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-26.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2482,11 +2482,15 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2494,12 +2498,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2509,7 +2513,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2524,7 +2528,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2534,15 +2538,11 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2590,11 +2590,15 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2602,12 +2606,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2617,12 +2621,12 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2632,7 +2636,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2642,13 +2646,13 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2658,12 +2662,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2673,12 +2677,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2698,15 +2702,11 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-58.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="L54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2754,11 +2754,19 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr"/>
+          <t>obrazcy/ФО-59.xlsx</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2766,12 +2774,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2781,12 +2789,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2796,7 +2804,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2804,21 +2812,17 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-59.xlsx</t>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2826,12 +2830,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2846,7 +2850,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2882,12 +2886,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2902,7 +2906,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2938,12 +2942,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2958,7 +2962,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -2994,12 +2998,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3009,12 +3013,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3024,24 +3028,20 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K60" s="13" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3050,51 +3050,59 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Бланк</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>язык интерфейса</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr"/>
-      <c r="L61" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3102,12 +3110,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3132,12 +3140,12 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -3150,11 +3158,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+      <c r="L62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3162,12 +3166,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3192,12 +3196,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3218,12 +3222,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3238,7 +3242,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3248,7 +3252,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3274,12 +3278,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3294,7 +3298,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик, залогодатель, орган регистрации</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3304,7 +3308,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3330,12 +3334,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3350,7 +3354,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3360,141 +3364,137 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
+          <t>старая система «Акт сверки»</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>вид «Акт сверки о полном погашении задолженности»</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 64</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J66" s="7" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>ФО-35</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Акт сверки»</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Департамент правового обеспечения</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>рус</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>вид «Акт сверки о полном погашении задолженности»</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 64</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr"/>
+      <c r="K68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-35</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3626,22 +3626,22 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
@@ -3649,7 +3649,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K71" s="7" t="inlineStr"/>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3658,12 +3662,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3678,22 +3682,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3701,11 +3705,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -3757,7 +3757,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="7" t="inlineStr"/>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3766,12 +3770,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-41</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Реестр погашений</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -3781,7 +3785,7 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -3796,141 +3800,141 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
+          <t>старая система, распечатка «Реестр погашений»</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>вид «Выписка по кредиту»</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Платежи</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>ФО-42</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>График погашения</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Реестр погашений»</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>старая система, выгрузка графика</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>вид «Выписка по кредиту»</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
-        </is>
-      </c>
+      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -3938,12 +3942,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-42</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>График погашения</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -3953,27 +3957,27 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>старая система, выгрузка графика</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -3981,11 +3985,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4009,27 +4009,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4037,7 +4037,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr"/>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4046,12 +4050,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4061,12 +4065,12 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4076,12 +4080,12 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4102,12 +4106,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4122,7 +4126,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4132,7 +4136,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -4158,12 +4162,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4173,12 +4177,12 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4188,7 +4192,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4214,12 +4218,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4270,12 +4274,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4326,12 +4330,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -4382,12 +4386,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4397,22 +4401,22 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4425,11 +4429,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K85" s="7" t="inlineStr"/>
       <c r="L85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4453,22 +4453,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4481,7 +4481,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr"/>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4490,12 +4494,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4510,17 +4514,17 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4533,11 +4537,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4589,7 +4589,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr"/>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4598,12 +4602,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4613,22 +4617,22 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4641,11 +4645,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K89" s="7" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4697,7 +4697,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr"/>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4706,12 +4710,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4721,22 +4725,22 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4749,11 +4753,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K91" s="7" t="inlineStr"/>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4918,12 +4918,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5193,12 +5193,12 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5505,22 +5505,22 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -5533,8 +5533,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr"/>
-      <c r="L106" s="7" t="inlineStr"/>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -5542,12 +5550,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5557,12 +5565,12 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -5572,7 +5580,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5590,11 +5598,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="L107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5602,12 +5606,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5622,7 +5626,7 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5632,7 +5636,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5658,12 +5662,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5673,12 +5677,12 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5688,7 +5692,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5714,12 +5718,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5729,7 +5733,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -5744,7 +5748,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5762,7 +5766,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -5770,12 +5778,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5785,12 +5793,12 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -5800,7 +5808,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5818,11 +5826,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5830,12 +5834,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5850,7 +5854,7 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5860,7 +5864,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5886,12 +5890,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5901,12 +5905,12 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5916,7 +5920,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5942,12 +5946,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5957,22 +5961,22 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>ТЗ 12</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -5985,11 +5989,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K114" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K114" s="7" t="inlineStr"/>
       <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6041,7 +6041,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr"/>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6050,12 +6054,12 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -6065,12 +6069,12 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>по виду письма</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -6080,7 +6084,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -6098,53 +6102,57 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>по виду письма</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>Реструктуризация</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>уполномоченный государственный орган</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
-        </is>
-      </c>
-      <c r="I117" s="7" t="inlineStr">
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
+        </is>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J117" s="7" t="inlineStr">
+      <c r="J117" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6154,11 +6162,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
-        </is>
-      </c>
+      <c r="L117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="n">
@@ -6171,7 +6175,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -6181,12 +6185,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -6196,7 +6200,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -6227,7 +6231,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6242,7 +6246,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6252,7 +6256,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6283,7 +6287,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6298,7 +6302,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6308,7 +6312,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6339,7 +6343,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6349,12 +6353,12 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6364,7 +6368,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6395,7 +6399,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6405,12 +6409,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6420,7 +6424,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6451,7 +6455,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6466,7 +6470,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6476,7 +6480,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6507,7 +6511,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6517,12 +6521,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6532,7 +6536,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>ТЗ 21</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6563,7 +6567,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -6573,12 +6577,12 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6588,7 +6592,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -6609,60 +6613,60 @@
       <c r="L125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="A126" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E126" s="10" t="inlineStr">
-        <is>
-          <t>Заявка и комиссия</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>заявитель</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>ПКМ №554 пп. 66, 74</t>
-        </is>
-      </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K126" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L126" s="10" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr"/>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -6670,12 +6674,12 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>ОТ-1</t>
+          <t>ОТ-2</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -6685,7 +6689,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Все модули</t>
+          <t>Отчётность</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -6700,7 +6704,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -6714,66 +6718,10 @@
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>Отчётность</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K128" s="7" t="inlineStr"/>
-      <c r="L128" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L128"/>
+  <autoFilter ref="A17:L127"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6828,8 +6776,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6842,7 +6789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7010,51 +6957,15 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>ФО-03</t>
+          <t>ФО-04</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Детальная задолженность по кредиту (по датам пересчёта)</t>
+          <t>Погашения за период</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>1. Остаток по основной сумме в последней строке = остатку основной суммы по карточке кредита на дату расчёта (КЗ-05: 2 100 000,00).
-2. Остаток по основной сумме каждой строки = остаток предыдущей + получено − фактическое погашение.
-3. Просроченная по основному долгу = нарастающий по графику − нарастающий по факту, если больше нуля, и согласуется с «Просроченная задолженность» карточки кредита.
-4. Колонка «Всего погашено» по строке = фактическое погашение основной суммы + погашение процентов + погашено штрафов; ИТОГО по ней = сумма «Всего погашено» по реестру платежей кредита.
-5. Сумма «Начислено процентов» в ИТОГО = сумме колонки «Начислено процентов» строк расчёта; то же значение — «Начислено за период + за предыдущие периоды» в ФО-07.
-6. КЗ-05 на 01.10.2026: просроченная по основному долгу 700 000,00, по процентам 260 000,00, остаток по штрафам 64 300,00, дней просрочки 409 — как в ФО-01.
-7. Блок «Всего на дату расчёта»: остаток = подлежит погашению всего − фактически погашено по каждой из трёх строк; просроченные суммы равны колонкам последней строки.</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01, КЗ-05</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>ФО-04</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Погашения за период</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Всего погашено» = сумма платежей реестра платежей с датой в периоде.
 2. «Всего погашено» платежа = сумма его разнесения по основной сумме, процентам, накопленным процентам и штрафам.
@@ -7066,32 +6977,32 @@
 8. Списание задолженности (КЗ-08) в отчёте не показывается: это не погашение.</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-01</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>ФО-04</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>вид «Собрано за месяц»</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Собрано всего» = сумма «Всего погашено» ФО-04 за тот же месяц.
 2. «Собрано всего» = основная сумма + проценты + накопленные проценты + штрафы в каждой строке.
@@ -7101,32 +7012,32 @@
 6. У КЗ-01 два платежа за месяц (по кредитам № 21-3/117 и № 22-2/031): «Платежей» у заёмщика — 2.</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
-      <c r="J9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>ФО-05</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Графики погашения</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>1. Строки кредита в отчёте = строки вкладки «График» действующей версии графика в карточке кредита (КЗ-01, оба кредита).
 2. «Всего по графику» = основная сумма + проценты + накопленные проценты + накопленные штрафы в каждой строке.
@@ -7137,32 +7048,32 @@
 7. Платежи по КЗ-01 приходятся на 15-е (кредит № 21-3/117) и 11-е (кредит № 22-2/031) числа каждого месяца.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr"/>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>ФО-06</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>План-прогноз поступлений</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>1. «Всего за год» = сумма четырёх кварталов = основная сумма + проценты + штрафы; «Итого за квартал» = сумма трёх месяцев.
 2. Для кредита группы 1.1 (КЗ-01, оба кредита) план по месяцам = платежам действующего графика этого месяца (основная сумма + проценты); сентябрь: 170 625,00 по кредиту № 21-3/117 и 112 500,00 по № 22-2/031.
@@ -7173,9 +7084,44 @@
 7. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке; по набору показаны все кредиты с остатком на 01.10.2026 (17).</t>
         </is>
       </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>весь набор; особо: КЗ-01, КЗ-13</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>ФО-07</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Начисления процентов и штрафов</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>1. Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (вкладка «Расчёт» карточки кредита) с датой в периоде.
+2. «С начала года» ≥ «за период» по каждой колонке.
+3. Накопленные проценты отличны от нуля только у кредитов, по которым была реструктуризация (КЗ-06): 8 400,00 за сентябрь и с начала года, так как реструктуризация действует с 08.09.2026.
+4. КЗ-01: штрафы за период 0,00; КЗ-02: штрафы за сентябрь 2026 2 350,00 (просрочка с 11.09.2026).
+5. Проценты за сентябрь 2026: КЗ-01 по кредиту № 21-3/117 — 40 625,00 (3 900 000,00 × 12,5 % / 12), КЗ-06 — 15 000,00 (1 800 000,00 × 10 % / 12).
+6. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-01, КЗ-13</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -7190,27 +7136,26 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>ФО-07</t>
+          <t>ФО-08</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Освоение и транши</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1. Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (ФО-03) с датой в периоде.
-2. «С начала года» ≥ «за период» по каждой колонке.
-3. Накопленные проценты отличны от нуля только у кредитов, по которым была реструктуризация (КЗ-06): 8 400,00 за сентябрь и с начала года, так как реструктуризация действует с 08.09.2026.
-4. КЗ-01: штрафы за период 0,00; КЗ-02: штрафы за сентябрь 2026 2 350,00 (просрочка с 11.09.2026).
-5. Проценты за сентябрь 2026: КЗ-01 по кредиту № 21-3/117 — 40 625,00 (3 900 000,00 × 12,5 % / 12), КЗ-06 — 15 000,00 (1 800 000,00 × 10 % / 12).
-6. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита, вкладка «Состав»; „Освоений, шт.“ = число этих освоений.
+2. „Неосвоенный остаток“ = „Сумма“ − „Освоено“ в каждой строке; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-12 (№ 24-2/088 от 12.03.2024): договор 4 000 000,00; два транша — 1 500 000,00 от 20.03.2024 и 1 000 000,00 от 25.06.2024; освоено 2 500 000,00; неосвоенный остаток 1 500 000,00 показан строкой «Не распределено по траншам».
+4. „Плата за неосвоенный остаток начислена“ по кредиту = значению вкладки «Расчёты» кредита на дату отчёта.
+5. Кредит без траншей (КЗ-14, КЗ-17) показан одной строкой; освоено равно сумме фактов освоения, КЗ-17 — 1 500 000,00 от 15.09.2026.</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
@@ -7225,26 +7170,26 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>ФО-08</t>
+          <t>ФО-09</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Освоение и транши</t>
+          <t>Условия кредита и их версии</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита, вкладка «Состав»; „Освоений, шт.“ = число этих освоений.
-2. „Неосвоенный остаток“ = „Сумма“ − „Освоено“ в каждой строке; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-12 (№ 24-2/088 от 12.03.2024): договор 4 000 000,00; два транша — 1 500 000,00 от 20.03.2024 и 1 000 000,00 от 25.06.2024; освоено 2 500 000,00; неосвоенный остаток 1 500 000,00 показан строкой «Не распределено по траншам».
-4. „Плата за неосвоенный остаток начислена“ по кредиту = значению вкладки «Расчёты» кредита на дату отчёта.
-5. Кредит без траншей (КЗ-14, КЗ-17) показан одной строкой; освоено равно сумме фактов освоения, КЗ-17 — 1 500 000,00 от 15.09.2026.</t>
+          <t>1. Условия действующей версии по кредиту = вкладке «Условия» карточки кредита на дату состояния.
+2. У каждого кредита ровно одна действующая версия на дату; периоды версий не пересекаются и не имеют разрывов.
+3. У КЗ-06 после реструктуризации две версии: первая заменена 07.09.2026, вторая действует с 08.09.2026 по доп. соглашению № 2; ставка 12,5 % → 10 %.
+4. У КЗ-01 по каждому из двух кредитов (№ 21-3/117 и № 22-2/031) одна версия; её дата начала совпадает с датой договора.
+5. Число версий в ИТОГО = сумме версий по кредитам (4).</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-01, КЗ-06</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -7259,26 +7204,25 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>ФО-09</t>
+          <t>ФО-10</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1. Условия действующей версии по кредиту = вкладке «Условия» карточки кредита на дату состояния.
-2. У каждого кредита ровно одна действующая версия на дату; периоды версий не пересекаются и не имеют разрывов.
-3. У КЗ-06 после реструктуризации две версии: первая заменена 07.09.2026, вторая действует с 08.09.2026 по доп. соглашению № 2; ставка 12,5 % → 10 %.
-4. У КЗ-01 по каждому из двух кредитов (№ 21-3/117 и № 22-2/031) одна версия; её дата начала совпадает с датой договора.
-5. Число версий в ИТОГО = сумме версий по кредитам (4).</t>
+          <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
+2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
+3. КЗ-06: одно обращение, кредит № 20-2/090 (1 800 000,00), обращение от 15.07.2026, закрыто с исходом „Одобрена“ 28.08.2026 (решение уполномоченного органа); дополнительное соглашение № 2 от 08.09.2026; срок стадии и просрочка пусты.
+4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-06</t>
+          <t>КЗ-02, КЗ-06</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
@@ -7288,53 +7232,20 @@
       <c r="J14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Реструктуризация — заявки и решения</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
-2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
-3. КЗ-06: одно обращение, кредит № 20-2/090 (1 800 000,00), обращение от 15.07.2026, закрыто с исходом „Одобрена“ 28.08.2026 (решение уполномоченного органа); дополнительное соглашение № 2 от 08.09.2026; срок стадии и просрочка пусты.
-4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-02, КЗ-06</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>ФО-10</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>вид «Влияние реструктуризации: условия до и после»</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>1. Значения „До“ и „После“ по кредиту = расчёт реструктуризации по этому кредиту (бланк ФО-80) на дату соглашения.
 2. „Изменение процентов к уплате“ = „После“ − „До“ в каждой строке кредита; подытоги и ИТОГО равны сумме строк ниже.
@@ -7342,32 +7253,32 @@
 4. Подытог заёмщика КЗ-06 равен его единственному кредиту; кредит, по которому обращение не дошло до вступления соглашения в силу, в отчёте не показан.</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr"/>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="10" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>ФО-11</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Списание задолженности</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>1. Сумма списания по кредиту = сумме списания в карточке кредита (вкладка «Списание»).
 2. «Всего» = основная сумма + проценты + штрафы в каждой строке.
@@ -7376,9 +7287,42 @@
 5. Списание не входит в «Погашения за период» (ФО-04).</t>
         </is>
       </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-08</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>ФО-12</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Перевод долга</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
+2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
+3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
+4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+        </is>
+      </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>КЗ-08</t>
+          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
@@ -7393,25 +7337,26 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
-2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
-3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
-4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
+2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
+3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
+4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
+5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-12, КЗ-13</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -7426,49 +7371,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
-2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
-3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
-4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
-5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12, КЗ-13</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>ФО-14</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Залоговое обеспечение — предметы</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7478,32 +7389,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7513,9 +7424,43 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
+2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
+3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
+4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
+5. Все даты снятия попадают в период отчёта.</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-15</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
@@ -7530,49 +7475,15 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
-2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
-3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
-4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
-5. Все даты снятия попадают в период отчёта.</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7582,32 +7493,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7615,9 +7526,43 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>вид «Претензии по областям за период»</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
+2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
+3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
+4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
+5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+        </is>
+      </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
@@ -7637,21 +7582,20 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
-2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
-3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
-4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
-5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7661,53 +7605,20 @@
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7716,32 +7627,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7751,32 +7662,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7786,9 +7697,43 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ФО-24</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Классификация — движение по группам платёжеспособности</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
+2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
+3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
+4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
+5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -7803,26 +7748,26 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
-2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
-3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
-4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
-5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
+2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
+3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
+4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
+5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-19</t>
+          <t>весь набор</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -7832,54 +7777,20 @@
       <c r="J30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
-2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
-3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
-4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
-5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7888,32 +7799,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7922,6 +7833,40 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>ФО-27</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Средняя просрочка по департаментам</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
+2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
+3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
+4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
+5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -7939,21 +7884,20 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
-2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
-3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
-4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
-5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -7973,25 +7917,26 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
+2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
+3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
+4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
+5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -8006,26 +7951,26 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
-2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
-3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
-4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
-5. Подытог по состоянию и источнику = сумма строк ниже.</t>
+          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
+2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
+3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
+4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
+5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-11</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -8040,49 +7985,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
-2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
-3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
-4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
-5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-11</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>ФО-54</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>План-факт погашений</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8092,9 +8003,43 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01, КЗ-02</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>ФО-55</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Заявки по программам и статусам</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
+2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
+3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
+4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
+5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-02</t>
+          <t>КЗ-17, КЗ-18</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -8109,26 +8054,25 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
-2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
-3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
-4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
-5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17, КЗ-18</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8143,48 +8087,15 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>ФО-57</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Данные для расчёта ОКУ на дату</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8194,9 +8105,43 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>ФО-58</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Изменения статусов кредитов за период</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
+2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
+3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
+4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
+5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -8211,49 +8156,15 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
-2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
-3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
-4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
-5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>ФО-59</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный риск портфеля</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8263,9 +8174,41 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>ФО-91</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -8280,12 +8223,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -8312,12 +8255,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8344,12 +8287,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8376,47 +8319,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8427,9 +8338,42 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-15, КЗ-16</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>КЗ-15, КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -8444,25 +8388,26 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
+2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
+4. Для КЗ-01 (без просрочки) бланк недоступен.
+5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
@@ -8477,26 +8422,26 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
-2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
-4. Для КЗ-01 (без просрочки) бланк недоступен.
-5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
+          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
+2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
+3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
+5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
@@ -8511,21 +8456,21 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
-2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
-3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
-5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
+          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
+2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
+3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
+5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -8545,26 +8490,26 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
-2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
-3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
-5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
+          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
+2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
+3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
+4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
+5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
@@ -8579,26 +8524,25 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
-2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
-3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
-4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
-5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -8608,53 +8552,20 @@
       <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8663,38 +8574,72 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="inlineStr"/>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="10" t="inlineStr"/>
+      <c r="H54" s="10" t="inlineStr"/>
+      <c r="I54" s="10" t="inlineStr"/>
+      <c r="J54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками ФО-03 на ту же дату.
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
 3. Просрочено по основной сумме = «по графику нарастающим» − «по факту нарастающим» в каждой строке; просрочено по процентам считается так же.
 4. Остаток процентов и штрафов в итоговом блоке = начислено − погашено; общая задолженность 1 313 699,48 совпадает с суммой в служебной записке ФО-36 на ту же дату.
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>ФО-36</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
+2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
+3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
+4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
+5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -8714,21 +8659,21 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
-2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
-3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
-4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
-5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
+          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
+2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
+3. Меры в тексте = записям ФО-17 по КЗ-05.
+4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
+5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -8748,21 +8693,21 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
-2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
-3. Меры в тексте = записям ФО-17 по КЗ-05.
-4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
-5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
+          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
+2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
+3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
+4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
+5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -8782,21 +8727,21 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
-2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
-3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
-4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
-5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
+          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
+2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
+3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
+4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
+5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -8816,49 +8761,15 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
-2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
-3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
-4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
-5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>ФО-40</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Справка о задолженности</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8868,6 +8779,39 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -8880,53 +8824,20 @@
       <c r="J61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -8935,32 +8846,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr"/>
-      <c r="H63" s="10" t="inlineStr"/>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="10" t="inlineStr"/>
+      <c r="H62" s="10" t="inlineStr"/>
+      <c r="I62" s="10" t="inlineStr"/>
+      <c r="J62" s="10" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -8968,32 +8879,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -9003,32 +8914,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -9038,32 +8949,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -9073,9 +8984,42 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>ФО-46</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Договор поручительства</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -9090,25 +9034,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9123,20 +9067,20 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -9156,20 +9100,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9189,20 +9133,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9222,25 +9166,26 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
+2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
+3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
+4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
+5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
@@ -9255,26 +9200,26 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
-2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
-3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
-4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
-5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
+          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
+2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
+3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
+4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
+5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -9289,49 +9234,15 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
-2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
-3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
-4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
-5. Договор без отнесённых предметов опись не формирует.</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-61</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Справка об обеспеченности кредита</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9341,6 +9252,39 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>ФО-62</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9358,25 +9302,25 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -9391,48 +9335,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr"/>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>ФО-64</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9442,9 +9353,43 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Бланк печатается пустым, данных набора не требует</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>ФО-65</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Карточка организации</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
+2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
+3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
+4. Дата формирования = дате печати.
+5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Бланк печатается пустым, данных набора не требует</t>
+          <t>Карточка организации из справочника ведомств</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
@@ -9459,26 +9404,25 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
-2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
-3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
-4. Дата формирования = дате печати.
-5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации из справочника ведомств</t>
+          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -9493,20 +9437,20 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -9526,48 +9470,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>ФО-68</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Опись дела</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9577,6 +9488,39 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9594,25 +9538,26 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
+2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
+3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
+4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
+5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
@@ -9627,26 +9572,26 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
-2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
-3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
-4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
-5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
+          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
+2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
+3. Задолженность = расчёту кредита на дату бланка.
+4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
+5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
@@ -9661,26 +9606,26 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
-2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
-3. Задолженность = расчёту кредита на дату бланка.
-4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
-5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
+          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
+2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
+3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
+4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
+5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
@@ -9695,26 +9640,25 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
-2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
-3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
-4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
-5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -9729,25 +9673,26 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
+2. Суммы в таблице = справке об обеспеченности на дату записки.
+3. Не хватает = требуется − имеется по каждому кредиту.
+4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
+5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
@@ -9762,49 +9707,15 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
-2. Суммы в таблице = справке об обеспеченности на дату записки.
-3. Не хватает = требуется − имеется по каждому кредиту.
-4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
-5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>ФО-75</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9814,6 +9725,39 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-12</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>ФО-76</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9831,25 +9775,25 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-13</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -9864,25 +9808,26 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
+2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
+3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
+4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
+5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -9897,26 +9842,25 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
-2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
-3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
-4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
-5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -9931,25 +9875,26 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
+          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
+2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
+3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
+4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
+5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-06</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -9964,21 +9909,20 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
-2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
-3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
-4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
-5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -9998,25 +9942,26 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
+2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
+3. В соглашении указано основание — реквизиты согласия кредитора.
+4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
+5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
@@ -10031,26 +9976,26 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
-2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
-3. В соглашении указано основание — реквизиты согласия кредитора.
-4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
-5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
+          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
+2. Сумма строк графика = сумме, присуждённой судебным актом.
+3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
+4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
+5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
@@ -10065,26 +10010,26 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
-2. Сумма строк графика = сумме, присуждённой судебным актом.
-3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
-4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
-5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
+          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
+2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
+3. Номер, дата и сумма договора = карточке кредита.
+4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
+5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-18</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
@@ -10099,26 +10044,25 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
-2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
-3. Номер, дата и сумма договора = карточке кредита.
-4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
-5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>КЗ-18</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -10133,25 +10077,26 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
+2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
+3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
+4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
+5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
@@ -10166,26 +10111,25 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
-2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
-3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
-4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
-5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -10200,25 +10144,25 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10233,20 +10177,21 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
+2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
+3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
+4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
+5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10266,26 +10211,25 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
-2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
-3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
-4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
-5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -10295,53 +10239,20 @@
       <c r="J103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr"/>
-      <c r="J104" s="7" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10349,9 +10260,42 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr"/>
+      <c r="G104" s="10" t="inlineStr"/>
+      <c r="H104" s="10" t="inlineStr"/>
+      <c r="I104" s="10" t="inlineStr"/>
+      <c r="J104" s="10" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
+4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+        </is>
+      </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
@@ -10371,15 +10315,15 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
+2. Каждый запрос получает отдельный исходящий номер.
+3. Данные умершего заёмщика = карточке субъекта.
+4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -10404,20 +10348,20 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
+2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
+3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
+4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
@@ -10437,20 +10381,21 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
-2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
-3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
-4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
+2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
+3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
+4. Срок устранения нарушений не раньше даты регистрации письма.
+5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
@@ -10470,44 +10415,10 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
-2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
-3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
-4. Срок устранения нарушений не раньше даты регистрации письма.
-5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr"/>
-      <c r="G109" s="10" t="inlineStr"/>
-      <c r="H109" s="10" t="inlineStr"/>
-      <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>1. Форма доступна, только если по договору освобождены все доли предметов (полное снятие) либо выбрана часть предмета при частичном снятии.
 2. Основание выбрано из классификатора; при полном погашении указан акт сверки о полном погашении (ФО-34).
@@ -10517,9 +10428,41 @@
 6. Зарегистрированное письмо видно в ФО-19.</t>
         </is>
       </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-15</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
+2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
+3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+        </is>
+      </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>КЗ-15</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
@@ -10539,19 +10482,20 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
-2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
-3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
+2. Перечень документов в письме = составу пакета действующей редакции методики.
+3. Установленная дата в письме не раньше даты запроса.
+4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
@@ -10571,15 +10515,14 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
-2. Перечень документов в письме = составу пакета действующей редакции методики.
-3. Установленная дата в письме не раньше даты запроса.
-4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
+          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
+2. Перечень недостатков в письме = замечаниям комиссии по заявке.
+3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -10594,52 +10537,20 @@
       <c r="J112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="n">
+      <c r="A113" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
-2. Перечень недостатков в письме = замечаниям комиссии по заявке.
-3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr"/>
-      <c r="G113" s="10" t="inlineStr"/>
-      <c r="H113" s="10" t="inlineStr"/>
-      <c r="I113" s="10" t="inlineStr"/>
-      <c r="J113" s="10" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>ОТ-1</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>Выгрузка любого экранного списка в xlsx</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>1. Файл xlsx содержит те же колонки, в том же порядке и с теми же заголовками, что видны на экране; скрытые колонки не выгружаются.
 2. Число строк в файле = число строк списка с учётом всех фильтров и поиска, а не только текущей страницы.
@@ -10650,9 +10561,43 @@
 7. Список с фильтром, не давшим строк, выгружается как файл с заголовками и без строк.</t>
         </is>
       </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется на списках всех модулей</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="7" t="inlineStr"/>
+      <c r="J113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-2</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
+2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
+3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
+4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
+5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
+        </is>
+      </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Проверяется на списках всех модулей</t>
+          <t>Проверяется на каждой строке перечня</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
@@ -10661,56 +10606,22 @@
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="7" t="inlineStr"/>
     </row>
-    <row r="115">
-      <c r="A115" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
-2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
-3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
-4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
-5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется на каждой строке перечня</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="7" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Сдал: ____________________ (разработчик)          Принял: ____________________ (заказчик)          Дата: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J115"/>
+  <autoFilter ref="A4:J114"/>
   <mergeCells count="3">
-    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A116:J116"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сдано,сдано с замечанием,не сдано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10883,7 +10794,7 @@
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>ФО-03, ФО-04, ФО-05, ФО-06, ФО-07, ФО-09, ФО-29, ФО-34, ФО-40, ФО-41, ФО-41|Выписка, ФО-42, ФО-44, ФО-52, ФО-54, ФО-79</t>
+          <t>ФО-04, ФО-05, ФО-06, ФО-07, ФО-09, ФО-29, ФО-34, ФО-40, ФО-41, ФО-41|Выписка, ФО-42, ФО-44, ФО-52, ФО-54, ФО-79</t>
         </is>
       </c>
     </row>
@@ -11170,7 +11081,7 @@
       </c>
       <c r="M10" s="7" t="inlineStr">
         <is>
-          <t>ФО-03, ФО-17, ФО-17|ОИП, ФО-17|События, ФО-35, ФО-36, ФО-37, ФО-38, ФО-39, ФО-70, ФО-83</t>
+          <t>ФО-17, ФО-17|ОИП, ФО-17|События, ФО-35, ФО-36, ФО-37, ФО-38, ФО-39, ФО-70, ФО-83</t>
         </is>
       </c>
     </row>
@@ -12471,7 +12382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12789,6 +12700,26 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>ФО-03 «Детальная задолженность по кредиту (по датам пересчёта)»</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Не отчёт: расчёт по одному кредиту — вкладка «Расчёт» карточки кредита; номер не используется</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>решение владельца 29.10.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -6967,14 +6967,17 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО по «Всего погашено» = сумма платежей реестра платежей с датой в периоде.
-2. «Всего погашено» платежа = сумма его разнесения по основной сумме, процентам, накопленным процентам и штрафам.
-3. Подытог кредита, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.
-4. За сентябрь 2026 показаны КЗ-01 (оба кредита: № 21-3/117 — 15.09.2026, № 22-2/031 — 11.09.2026), КЗ-06, КЗ-07, КЗ-11, КЗ-12, КЗ-13, КЗ-14, КЗ-15, КЗ-20.
-5. Платёж КЗ-11 в долларах показан в сомах по курсу 87,4000 на дату платежа (5 000,00 USD основной суммы = 437 000,00).
-6. Платёж КЗ-15 от 18.09.2026 виден в отчёте, хотя после него кредит погашен.
-7. КЗ-02, КЗ-03, КЗ-04, КЗ-05, КЗ-09, КЗ-10, КЗ-19 в отчёте не показаны: платежей в сентябре 2026 по ним не было, просрочка не погашена.
-8. Списание задолженности (КЗ-08) в отчёте не показывается: это не погашение.</t>
+          <t>1. За сентябрь 2026: 9 заёмщиков, 10 кредитов, 10 платежей; «Всего погашено» 1 667,910 тыс. сом, в том числе основная сумма 1 467,000, проценты 200,910, штрафы 0,000.
+2. «Всего погашено» каждой строки = по основной сумме + по процентам + по штрафам.
+3. Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.
+4. ИТОГО «Всего погашено» = ИТОГО вида «Собрано за месяц» за тот же месяц.
+5. У КЗ-01 «Ак-Дан» два кредита, у каждого своя строка и свой платёж: № 21-3/117 — п/п 4417 от 15.09.2026 (170,625), № 22-2/031 — п/п 4398 от 11.09.2026 (112,500).
+6. Платёж КЗ-11 по кредиту в долларах США — в сомах, как поступил: 461,035 тыс. сом (основная сумма 437,000, проценты 24,035); строки в валюте нет.
+7. Платёж КЗ-15 от 18.09.2026 (полное погашение, 520,000) в отчёте есть, хотя на 01.10.2026 кредит закрыт.
+8. Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 (ФО-12) и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.
+9. Остальные заёмщики набора в сентябре 2026 не платили и не показаны; платёж КЗ-24 от 14.08.2026 — в отчёте за август.
+10. Отбор «вид погашения: имущество в счёт погашения» за 01.01.2026–30.09.2026 — только КЗ-16, платёж 20.03.2026 на 4 250,000 тыс. сом.
+11. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -7004,12 +7007,13 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>1. ИТОГО по «Собрано всего» = сумма «Всего погашено» ФО-04 за тот же месяц.
-2. «Собрано всего» = основная сумма + проценты + накопленные проценты + штрафы в каждой строке.
-3. Подытог подразделения и куратора и ИТОГО = сумма строк ниже по каждой числовой колонке.
-4. КЗ-15 в сентябре 2026 включён: полное погашение 18.09.2026 — собранные деньги.
-5. Списанная задолженность КЗ-08 в «Собрано» не входит.
-6. У КЗ-01 два платежа за месяц (по кредитам № 21-3/117 и № 22-2/031): «Платежей» у заёмщика — 2.</t>
+          <t>1. За сентябрь 2026: ИТОГО — 9 заёмщиков, 10 платежей, «Всего погашено» 1 667,910 тыс. сом = ИТОГО ФО-04 за 01.09.2026–30.09.2026; основная сумма 1 467,000, проценты 200,910, штрафы 0,000.
+2. «С начала года» каждой строки = «Всего погашено» ФО-04 за 01.01.2026–30.09.2026 по тому же заёмщику или разрезу; «С начала года — прошлый год» = то же за 01.01.2025–30.09.2025.
+3. Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.
+4. КЗ-16 «Бишкексүт» (имуществом 20.03.2026, 4 250,000) и КЗ-24 «Ак-Суу» (платёж 14.08.2026) в сентябре не платили — стоят строками с 0,00 за месяц и в «Заёмщиков» не считаются.
+5. У КЗ-01 «Ак-Дан» два платежа за месяц по двум кредитам: «Платежей» — 2, строка одна.
+6. Списание КЗ-08 и перевод долга КЗ-07 не платежи и в суммы не входят.
+7. История платежей до сентября 2026 в контрольном наборе задана только у КЗ-16; остальные суммы колонок «С начала года» в образце — для вида формы и на приёмке сверяются по правилу 2.</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -10977,7 +10981,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Региональное представительство «Ош»</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -11040,7 +11044,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -11166,7 +11170,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -11292,7 +11296,7 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -11355,7 +11359,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -11481,7 +11485,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Региональное представительство «Ош»</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -11544,7 +11548,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -11607,7 +11611,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Региональное представительство «Ош»</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -11670,7 +11674,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Региональное представительство «Ош»</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -11796,7 +11800,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Региональное представительство «Ош»</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -11859,7 +11863,7 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
@@ -11918,7 +11922,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
@@ -11981,7 +11985,7 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Отраслевой департамент промышленности</t>
+          <t>Департамент регионального развития</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>Платежи по графику за период</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -992,7 +992,7 @@
       <c r="K22" s="7" t="inlineStr"/>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>Данные для формы обеспечивает разработчик</t>
+          <t>В старой системе — «Информация по графикам» («Отчет по графикам»)</t>
         </is>
       </c>
     </row>
@@ -7038,23 +7038,28 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Графики погашения</t>
+          <t>Платежи по графику за период</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1. Строки кредита в отчёте = строки вкладки «График» действующей версии графика в карточке кредита (КЗ-01, оба кредита).
-2. «Всего по графику» = основная сумма + проценты + накопленные проценты + накопленные штрафы в каждой строке.
-3. «Осталось оплатить» = всего по графику − оплачено; статус «Оплачен» только при нуле.
-4. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке; «Кол-во платежей» в ИТОГО = числу строк графика в периоде.
-5. КЗ-02 на 01.10.2026: платёж 11.09.2026 (основная сумма 150 000,00, проценты 28 500,00) не оплачен, статус «Просрочен», осталось оплатить 178 500,00.
-6. КЗ-06: накопленные проценты 8 400,00 включены в платёж 12.10.2026.
-7. Платежи по КЗ-01 приходятся на 15-е (кредит № 21-3/117) и 11-е (кредит № 22-2/031) числа каждого месяца.</t>
+          <t>1. Октябрь 2026, оплата на 01.10.2026: заёмщиков 19, кредитов 22, платежей по графику 92; «Не оплачено на начало периода» 9 805,365 тыс. сом, «По графику за период» 2 812,982, оплачено 0,000, осталось оплатить 12 618,347.
+2. ИТОГО «Не оплачено на начало периода» = просроченные основная сумма + проценты ФО-01 на 01.10.2026: 7 454,500 + 2 350,865 = 9 805,365 тыс. сом; штрафы в график не входят.
+3. «Осталось оплатить» = «Не оплачено на начало периода» + «По графику за период» − «Оплачено» в каждой строке; «По графику за период» = основная сумма + проценты + накопленные проценты + накопленные штрафы.
+4. Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику; справочные строки соглашения и строки «в тыс. USD/EUR» в итоги не входят.
+5. За прошлый месяц ИТОГО «По графику за период» = «По графику за период» ФО-54 за тот же месяц. Сентябрь 2026: «Оплачено» = ИТОГО ФО-04 1 667,910 − досрочное погашение КЗ-15 сверх графика 250,000 + разница курса КЗ-11 0,528 (5,275 тыс. USD по 87,50 = 461,563 против 461,035 по курсу дня платежа) = 1 418,438 тыс. сом.
+6. КЗ-23 (иск на просрочку 03.09.2026): платежи до 03.09.2026 — строкой «не оплачено до 01.10.2026, в суде» (8 платежей с 29.01.2026, 16,933 тыс. USD), платёж 29.09.2026 — строкой «не оплачено до 01.10.2026» со статусом «Просрочен» (2,117 тыс. USD, 2 дня); дней просрочки у кредита — 245, как в ФО-01.
+7. КЗ-05 (суд на весь долг): все строки «Предъявлен в суд»; справочная строка «по соглашению № 3: платёж 1 из 6» (соглашение о добровольном исполнении № 3 от 10.09.2026) — 10.10.2026, 404,050 тыс. сом, в итоги не входит.
+8. КЗ-06: платёж 12.10.2026 72,983 = основная сумма 50,000 + проценты 14,583 + накопленные проценты 8,400 (новые условия с 01.10.2026).
+9. КЗ-21 № 24-3/105: не оплачены только проценты — строка «не оплачено до 01.10.2026» 45,000, основная сумма 0,00; КЗ-21 — одна строка заёмщика, три кредита по дате договора.
+10. Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): все суммы по курсу на 30.09.2026; под кредитом строка «в тыс. USD (курс 87,50000)» / «в тыс. EUR (курс 101,50000)».
+11. КЗ-07 — под заёмщиком на дату состояния ОсОО «Ысык-Көл Логистик» (долг переведён 09.09.2026); КЗ-17 — первый платёж 15.10.2026.
+12. Не показаны: КЗ-08 (списан 17.09.2026), КЗ-18 (расторгнут до выдачи), КЗ-15 (погашен 18.09.2026, в октябре платежей нет; в отчёте за сентябрь — платёж 18.09.2026 «Оплачен»), КЗ-16 и КЗ-24 (платежей по графику нет; у КЗ-24 остались только штрафы).</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>весь набор; особо: КЗ-01</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
@@ -12351,7 +12356,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-06, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
+          <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-05, ФО-06, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>План погашений на год</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Правила план-прогноза по группам заёмщиков — Методика №17</t>
+          <t>В старой системе — «Отчет по плану» («Информация по плановым показателям»); прежнее название — «План-прогноз поступлений»</t>
         </is>
       </c>
     </row>
@@ -7079,18 +7079,19 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>План-прогноз поступлений</t>
+          <t>План погашений на год</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1. «Всего за год» = сумма четырёх кварталов = основная сумма + проценты + штрафы; «Итого за квартал» = сумма трёх месяцев.
-2. Для кредита группы 1.1 (КЗ-01, оба кредита) план по месяцам = платежам действующего графика этого месяца (основная сумма + проценты); сентябрь: 170 625,00 по кредиту № 21-3/117 и 112 500,00 по № 22-2/031.
-3. Для кредита группы 1.2 (КЗ-02, КЗ-03, КЗ-04, КЗ-06, КЗ-09) план по месяцам не больше платежа по графику и не меньше нуля; в «Правиле учёта» указан п. 2.1 пп. 2 и процент.
-4. КЗ-05 (принудительное взыскание): график в плане не учитывается; поступления по соглашению о добровольном исполнении № 3 от 10.09.2026 — по 404 050,00 в октябре, ноябре и декабре с пометкой п. 2.2.
-5. КЗ-10 (группа 2.3) и КЗ-19 (группа 3.1): суммы плана нулевые, правило учёта — п. 2.1 пп. 4–5.
-6. Кредит КЗ-11 в долларах: план в сомах по курсу на дату составления (87,50).
-7. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке; по набору показаны все кредиты с остатком на 01.10.2026 (17).</t>
+          <t>1. 2026 год, план на 01.10.2026: заёмщиков 23, кредитов 26; за год 26 516,816 тыс. сом, в том числе основная сумма 22 121,738, проценты 4 344,528, штрафы 50,550; кварталы 6 903,226 · 7 299,326 · 6 052,045 · 6 262,220.
+2. «За год — всего» = основная сумма + проценты + штрафы = сумма четырёх кварталов; квартал = сумма трёх месяцев; строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику; строки «в тыс. USD/EUR» в итоги не входят; пустые месяцы складываются как ноль.
+3. План месяца по кредиту — тот, что записан в системе на дату «План на» (карточка кредита, вкладка «План и исполнение»); план сентября по кредиту = «По плану за период» ФО-54 за сентябрь 2026. КЗ-01: октябрь 169,271 по № 21-3/117 и 111,458 по № 22-2/031 — как платежи октября в ФО-05.
+4. Правки видны колонкой «План изменён» (10 кредитов): КЗ-05 10.09.2026 — октябрь–декабрь по 404,050 (соглашение о добровольном исполнении № 3 от 10.09.2026); КЗ-06 10.09.2026 — октябрь 72,983 по новым условиям с 01.10.2026, как в ФО-05; КЗ-21 15.07.2026 — август–декабрь 0,00 по трём кредитам; КЗ-23 04.09.2026 — сентябрь–декабрь 0,00 после иска 03.09.2026; КЗ-24 20.08.2026 — штрафы 18,400 в сентябре по претензии.
+5. Снятые месяцы — пусто: КЗ-15 (погашен 18.09.2026) — декабрь, план года 840,000; КЗ-08 (списан 17.09.2026) — октябрь–декабрь, январь–сентябрь 0,00; КЗ-16 (погашен имуществом 20.03.2026) — апрель–декабрь, январь–март 0,00. План 0,00 весь год — КЗ-10 (группа 2.3) и КЗ-19 (группа 3.1).
+6. КЗ-17 (выдан 15.09.2026): январь–сентябрь пусто, октябрь–декабрь по 49,167, как платёж октября в ФО-05; «План изменён» пусто — первое заведение. КЗ-20: план на 2026 год не заведён — строка с пустыми суммами.
+7. Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): все месяцы по курсу на 30.09.2026; КЗ-11 за год 5 604,375 тыс. сом = 64,050 тыс. USD × 87,50000, строка «в тыс. USD (курс 87,50000)» под кредитом.
+8. КЗ-07 — под заёмщиком ОсОО «Ысык-Көл Логистик» (долг переведён 09.09.2026), группа 1.1; КЗ-19 — в группе 3.1 (понижена 22.09.2026); КЗ-21 — одна строка заёмщика, три кредита по дате договора. Не показан КЗ-18 (расторгнут до выдачи).</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Проценты и штрафы за период</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -1102,7 +1102,11 @@
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr"/>
-      <c r="L24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (тип «LOAN_ACCRUE» без формы); прежнее название — «Начисления процентов и штрафов»</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n">
@@ -7116,22 +7120,23 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Начисления процентов и штрафов</t>
+          <t>Проценты и штрафы за период</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1. Начислено за период по кредиту = сумма начислений по строкам расчёта кредита (вкладка «Расчёт» карточки кредита) с датой в периоде.
-2. «С начала года» ≥ «за период» по каждой колонке.
-3. Накопленные проценты отличны от нуля только у кредитов, по которым была реструктуризация (КЗ-06): 8 400,00 за сентябрь и с начала года, так как реструктуризация действует с 08.09.2026.
-4. КЗ-01: штрафы за период 0,00; КЗ-02: штрафы за сентябрь 2026 2 350,00 (просрочка с 11.09.2026).
-5. Проценты за сентябрь 2026: КЗ-01 по кредиту № 21-3/117 — 40 625,00 (3 900 000,00 × 12,5 % / 12), КЗ-06 — 15 000,00 (1 800 000,00 × 10 % / 12).
-6. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. Сентябрь 2026: заёмщиков 22, кредитов 25 (KGS — 19 и 21, USD — 3 и 3, EUR — 1 и 1). Проценты: на начало 2 780,378 + начислено 500,186 − погашено 200,910 − списано 112,500 + курсовая разница 3,785 = на конец 2 970,938. Штрафы: 490,548 + 88,649 − 0,000 − 38,000 + 0,653 = 541,850.
+2. В каждой строке и в каждом блоке на конец = на начало + начислено − погашено − списано + курсовая разница; строка разреза = сумма строк на уровень ниже по каждой сумме и по «Кредитов»; строки «в тыс. USD/EUR» в итоги не входят; «Заёмщиков» в ИТОГО — различные заёмщики: КЗ-21 считается в KGS и в USD, в ИТОГО один раз.
+3. Остатки на конец по каждому кредиту = ФО-02 на 01.10.2026 («по процентам», «по штрафам»): ИТОГО 2 970,938 и 541,850. Погашено = ФО-04 за сентябрь 2026: по процентам 200,910, по штрафам 0,000. Списано = ФО-11: КЗ-08 № 20-3/052 (списан 17.09.2026) — проценты 112,500, штрафы 38,000.
+4. Начисление процентов — по дням на остаток основной суммы по ставке договора, база меняется в день платежа: КЗ-01 № 21-3/117 — 4 030 000 × 12,5 % × 15/365 + 3 900 000 × 12,5 % × 15/365 = 40,736, погашено 40,625 (15.09.2026); КЗ-17 (выдан 15.09.2026) — 1 500 000 × 6 % × 15/365 = 3,699, на начало 0,000; КЗ-02 — 1 900 000 × 12,5 % × 30/365 = 19,521, штрафы начислены 2,350 (просрочка с 11.09.2026).
+5. Попадают: КЗ-15 (погашен 18.09.2026, на конец 0,000), КЗ-08 (списан 17.09.2026), КЗ-24 (только штрафы 18,400 на обоих концах, движения нет), КЗ-17 (выдан 15.09.2026). Не попадают: КЗ-18 (средства не получены) и КЗ-16 (погашен 20.03.2026, в сентябре ни остатка, ни движения).
+6. Валютные: на начало — курс 31.08.2026 (USD 87,20000, EUR 101,20000), на конец — 30.09.2026 (USD 87,50000, EUR 101,50000), начисление — по курсу каждого дня. КЗ-21 № 19-3/061: проценты 5,955 + 0,690 = 6,645 тыс. USD; в сомах 519,258 + 60,311 + курсовая разница 1,887 = 581,456. КЗ-11: платёж 05.09.2026 — 24,035 тыс. сом на проценты по курсу 87,25000.
+7. КЗ-07 — под ОсОО «Ысык-Көл Логистик» (реквизиты на 30.09.2026, долг переведён 09.09.2026), одной строкой: 20,604 + 21,808 − 22,083 = 20,329. КЗ-21 «Кемин-Курулуш» — в KGS (два кредита) и в USD (№ 19-3/061).</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>весь набор; особо: КЗ-01</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
@@ -12357,7 +12362,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-05, ФО-06, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
+          <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-05, ФО-06, ФО-07, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 6. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Условия кредитов по состоянию на дату</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -1214,167 +1214,171 @@
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr"/>
-      <c r="L26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе отчёта не было (условия — во вкладке «Условия кредита» по одному кредиту); прежнее название — «Условия кредита и их версии»</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>ФО-09</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>вид «Изменения условий кредитов за период»</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶419–427; ТЗ 05</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-09.xlsx</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶87, ¶435–438; Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
-      <c r="L27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>вид «Влияние реструктуризации: условия до и после»</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>Реструктуризация</t>
         </is>
       </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶87</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J28" s="12" t="inlineStr">
+      <c r="J29" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-10.xlsx</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>Свод по кредитам за период. Расчёт по одному кредиту для письма — бланк ФО-80</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>ФО-11</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Списание задолженности</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по списанию»</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-11.xlsx</t>
-        </is>
-      </c>
-      <c r="K29" s="7" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -1382,12 +1386,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-11</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Списание задолженности</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1412,17 +1416,17 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶417; Порядок №41 пп. 62–63; Политика №28 п. 4.1.1 пп. 9, 12; старая система</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>старая система «Отчет по списанию»</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-12.xlsx</t>
+          <t>obrazcy/ФО-11.xlsx</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr"/>
@@ -1434,12 +1438,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1449,7 +1453,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1464,25 +1468,21 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-12.xlsx</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1520,21 +1520,25 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-13.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1542,12 +1546,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1572,25 +1576,21 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1628,21 +1628,25 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1650,107 +1654,107 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-16.xlsx</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr"/>
-      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -1763,7 +1767,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1788,12 +1792,12 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1815,7 +1819,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1840,12 +1844,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1857,60 +1861,56 @@
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-18.xlsx</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-17.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-18.xlsx</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2004,17 +2004,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2060,21 +2060,25 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2082,12 +2086,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2097,7 +2101,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2112,7 +2116,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2122,115 +2126,115 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-25.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr"/>
-      <c r="L44" s="10" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-26.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2238,12 +2242,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2268,7 +2272,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2278,7 +2282,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-26.xlsx</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -2290,12 +2294,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2320,7 +2324,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2330,7 +2334,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2342,12 +2346,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2357,7 +2361,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2372,7 +2376,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2382,7 +2386,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2394,12 +2398,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2409,7 +2413,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2424,7 +2428,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2434,7 +2438,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2461,7 +2465,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2476,7 +2480,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2486,15 +2490,11 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2542,11 +2542,15 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2554,12 +2558,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2584,7 +2588,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2594,15 +2598,11 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2650,13 +2650,13 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2706,11 +2706,15 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -2718,12 +2722,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2733,12 +2737,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2748,7 +2752,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2758,19 +2762,11 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-59.xlsx</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>obrazcy/ФО-58.xlsx</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2778,12 +2774,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2793,12 +2789,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2808,7 +2804,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2816,17 +2812,21 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-59.xlsx</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3032,20 +3032,24 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3054,59 +3058,51 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Бланк</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>язык интерфейса</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3114,12 +3110,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3144,12 +3140,12 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -3162,7 +3158,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3338,167 +3338,171 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
+          <t>ФО-33</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик, залогодатель, орган регистрации</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>старая система «Акт сверки»</t>
         </is>
       </c>
-      <c r="J66" s="7" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Порядок №41 п. 64</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J67" s="10" t="inlineStr">
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L67" s="10" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ФО-35</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Департамент правового обеспечения</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>рус</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr"/>
-      <c r="L68" s="7" t="inlineStr"/>
+      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -3506,12 +3510,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-35</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3536,12 +3540,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -3558,12 +3562,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3578,7 +3582,7 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3588,7 +3592,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -3610,12 +3614,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3630,22 +3634,22 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
@@ -3653,11 +3657,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3686,22 +3686,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3709,7 +3709,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr"/>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3718,12 +3722,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3733,22 +3737,22 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -3761,11 +3765,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3774,171 +3774,171 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
+          <t>ФО-40</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Справка о задолженности</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Реестр погашений</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>старая система, распечатка «Реестр погашений»</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>ТЗ 14</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr">
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>ФО-42</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>График погашения</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>График</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>старая система, выгрузка графика</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-42</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>График погашения</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -3961,27 +3961,27 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>График</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система, выгрузка графика</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -3989,7 +3989,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr"/>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
@@ -3998,12 +4002,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4013,27 +4017,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4041,11 +4045,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K78" s="7" t="inlineStr"/>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4405,22 +4405,22 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4433,7 +4433,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr"/>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4442,12 +4446,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4457,22 +4461,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4485,11 +4489,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4541,7 +4541,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr"/>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4550,12 +4554,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4570,17 +4574,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4593,11 +4597,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K88" s="7" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4621,22 +4621,22 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4649,7 +4649,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="7" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4658,12 +4662,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4678,17 +4682,17 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4701,11 +4705,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K90" s="7" t="inlineStr"/>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4729,22 +4729,22 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4757,7 +4757,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr"/>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4766,12 +4770,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4781,7 +4785,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4796,7 +4800,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4818,12 +4822,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4848,7 +4852,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4870,12 +4874,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4922,12 +4926,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4974,12 +4978,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5004,7 +5008,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -5026,12 +5030,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5056,7 +5060,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5078,12 +5082,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5098,7 +5102,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -5108,7 +5112,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5130,12 +5134,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5160,7 +5164,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5182,12 +5186,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5197,12 +5201,12 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -5212,7 +5216,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5234,12 +5238,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5249,12 +5253,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5264,12 +5268,12 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -5286,12 +5290,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5316,12 +5320,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5338,12 +5342,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5368,12 +5372,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5390,12 +5394,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5410,7 +5414,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -5420,12 +5424,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5442,12 +5446,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5457,12 +5461,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5472,12 +5476,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5494,12 +5498,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5509,22 +5513,22 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -5537,16 +5541,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K106" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="K106" s="7" t="inlineStr"/>
+      <c r="L106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -5554,12 +5550,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5569,12 +5565,12 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -5584,7 +5580,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5602,7 +5598,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5722,12 +5722,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5770,11 +5770,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -5782,12 +5778,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5797,12 +5793,12 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -5812,7 +5808,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5830,7 +5826,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5965,22 +5965,22 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -5993,7 +5993,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K114" s="7" t="inlineStr"/>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -6002,12 +6006,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6022,12 +6026,12 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6045,11 +6049,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K115" s="7" t="inlineStr"/>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6058,115 +6058,115 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
+          <t>ФО-89</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к договору залога</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>залогодатель</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 12</t>
+        </is>
+      </c>
+      <c r="I116" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr">
         <is>
           <t>Письмо по кредиту</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>по виду письма</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
+      <c r="I117" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J116" s="7" t="inlineStr">
+      <c r="J117" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="13" t="inlineStr">
+      <c r="K117" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L116" s="7" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>Один бланк с видами ниже; у каждого вида свой текст</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t>уполномоченный государственный орган</t>
-        </is>
-      </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J117" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K117" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="n">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6571,106 +6571,106 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 21</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
           <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>Заявка и комиссия</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>заявитель</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
-      <c r="I125" s="10" t="inlineStr">
+      <c r="I126" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J125" s="10" t="inlineStr">
+      <c r="J126" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K126" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L125" s="10" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-1</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Все модули</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
-        </is>
-      </c>
-      <c r="I126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K126" s="7" t="inlineStr"/>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
+      <c r="L126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -6678,54 +6678,110 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
           <t>ОТ-2</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>Требование</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>Отчётность</t>
         </is>
       </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="7" t="inlineStr">
+      <c r="H128" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr">
+      <c r="J128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K127" s="7" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L127"/>
+  <autoFilter ref="A17:L128"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6780,7 +6836,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6793,7 +6850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7190,21 +7247,26 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Условия кредита и их версии</t>
+          <t>Условия кредитов по состоянию на дату</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1. Условия действующей версии по кредиту = вкладке «Условия» карточки кредита на дату состояния.
-2. У каждого кредита ровно одна действующая версия на дату; периоды версий не пересекаются и не имеют разрывов.
-3. У КЗ-06 после реструктуризации две версии: первая заменена 07.09.2026, вторая действует с 08.09.2026 по доп. соглашению № 2; ставка 12,5 % → 10 %.
-4. У КЗ-01 по каждому из двух кредитов (№ 21-3/117 и № 22-2/031) одна версия; её дата начала совпадает с датой договора.
-5. Число версий в ИТОГО = сумме версий по кредитам (4).</t>
+          <t>1. На 01.10.2026 по всему набору: 25 заёмщиков, 28 кредитов — действует 24, закрыт 4 (КЗ-08 списан, КЗ-15 погашен, КЗ-16 погашен имуществом, КЗ-18 расторгнут); проектов и зарегистрированных нет. Кредитов в состоянии «Действует» столько же, сколько в ФО-02 на 01.10.2026 (24, с КЗ-25). Образец — выборка из 9 заёмщиков: ИТОГО 9 заёмщиков, 10 кредитов, 11 траншей, 11 версий, сумма по договору 43 030,000.
+2. КЗ-25 № 21-9/040 (EUR, плавающая ставка): ставка на дату 6,08 = Euribor-6m на 30.09.2026 (2,08) + маржа 4,00; штрафы 0,0493 % в день = двукратная учётная ставка НБКР (2 × 9,00 %) / 365; метод дней факт/360; сумма по договору 120 000,00 EUR = 12 180,000 тыс. сом по курсу 101,50000, строка «в тыс. EUR» — 120,000; версий 1 — ежедневный пересчёт версий не добавляет. У остальных кредитов тип плавающей ставки, маржа и тип плавающего штрафа пусты.
+3. Условия каждого транша = вкладке «Условия» карточки кредита на дату состояния; у каждого условия на дату ровно одно действующее значение.
+4. КЗ-06 № 20-2/090: версий 2, условия с 08.09.2026 по доп. соглашению № 2 от 08.09.2026 — ставка 10,00 %, срок возврата 12.08.2029, льгота по основной сумме 12 мес.; совпадает с ФО-10 (вид «Влияние реструктуризации») и ФО-58.
+5. КЗ-01: два кредита по одной версии, условия с даты договора (15.04.2021 и 11.03.2022), ставка 12,50 %.
+6. КЗ-12 № 24-2/088: два транша (20.03.2024, 25.06.2024) отдельными строками, ставка 8,00 %; в строке кредита — плата за неосвоенный остаток 0,50 % годовых, та, по которой ФО-08 начислил плату 16 993,15.
+7. КЗ-11 (USD): сумма по договору 100 000,00 USD = 8 750,000 тыс. сом по курсу 87,50000 на 30.09.2026; строка «в тыс. USD» — 100,000, в итоги не входит; ставка 6,00 %.
+8. КЗ-17: зарегистрирован 08.09.2026, выдан 15.09.2026 — на 01.10.2026 «Действует», ставка 6,00 %, срок возврата 15.09.2029, одна версия. КЗ-24 (остались только штрафы) — «Действует», ставка 5,00 %, срок возврата 12.05.2026 прошёл. КЗ-08 и КЗ-15 — «Закрыт», условия на дату закрытия (17.09.2026 и 18.09.2026).
+9. Строка разреза = сумма строк на уровень ниже по «Кредитов», «Траншей», «Версий» и «Сумма по договору»; строки «в тыс. USD/EUR» в итоги не входят.
+10. Ставки штрафов, льготы, отсрочка, метод дней и сроки возврата закрытых кредитов в наборе не заданы (кроме КЗ-25); в образце: штрафы 0,05 % в день по основной сумме и по процентам, льгота по основной сумме 12 мес. (у КЗ-06 до соглашения — 6), по процентам и отсрочка — 0, метод факт/факт; срок возврата КЗ-08 — 21.07.2027, КЗ-15 — 14.10.2027.</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-06</t>
+          <t>КЗ-01, КЗ-06, КЗ-08, КЗ-11, КЗ-12, КЗ-15, КЗ-17, КЗ-24, КЗ-25</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
@@ -7214,20 +7276,54 @@
       <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>ФО-09</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>вид «Изменения условий кредитов за период»</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>1. Сентябрь 2026: 3 изменения у одного кредита — КЗ-06 № 20-2/090, доп. соглашение № 2 от 08.09.2026: ставка 12,50 → 10,00, срок возврата 12.08.2027 → 12.08.2029, льгота по основной сумме 6 → 12 мес. В ФО-58 за тот же период у КЗ-06 одно событие «Изменение условий (реструктуризация)» с тем же основанием; в ФО-10 (вид «Влияние реструктуризации») — та же ставка и те же сроки до и после.
+2. Не показываются: регистрация КЗ-17 (08.09.2026) — первичные условия не изменение; перевод долга КЗ-07 (09.09.2026) и соглашение о добровольном исполнении КЗ-05 (10.09.2026) условия не меняют.
+3. Изменение, внесённое в периоде задним числом (вступило раньше начала периода), показывается; изменение, вступившее в периоде и внесённое позже, показывается при формировании после внесения.
+4. КЗ-25 (Euribor-6m + 4,00, пересчёт ежедневно) в сентябре не показывается: тип и маржа не менялись, ежедневные значения ставки — не изменения условий.
+5. Подытоги и ИТОГО = числу строк-условий ниже.</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="inlineStr"/>
+      <c r="J14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Реструктуризация — заявки и решения</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
 2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
@@ -7235,32 +7331,32 @@
 4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>КЗ-02, КЗ-06</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>ФО-10</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>вид «Влияние реструктуризации: условия до и после»</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>1. Значения „До“ и „После“ по кредиту = расчёт реструктуризации по этому кредиту (бланк ФО-80) на дату соглашения.
 2. „Изменение процентов к уплате“ = „После“ − „До“ в каждой строке кредита; подытоги и ИТОГО равны сумме строк ниже.
@@ -7268,32 +7364,32 @@
 4. Подытог заёмщика КЗ-06 равен его единственному кредиту; кредит, по которому обращение не дошло до вступления соглашения в силу, в отчёте не показан.</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>ФО-11</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Списание задолженности</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>1. Сумма списания по кредиту = сумме списания в карточке кредита (вкладка «Списание»).
 2. «Всего» = основная сумма + проценты + штрафы в каждой строке.
@@ -7302,42 +7398,9 @@
 5. Списание не входит в «Погашения за период» (ФО-04).</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>КЗ-08</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>ФО-12</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Перевод долга</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
-2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
-3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
-4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
@@ -7352,15 +7415,48 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
+          <t>ФО-12</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Перевод долга</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
+2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
+3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
+4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-07</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
           <t>ФО-13</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Целевое использование средств</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
 2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
@@ -7369,32 +7465,32 @@
 5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>КЗ-12, КЗ-13</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
-      <c r="J18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ФО-14</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7404,32 +7500,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7439,32 +7535,32 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>ФО-16</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
 2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
@@ -7473,32 +7569,32 @@
 5. Все даты снятия попадают в период отчёта.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7508,32 +7604,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7541,32 +7637,32 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
 2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
@@ -7575,42 +7671,9 @@
 5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>КЗ-02</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7620,20 +7683,53 @@
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7642,32 +7738,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7677,32 +7773,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7712,32 +7808,32 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>ФО-24</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
 2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
@@ -7746,32 +7842,32 @@
 5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
 2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
@@ -7780,32 +7876,32 @@
 5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7814,32 +7910,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7848,32 +7944,32 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>ФО-27</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
 2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
@@ -7882,39 +7978,6 @@
 5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>ФО-28</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Доля проблемных кредитов</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
-        </is>
-      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -7932,15 +7995,48 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>ФО-28</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Доля проблемных кредитов</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>ФО-47</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Реестр имущества на дату</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
 2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
@@ -7949,32 +8045,32 @@
 5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>КЗ-16</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>ФО-53</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
 2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
@@ -7983,32 +8079,32 @@
 5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>КЗ-11</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>ФО-54</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>План-факт погашений</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8018,32 +8114,32 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-02</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>ФО-55</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Заявки по программам и статусам</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
 2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
@@ -8052,42 +8148,9 @@
 5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>КЗ-17, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-56</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>План и факт выдачи</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8102,15 +8165,48 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
+          <t>ФО-56</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>План и факт выдачи</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>ФО-57</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8120,32 +8216,32 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>ФО-58</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
 2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
@@ -8154,32 +8250,32 @@
 5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>ФО-59</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Кредитный риск портфеля</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8189,41 +8285,9 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>ФО-91</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -8238,12 +8302,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -8270,12 +8334,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8302,12 +8366,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8334,15 +8398,47 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Состав — по образцу заказчика</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8353,42 +8449,9 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>КЗ-15, КЗ-16</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>ФО-29</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Уведомление о наступающем платеже</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -8403,15 +8466,48 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
           <t>ФО-30</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Первичная претензия</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
 2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
@@ -8420,32 +8516,32 @@
 5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>КЗ-02</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr"/>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>ФО-31</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Повторная претензия</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
 2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
@@ -8454,32 +8550,32 @@
 5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>ФО-32</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
 2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
@@ -8488,32 +8584,32 @@
 5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>ФО-33</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
 2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
@@ -8522,42 +8618,9 @@
 5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -8567,20 +8630,53 @@
       <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Акт сверки задолженности на 1 января</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8589,32 +8685,32 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="10" t="inlineStr"/>
-      <c r="H54" s="10" t="inlineStr"/>
-      <c r="I54" s="10" t="inlineStr"/>
-      <c r="J54" s="10" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="10" t="inlineStr"/>
+      <c r="H55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
@@ -8623,32 +8719,32 @@
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>ФО-36</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
 2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
@@ -8657,32 +8753,32 @@
 5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>ФО-37</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
 2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
@@ -8691,32 +8787,32 @@
 5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>ФО-38</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Исковое заявление</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
 2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
@@ -8725,32 +8821,32 @@
 5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
-      <c r="J58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>ФО-39</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
 2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
@@ -8759,32 +8855,32 @@
 5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>ФО-40</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Справка о задолженности</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8794,39 +8890,6 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -8839,20 +8902,53 @@
       <c r="J61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr"/>
+      <c r="J62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -8861,32 +8957,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr"/>
-      <c r="G62" s="10" t="inlineStr"/>
-      <c r="H62" s="10" t="inlineStr"/>
-      <c r="I62" s="10" t="inlineStr"/>
-      <c r="J62" s="10" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -8894,32 +8990,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -8929,32 +9025,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -8964,32 +9060,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -8999,42 +9095,9 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>ФО-46</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Договор поручительства</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -9049,25 +9112,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9082,20 +9145,20 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -9115,20 +9178,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9148,20 +9211,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9181,15 +9244,48 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
+          <t>ФО-51</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Претензия покупателю</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-16</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
           <t>ФО-52</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Справка по заёмщику</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
 2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
@@ -9198,32 +9294,32 @@
 5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr"/>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr"/>
-      <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>ФО-60</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Опись предметов залога по договору</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
 2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
@@ -9232,32 +9328,32 @@
 5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>ФО-61</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9267,39 +9363,6 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-62</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
-        </is>
-      </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9317,25 +9380,25 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -9350,15 +9413,48 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
+          <t>ФО-63</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по заявкам</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
           <t>ФО-64</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9368,32 +9464,32 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>Бланк печатается пустым, данных набора не требует</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>ФО-65</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Карточка организации</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
 2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
@@ -9402,42 +9498,9 @@
 5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Карточка организации из справочника ведомств</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>ФО-66</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Журнал регистрации документов за период</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -9452,20 +9515,20 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -9485,15 +9548,48 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
+          <t>ФО-67</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Лист ознакомления</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>ФО-68</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Опись дела</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9503,39 +9599,6 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>ФО-69</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Регистрационно-контрольная карточка документа</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
-        </is>
-      </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9553,15 +9616,48 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>ФО-70</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
 2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
@@ -9570,32 +9666,32 @@
 5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr"/>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>ФО-71</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
 2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
@@ -9604,32 +9700,32 @@
 5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>ФО-72</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
 2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
@@ -9638,42 +9734,9 @@
 5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>КЗ-09</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr"/>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>ФО-73</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Служебная записка об инициировании банкротства</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -9688,15 +9751,48 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
+          <t>ФО-73</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании банкротства</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-10</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
           <t>ФО-74</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
 2. Суммы в таблице = справке об обеспеченности на дату записки.
@@ -9705,32 +9801,32 @@
 5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>ФО-75</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9740,39 +9836,6 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>ФО-76</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
-        </is>
-      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9790,25 +9853,25 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -9823,15 +9886,48 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
+          <t>ФО-77</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-13</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
           <t>ФО-78</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
 2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
@@ -9840,42 +9936,9 @@
 5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>ФО-79</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>Внутренний акт сверки платежей</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -9890,15 +9953,48 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
+          <t>ФО-79</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Внутренний акт сверки платежей</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
           <t>ФО-80</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
 2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
@@ -9907,39 +10003,6 @@
 5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>ФО-81</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
-        </is>
-      </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
           <t>КЗ-06</t>
@@ -9957,15 +10020,48 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
+          <t>ФО-81</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к кредитному договору</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
           <t>ФО-82</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Соглашение о переводе долга</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
 2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
@@ -9974,32 +10070,32 @@
 5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>КЗ-07</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>ФО-83</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
 2. Сумма строк графика = сумме, присуждённой судебным актом.
@@ -10008,32 +10104,32 @@
 5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr"/>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="7" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>ФО-84</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
 2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
@@ -10042,42 +10138,9 @@
 5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>КЗ-18</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>ФО-85</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -10092,15 +10155,48 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
+          <t>ФО-85</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт распределения выручки от реализации залога</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-04</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
           <t>ФО-86</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
 2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
@@ -10109,42 +10205,9 @@
 5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr"/>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>ФО-87</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -10159,25 +10222,25 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10192,15 +10255,48 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
+          <t>ФО-88</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Паспорт предмета залога</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
           <t>ФО-89</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
 2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
@@ -10209,42 +10305,9 @@
 5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr"/>
-      <c r="G102" s="7" t="inlineStr"/>
-      <c r="H102" s="7" t="inlineStr"/>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -10254,20 +10317,53 @@
       <c r="J103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n">
+      <c r="A104" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Письмо по кредиту</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется по видам</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10275,42 +10371,9 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="inlineStr"/>
-      <c r="G104" s="10" t="inlineStr"/>
-      <c r="H104" s="10" t="inlineStr"/>
-      <c r="I104" s="10" t="inlineStr"/>
-      <c r="J104" s="10" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
@@ -10330,15 +10393,15 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
+4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -10363,20 +10426,20 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
-2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
-3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
-4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
+2. Каждый запрос получает отдельный исходящий номер.
+3. Данные умершего заёмщика = карточке субъекта.
+4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
@@ -10396,10 +10459,43 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
+2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
+3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
+4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-10</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr"/>
+      <c r="G108" s="10" t="inlineStr"/>
+      <c r="H108" s="10" t="inlineStr"/>
+      <c r="I108" s="10" t="inlineStr"/>
+      <c r="J108" s="10" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
           <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
-      <c r="D108" s="10" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
 2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
@@ -10408,32 +10504,32 @@
 5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
         </is>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>КЗ-12</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr"/>
-      <c r="G108" s="10" t="inlineStr"/>
-      <c r="H108" s="10" t="inlineStr"/>
-      <c r="I108" s="10" t="inlineStr"/>
-      <c r="J108" s="10" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="10" t="n">
-        <v>105</v>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>1. Форма доступна, только если по договору освобождены все доли предметов (полное снятие) либо выбрана часть предмета при частичном снятии.
 2. Основание выбрано из классификатора; при полном погашении указан акт сверки о полном погашении (ФО-34).
@@ -10443,41 +10539,9 @@
 6. Зарегистрированное письмо видно в ФО-19.</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr"/>
-      <c r="G109" s="10" t="inlineStr"/>
-      <c r="H109" s="10" t="inlineStr"/>
-      <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
-2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
-3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
@@ -10497,20 +10561,19 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
-2. Перечень документов в письме = составу пакета действующей редакции методики.
-3. Установленная дата в письме не раньше даты запроса.
-4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
+          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
+2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
+3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>КЗ-17</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
@@ -10530,14 +10593,15 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
-2. Перечень недостатков в письме = замечаниям комиссии по заявке.
-3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
+          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
+2. Перечень документов в письме = составу пакета действующей редакции методики.
+3. Установленная дата в письме не раньше даты запроса.
+4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -10552,20 +10616,52 @@
       <c r="J112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="10" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
+2. Перечень недостатков в письме = замечаниям комиссии по заявке.
+3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr"/>
+      <c r="G113" s="10" t="inlineStr"/>
+      <c r="H113" s="10" t="inlineStr"/>
+      <c r="I113" s="10" t="inlineStr"/>
+      <c r="J113" s="10" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>ОТ-1</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>Выгрузка любого экранного списка в xlsx</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>1. Файл xlsx содержит те же колонки, в том же порядке и с теми же заголовками, что видны на экране; скрытые колонки не выгружаются.
 2. Число строк в файле = число строк списка с учётом всех фильтров и поиска, а не только текущей страницы.
@@ -10576,32 +10672,32 @@
 7. Список с фильтром, не давшим строк, выгружается как файл с заголовками и без строк.</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>Проверяется на списках всех модулей</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr"/>
-      <c r="G113" s="7" t="inlineStr"/>
-      <c r="H113" s="7" t="inlineStr"/>
-      <c r="I113" s="7" t="inlineStr"/>
-      <c r="J113" s="7" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="7" t="inlineStr"/>
+      <c r="J114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>ОТ-2</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
 2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
@@ -10610,33 +10706,33 @@
 5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Проверяется на каждой строке перечня</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr"/>
-      <c r="I114" s="7" t="inlineStr"/>
-      <c r="J114" s="7" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Сдал: ____________________ (разработчик)          Принял: ____________________ (заказчик)          Дата: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J114"/>
+  <autoFilter ref="A4:J115"/>
   <mergeCells count="3">
-    <mergeCell ref="A116:J116"/>
+    <mergeCell ref="A117:J117"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сдано,сдано с замечанием,не сдано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10651,7 +10747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10679,7 +10775,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Приёмка идёт на контрольном наборе: 24 заёмщика, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по подразделениям и пяти кураторам; кредиты — в сомах, четыре — в иностранной валюте (три в долларах США, один в евро). Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
+          <t>Приёмка идёт на контрольном наборе: 25 заёмщиков, у каждого — свой случай кредитного цикла. Данные набора заводятся на стенде по этому листу. Заёмщики распределены по подразделениям и пяти кураторам; кредиты — в сомах, пять — в иностранной валюте (три в долларах США, два в евро); один кредит — с плавающей ставкой. Дата состояния для проверки — 01.10.2026, отчётный период — сентябрь 2026. Остаток — основной долг на 01.10.2026. Числа в образцах форм взяты из этого листа; на приёмке сверяются по правилам проверки.</t>
         </is>
       </c>
     </row>
@@ -11159,7 +11255,7 @@
       </c>
       <c r="M11" s="7" t="inlineStr">
         <is>
-          <t>ФО-09, ФО-10, ФО-10|Влияние, ФО-58, ФО-80, ФО-81, ФО-90|По реструктуризации</t>
+          <t>ФО-09, ФО-09|Изменения, ФО-10, ФО-10|Влияние, ФО-58, ФО-80, ФО-81, ФО-90|По реструктуризации</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11381,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>ФО-11, ФО-58</t>
+          <t>ФО-09, ФО-11, ФО-58</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11570,7 @@
       </c>
       <c r="M16" s="7" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-09, ФО-53</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11633,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>ФО-08, ФО-13, ФО-75, ФО-76, ФО-78, ФО-87, ФО-90|По целевому</t>
+          <t>ФО-08, ФО-09, ФО-13, ФО-75, ФО-76, ФО-78, ФО-87, ФО-90|По целевому</t>
         </is>
       </c>
     </row>
@@ -11726,7 +11822,7 @@
       </c>
       <c r="M20" s="7" t="inlineStr">
         <is>
-          <t>ФО-95, ФО-04|Собрано, ФО-16, ФО-25|Погашенные, ФО-34|Акт сверки о полном, ФО-58, ФО-90|О снятии запрета</t>
+          <t>ФО-95, ФО-04|Собрано, ФО-09, ФО-16, ФО-25|Погашенные, ФО-34|Акт сверки о полном, ФО-58, ФО-90|О снятии запрета</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11948,7 @@
       </c>
       <c r="M22" s="7" t="inlineStr">
         <is>
-          <t>ФО-44, ФО-55, ФО-56, ФО-63, ФО-90|Возврат проекта, ФО-90|Запрос финансового</t>
+          <t>ФО-09, ФО-44, ФО-55, ФО-56, ФО-63, ФО-90|Возврат проекта, ФО-90|Запрос финансового</t>
         </is>
       </c>
     </row>
@@ -12355,12 +12451,75 @@
       </c>
       <c r="M31" s="7" t="inlineStr">
         <is>
-          <t>ФО-01, ФО-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+          <t>ФО-01, ФО-02, ФО-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-25</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Арча Энерго»</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Чуйская обл., Аламудунский р-н</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Департамент администрирования кредитов</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Бекова Н. С.</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>№ 21-9/040 от 20.09.2021</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>120000</v>
+      </c>
+      <c r="I32" s="14" t="n">
+        <v>72000</v>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>ставка плавающая: Euribor-6m + 4,00, пересчёт ежедневно (Euribor-6m на 30.09.2026 — 2,08, ставка на эту дату — 6,08 %); штраф по основной сумме и по процентам — двукратная учётная ставка НБКР (учётная ставка на 30.09.2026 — 9,00 %, штраф — 0,0493 % в день); метод дней факт/360; срок возврата 20.09.2028; платит по графику без просрочки; остаток в сомах по курсу 101,50 на 30.09.2026 — 7 308 000,00</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Кредит в евро с плавающей ставкой и плавающим штрафом: ставка пересчитывается ежедневно по типу плавающей ставки</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>ФО-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>На всём наборе проверяются: ФО-01, ФО-02, ФО-04, ФО-05, ФО-06, ФО-07, ФО-24, ФО-25, ФО-26, ФО-27, ФО-28, ФО-57, ФО-59.</t>
         </is>
@@ -12375,9 +12534,9 @@
     <mergeCell ref="L26:L28"/>
     <mergeCell ref="M26:M28"/>
     <mergeCell ref="B26:B28"/>
-    <mergeCell ref="A33:M33"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="D26:D28"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="D5:D6"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -7252,16 +7252,16 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1. На 01.10.2026 по всему набору: 25 заёмщиков, 28 кредитов — действует 24, закрыт 4 (КЗ-08 списан, КЗ-15 погашен, КЗ-16 погашен имуществом, КЗ-18 расторгнут); проектов и зарегистрированных нет. Кредитов в состоянии «Действует» столько же, сколько в ФО-02 на 01.10.2026 (24, с КЗ-25). Образец — выборка из 9 заёмщиков: ИТОГО 9 заёмщиков, 10 кредитов, 11 траншей, 11 версий, сумма по договору 43 030,000.
-2. КЗ-25 № 21-9/040 (EUR, плавающая ставка): ставка на дату 6,08 = Euribor-6m на 30.09.2026 (2,08) + маржа 4,00; штрафы 0,0493 % в день = двукратная учётная ставка НБКР (2 × 9,00 %) / 365; метод дней факт/360; сумма по договору 120 000,00 EUR = 12 180,000 тыс. сом по курсу 101,50000, строка «в тыс. EUR» — 120,000; версий 1 — ежедневный пересчёт версий не добавляет. У остальных кредитов тип плавающей ставки, маржа и тип плавающего штрафа пусты.
-3. Условия каждого транша = вкладке «Условия» карточки кредита на дату состояния; у каждого условия на дату ровно одно действующее значение.
-4. КЗ-06 № 20-2/090: версий 2, условия с 08.09.2026 по доп. соглашению № 2 от 08.09.2026 — ставка 10,00 %, срок возврата 12.08.2029, льгота по основной сумме 12 мес.; совпадает с ФО-10 (вид «Влияние реструктуризации») и ФО-58.
-5. КЗ-01: два кредита по одной версии, условия с даты договора (15.04.2021 и 11.03.2022), ставка 12,50 %.
-6. КЗ-12 № 24-2/088: два транша (20.03.2024, 25.06.2024) отдельными строками, ставка 8,00 %; в строке кредита — плата за неосвоенный остаток 0,50 % годовых, та, по которой ФО-08 начислил плату 16 993,15.
-7. КЗ-11 (USD): сумма по договору 100 000,00 USD = 8 750,000 тыс. сом по курсу 87,50000 на 30.09.2026; строка «в тыс. USD» — 100,000, в итоги не входит; ставка 6,00 %.
-8. КЗ-17: зарегистрирован 08.09.2026, выдан 15.09.2026 — на 01.10.2026 «Действует», ставка 6,00 %, срок возврата 15.09.2029, одна версия. КЗ-24 (остались только штрафы) — «Действует», ставка 5,00 %, срок возврата 12.05.2026 прошёл. КЗ-08 и КЗ-15 — «Закрыт», условия на дату закрытия (17.09.2026 и 18.09.2026).
-9. Строка разреза = сумма строк на уровень ниже по «Кредитов», «Траншей», «Версий» и «Сумма по договору»; строки «в тыс. USD/EUR» в итоги не входят.
-10. Ставки штрафов, льготы, отсрочка, метод дней и сроки возврата закрытых кредитов в наборе не заданы (кроме КЗ-25); в образце: штрафы 0,05 % в день по основной сумме и по процентам, льгота по основной сумме 12 мес. (у КЗ-06 до соглашения — 6), по процентам и отсрочка — 0, метод факт/факт; срок возврата КЗ-08 — 21.07.2027, КЗ-15 — 14.10.2027.</t>
+          <t>1. На 01.10.2026 по всему набору: 25 заёмщиков, 28 кредитов — действует 24, закрыт 4 (КЗ-08 списан, КЗ-15 погашен, КЗ-16 погашен имуществом, КЗ-18 расторгнут); проектов и зарегистрированных нет. Кредитов в состоянии «Действует» столько же, сколько в ФО-02 на 01.10.2026 (24). Образец — выборка из 9 заёмщиков: ИТОГО 9 заёмщиков, 10 кредитов, 11 траншей, 1 изменение.
+2. Условия каждого транша и условия платы кредита = вкладке «Условия» карточки кредита на дату состояния; у каждого условия на дату ровно одно действующее значение.
+3. КЗ-06 № 20-2/090: изменений 1, условия с 08.09.2026 по доп. соглашению № 2 от 08.09.2026 — ставка 12,50 → 10,00, срок 84 → 108 мес. (срок возврата 12.08.2029), льгота по основной сумме 6 → 12 мес.; эти три ячейки выделены. Совпадает с видом «Изменения условий кредитов за период», ФО-10 (вид «Влияние реструктуризации») и ФО-58.
+4. КЗ-25 № 21-9/040 (EUR, плавающие ставки): ставка «Euribor-6m + 4,00 = 6,08» — Euribor-6m на 30.09.2026 2,08; штрафы «Двукратная учётная ставка НБКР = 0,0493» — 2 × 9,00 % / 365; выделения нет: тип и маржа не менялись, ежедневный пересчёт — не изменение; метод погашения — аннуитет, метод дней факт/360, нерабочие дни — на следующий рабочий день.
+5. КЗ-12 № 24-2/088: два транша (20.03.2024 — 58 мес., 25.06.2024 — 55 мес.) отдельными строками, ставка 8,00 %; в строке кредита — плата за неосвоенный остаток: 0,50 % годовых с 12.03.2024, ежеквартально, 12-го числа, штраф 0,05 % в день; по этой ставке ФО-08 начислил плату 16 993,15.
+6. КЗ-17 № 26-5/090 — кредит, выданный через заявку новой системы: основание «Заявка № 14 · протокол комиссии № 7 от 20.08.2026», условия с 08.09.2026, срок 36 мес., возврат 15.09.2029; льгота по процентам 6 мес., отсроченные проценты распределены на периоды 7–12. У остальных кредитов выборки первичные условия перенесены из старой системы — основание «Перенос из старой системы».
+7. КЗ-24 № 20-6/027 (кредит АПК): платежи по конкретным месяцам — «по месяцам: 5, 11»; срок возврата 12.05.2026 прошёл, кредит «Действует» — остались неоплаченные штрафы. КЗ-08 и КЗ-15 — «Закрыт», условия на дату закрытия (17.09.2026 и 18.09.2026).
+8. Срок возврата согласуется со сроком в месяцах: КЗ-01 № 21-3/117 — 15.04.2021 + 95 мес. = 15.03.2029.
+9. Строка разреза = сумма строк на уровень ниже по «Кредитов», «Траншей» и «Изменений».
+10. Условия, не заданные в наборе (кроме КЗ-25), в образце: штрафы 0,05 % в день, предел штрафов 20 % суммы кредита, метод погашения — равными долями, ежемесячно, день платежа — число даты договора, нерабочие дни — не переносить, последний платёж — по дате выдачи, льгота по основной сумме 12 мес. (у КЗ-06 до соглашения — 6), по процентам и отсрочка — 0 (у КЗ-17 по процентам — 6), метод дней факт/факт; срок КЗ-06 до соглашения — 84 мес.; сроки возврата КЗ-08 — 21.07.2027, КЗ-15 — 14.10.2027; ставки КЗ-12 — 8 %, КЗ-11 — 6 %, КЗ-08 и КЗ-15 — 10 % (восстановлены из начислений ФО-07).</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -7291,11 +7291,11 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>1. Сентябрь 2026: 3 изменения у одного кредита — КЗ-06 № 20-2/090, доп. соглашение № 2 от 08.09.2026: ставка 12,50 → 10,00, срок возврата 12.08.2027 → 12.08.2029, льгота по основной сумме 6 → 12 мес. В ФО-58 за тот же период у КЗ-06 одно событие «Изменение условий (реструктуризация)» с тем же основанием; в ФО-10 (вид «Влияние реструктуризации») — та же ставка и те же сроки до и после.
-2. Не показываются: регистрация КЗ-17 (08.09.2026) — первичные условия не изменение; перевод долга КЗ-07 (09.09.2026) и соглашение о добровольном исполнении КЗ-05 (10.09.2026) условия не меняют.
+          <t>1. Сентябрь 2026: одно изменение у одного кредита — КЗ-06 № 20-2/090, доп. соглашение № 2 от 08.09.2026, три условия: ставка 12,50 → 10,00, срок 84 → 108 мес., льгота по основной сумме 6 → 12 мес. В основном отчёте на 01.10.2026 у КЗ-06 «Изменений» 1 и эти три ячейки выделены; в ФО-58 за тот же период у КЗ-06 одно событие «Изменение условий (реструктуризация)» с тем же основанием; в ФО-10 (вид «Влияние реструктуризации») — та же ставка и тот же срок до и после.
+2. Не показываются: регистрация КЗ-17 (08.09.2026) — первичные условия из заявки — не изменение; перевод долга КЗ-07 (09.09.2026) и соглашение о добровольном исполнении КЗ-05 (10.09.2026) условия не меняют.
 3. Изменение, внесённое в периоде задним числом (вступило раньше начала периода), показывается; изменение, вступившее в периоде и внесённое позже, показывается при формировании после внесения.
 4. КЗ-25 (Euribor-6m + 4,00, пересчёт ежедневно) в сентябре не показывается: тип и маржа не менялись, ежедневные значения ставки — не изменения условий.
-5. Подытоги и ИТОГО = числу строк-условий ниже.</t>
+5. Подытоги и ИТОГО: «Изменений» — число строк-документов ниже, «Условий» — число строк-условий ниже.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация — заявки и решения</t>
+          <t>Обращения о реструктуризации за период</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -1322,7 +1322,11 @@
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr"/>
-      <c r="L28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>Новая форма: в старой системе реструктуризация велась отдельным кредитом-обёрткой без обращений и стадий; прежнее название — «Реструктуризация — заявки и решения»</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
+          <t>вид «Влияние реструктуризации на условия кредитов за период»</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -7320,20 +7324,22 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация — заявки и решения</t>
+          <t>Обращения о реструктуризации за период</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1. Число обращений и сумма в ИТОГО = число и сумма обращений с датой регистрации в периоде в журнале реструктуризации.
-2. Подытоги подразделения и заёмщика = сумма строк ниже по колонкам „Обращений“, „Кредитов в охвате“ и „Остаток основной суммы“.
-3. КЗ-06: одно обращение, кредит № 20-2/090 (1 800 000,00), обращение от 15.07.2026, закрыто с исходом „Одобрена“ 28.08.2026 (решение уполномоченного органа); дополнительное соглашение № 2 от 08.09.2026; срок стадии и просрочка пусты.
-4. КЗ-02: обращение от 10.09.2026 на стадии «Анализ», срок стадии 10.10.2026, просрочка срока на 01.10.2026 — 0 дней; если стадию не закрыть до 10.10.2026, с 11.10.2026 колонка «Просрочка срока» показывает число дней сверх срока.</t>
+          <t>1. За 01.01.2026–30.09.2026 по всему набору: 4 обращения — 2 в работе, 2 закрыты; 1 с нарушением срока; 4 кредита; остаток основной суммы 15 525,000 тыс. сом. В работе на 30.09.2026 — столько же, сколько на плитке дашборда «Обращений о реструктуризации в работе» (2, срок нарушен 1).
+2. КЗ-02 № 22-1/045: обращение от 10.09.2026, стадия «Анализ», срок 10.10.2026 (30 календарных дней), просрочка 0, в работе 20 дней. В отчёте за период по 11.10.2026 и позже просрочка — число дней сверх 10.10.2026.
+3. КЗ-13 № 25-4/030: обращение от 20.08.2026, стадия «Комитет Холдинга», срок 19.09.2026 истёк — просрочка 11 дней, в работе 41 день; остаток 3 900 000,00 — после платежа 10.09.2026 (ФО-04).
+4. КЗ-06 № 20-2/090: обращение от 15.07.2026 закрыто исходом «одобрена»: решение комитета 10.08.2026 (26 дней от регистрации — в срок 30), письмо 14.08.2026 (4-й рабочий день — в срок 5), постановление Кабинета Министров 04.09.2026 (21 день от письма — в срок 70), соглашение 08.09.2026, в работе 55 дней. Остаток на дату закрытия 1 850 000,00 = остаток на дату соглашения в виде «Влияние» (1 800 000,00 на 01.10.2026 + 50 000,00 основной суммы, погашенных 12.09.2026, ФО-04). Дата соглашения = «Условия с» в ФО-09 и дата события в ФО-58.
+5. КЗ-23 № 20-5/118 (USD): обращение от 16.02.2026 закрыто исходом «отказ» по отрицательному заключению уполномоченного органа 05.05.2026, в работе 78 дней; остаток 90 000,00 USD × 87,50000 = 7 875 000,00, под обращением строка «в тыс. USD». Закрыто до начала периода — в отчёт за сентябрь 2026 не попадает.
+6. Строка разреза = сумма строк на уровень ниже по «Обращений», «С нарушением срока», «Кредитов» и «Остаток основной суммы в охвате».</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>КЗ-02, КЗ-06</t>
+          <t>КЗ-02, КЗ-06, КЗ-13, КЗ-23</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -7353,15 +7359,16 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>вид «Влияние реструктуризации: условия до и после»</t>
+          <t>вид «Влияние реструктуризации на условия кредитов за период»</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>1. Значения „До“ и „После“ по кредиту = расчёт реструктуризации по этому кредиту (бланк ФО-80) на дату соглашения.
-2. „Изменение процентов к уплате“ = „После“ − „До“ в каждой строке кредита; подытоги и ИТОГО равны сумме строк ниже.
-3. КЗ-06: один кредит № 20-2/090 от 12.08.2020, дополнительное соглашение № 2 от 08.09.2026; остаток 1 800 000,00; ставка 12,5 → 10,0 % и сроки 12.08.2027 → 12.08.2029 совпадают с версиями 1 и 2 в ФО-09; срок после соглашения позже срока до.
-4. Подытог заёмщика КЗ-06 равен его единственному кредиту; кредит, по которому обращение не дошло до вступления соглашения в силу, в отчёте не показан.</t>
+          <t>1. За сентябрь 2026 по всему набору — один кредит: КЗ-06 № 20-2/090, соглашение № 2 от 08.09.2026 по обращению от 15.07.2026. КЗ-02 и КЗ-13 (обращения в работе) и КЗ-23 (отказ) в вид не попадают.
+2. КЗ-06: остаток на 08.09.2026 1 850 000,00 = остаток на дату закрытия обращения в ФО-10. Ставка 12,50 → 10,00, срок возврата 12.08.2027 → 12.08.2029 — те же значения, что в ФО-09, вид «Изменения условий кредитов за период» (ставка; срок 84 → 108 мес.).
+3. КЗ-06: проценты к уплате с 08.09.2026 по графику равными долями, платёж 12-го числа, факт/365: до соглашения 108 233,45 (12 платежей по 12,50 %), после 271 840,18 (36 платежей по 10,00 %), изменение +163 606,73. Значения «До» и «После» = расчёту, по которому заключено соглашение.
+4. КЗ-06: прощено 0,00 и капитализировано 0,00 — штрафов и просроченных процентов на дату соглашения нет (ФО-07: штрафы КЗ-06 за сентябрь 0,00); виды обращения прощения и капитализации не содержат.
+5. „Изменение процентов к уплате“ = „После“ − „До“ в строке кредита; строка разреза = сумма строк на уровень ниже.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -11245,7 +11252,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>ставка 10 %; обращение о реструктуризации 15.07.2026, решение комитета № 31 от 10.08.2026, решение уполномоченного органа № 14/218 от 28.08.2026, дополнительное соглашение № 2 от 08.09.2026, новые условия с 01.10.2026</t>
+          <t>ставка 10 %; обращение о реструктуризации 15.07.2026, решение комитета № 31 от 10.08.2026, письмо уполномоченному органу 14.08.2026, заключение уполномоченного органа № 14/218 от 28.08.2026, постановление Кабинета Министров № 512 от 04.09.2026, дополнительное соглашение № 2 от 08.09.2026, новые условия с 08.09.2026; остаток на 08.09.2026 — 1 850 000,00</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -11686,17 +11693,17 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>кредит АПК</t>
+          <t>кредит АПК; обращение о реструктуризации от 20.08.2026 на стадии «Комитет Холдинга», срок стадии 19.09.2026 истёк — на 30.09.2026 просрочка срока 11 дней</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Кредит АПК; отчётность целевого использования через региональное представительство</t>
+          <t>Кредит АПК; отчётность целевого использования через региональное представительство; обращение о реструктуризации не вынесено на комитет в срок</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>ФО-06, ФО-13, ФО-77</t>
+          <t>ФО-06, ФО-10, ФО-13, ФО-77</t>
         </is>
       </c>
     </row>
@@ -12378,17 +12385,17 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>ставка 7 %; просрочка 245 дней: основная сумма 15 000,00 USD, проценты 4 050,00 USD, штрафы 1 200,00 USD; остаток в сомах по курсу 87,50 на 30.09.2026 — 7 875 000,00</t>
+          <t>ставка 7 %; просрочка 245 дней: основная сумма 15 000,00 USD, проценты 4 050,00 USD, штрафы 1 200,00 USD; остаток в сомах по курсу 87,50 на 30.09.2026 — 7 875 000,00; обращение о реструктуризации от 16.02.2026: решение комитета 13.03.2026, письмо уполномоченному органу 18.03.2026, отрицательное заключение № 14/061 от 05.05.2026 — отказ, взыскание возобновлено</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Кредит в долларах США с просрочкой 245 дней, исковое заявление в суд</t>
+          <t>Кредит в долларах США с просрочкой 245 дней: отказ в реструктуризации, исковое заявление в суд</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
         <is>
-          <t>ФО-01</t>
+          <t>ФО-01, ФО-10</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$129</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$116</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 7. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Списание задолженности за период</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -1434,59 +1434,67 @@
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название в старой системе — «Отчет по списанию» («Информация по списанию», по состоянию на дату)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>ФО-12</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Перевод долга</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>вид «Списанная задолженность по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по переводу долга»</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-12.xlsx</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 пп. 62, 65</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-11.xlsx</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>Внебалансовый учёт: списано, поступило после списания, не возвращено, идёт ли взыскание</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
@@ -1494,12 +1502,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-12</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Перевод долга</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1509,7 +1517,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1524,25 +1532,21 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по переводу долга»</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-12.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1550,12 +1554,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1580,21 +1584,25 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-13.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1602,12 +1610,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1632,25 +1640,21 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1658,12 +1662,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1688,21 +1692,25 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1710,107 +1718,107 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-16.xlsx</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -1823,7 +1831,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1848,12 +1856,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1875,7 +1883,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1900,12 +1908,12 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -1917,60 +1925,56 @@
       <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-18.xlsx</t>
-        </is>
-      </c>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-17.xlsx</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr"/>
+      <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -1978,12 +1982,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2008,17 +2012,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-18.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2034,12 +2038,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2049,7 +2053,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2064,17 +2068,17 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2090,12 +2094,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2105,7 +2109,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2120,21 +2124,25 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr"/>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2142,12 +2150,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -2157,7 +2165,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2172,7 +2180,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -2182,115 +2190,115 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-25.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D45" s="10" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E45" s="10" t="inlineStr">
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-26.xlsx</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr"/>
+      <c r="K46" s="10" t="inlineStr"/>
+      <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2298,12 +2306,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2328,7 +2336,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2338,7 +2346,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-26.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2350,12 +2358,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2380,7 +2388,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2390,7 +2398,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2402,12 +2410,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2417,7 +2425,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2432,7 +2440,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2442,7 +2450,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2454,12 +2462,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2469,7 +2477,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2484,7 +2492,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2494,7 +2502,7 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -2506,12 +2514,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2521,7 +2529,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2536,7 +2544,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2546,15 +2554,11 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2562,12 +2566,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2577,7 +2581,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2592,7 +2596,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2602,11 +2606,15 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2614,12 +2622,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2629,7 +2637,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2644,7 +2652,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2654,15 +2662,11 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="L53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -2670,12 +2674,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2685,12 +2689,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2700,7 +2704,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2710,13 +2714,13 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2730,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2741,12 +2745,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2756,7 +2760,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2766,11 +2770,15 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2778,12 +2786,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2793,12 +2801,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2808,7 +2816,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2818,19 +2826,11 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-59.xlsx</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>obrazcy/ФО-58.xlsx</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr"/>
+      <c r="L56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -2876,17 +2876,21 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J57" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-59.xlsx</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -2894,12 +2898,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2950,12 +2954,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2970,7 +2974,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3006,12 +3010,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3026,7 +3030,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3062,12 +3066,12 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3077,12 +3081,12 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -3092,20 +3096,24 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
       <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3114,59 +3122,51 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Бланк</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>язык интерфейса</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3222,7 +3222,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr"/>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -3230,12 +3234,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3260,12 +3264,12 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
@@ -3286,12 +3290,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3306,7 +3310,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3316,7 +3320,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3342,12 +3346,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3362,7 +3366,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3372,7 +3376,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -3398,167 +3402,171 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
+          <t>ФО-33</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик, залогодатель, орган регистрации</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H67" s="7" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>старая система «Акт сверки»</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="J68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr">
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D68" s="10" t="inlineStr">
+      <c r="D69" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G69" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Порядок №41 п. 64</t>
         </is>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J68" s="10" t="inlineStr">
+      <c r="J69" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K68" s="13" t="inlineStr">
+      <c r="K69" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L68" s="10" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>ФО-35</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>Департамент правового обеспечения</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>рус</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I69" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr"/>
-      <c r="L69" s="7" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -3566,12 +3574,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-35</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3596,12 +3604,12 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
@@ -3618,12 +3626,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3638,7 +3646,7 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -3648,7 +3656,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -3670,12 +3678,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3690,22 +3698,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3713,11 +3721,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3726,12 +3730,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3746,22 +3750,22 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -3769,7 +3773,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="7" t="inlineStr"/>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3778,12 +3786,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -3793,22 +3801,22 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -3821,11 +3829,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K74" s="7" t="inlineStr"/>
       <c r="L74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3834,171 +3838,171 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
+          <t>ФО-40</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Справка о задолженности</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Реестр погашений</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>старая система, распечатка «Реестр погашений»</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="J76" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C76" s="11" t="inlineStr">
+      <c r="C77" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E77" s="10" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F76" s="10" t="inlineStr">
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G76" s="10" t="inlineStr">
+      <c r="G77" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>ТЗ 14</t>
         </is>
       </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J76" s="10" t="inlineStr">
+      <c r="J77" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K76" s="13" t="inlineStr">
+      <c r="K77" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L76" s="10" t="inlineStr">
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>ФО-42</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>График погашения</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>График</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>старая система, выгрузка графика</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -4006,12 +4010,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-42</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>График погашения</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4021,27 +4025,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>График</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система, выгрузка графика</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4049,7 +4053,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr"/>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4058,12 +4066,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4073,27 +4081,27 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4101,11 +4109,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K79" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K79" s="7" t="inlineStr"/>
       <c r="L79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
@@ -4114,12 +4118,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4129,12 +4133,12 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4144,12 +4148,12 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
@@ -4170,12 +4174,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4190,7 +4194,7 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4200,7 +4204,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4226,12 +4230,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4241,12 +4245,12 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -4256,7 +4260,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -4282,12 +4286,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4338,12 +4342,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4394,12 +4398,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4414,7 +4418,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -4424,7 +4428,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4450,12 +4454,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4465,22 +4469,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4493,7 +4497,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr"/>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4502,12 +4510,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4517,22 +4525,22 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4545,11 +4553,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4558,12 +4562,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4578,17 +4582,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4601,7 +4605,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr"/>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4610,12 +4618,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4630,17 +4638,17 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4653,11 +4661,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K89" s="7" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4666,12 +4670,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4681,22 +4685,22 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4709,7 +4713,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr"/>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4718,12 +4726,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4738,17 +4746,17 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4761,11 +4769,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K91" s="7" t="inlineStr"/>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4774,12 +4778,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4789,22 +4793,22 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4817,7 +4821,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr"/>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
@@ -4826,12 +4834,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4841,7 +4849,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -4856,7 +4864,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4878,12 +4886,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4908,7 +4916,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -4930,12 +4938,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4982,12 +4990,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -5034,12 +5042,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5049,7 +5057,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -5064,7 +5072,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5086,12 +5094,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5116,7 +5124,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5138,12 +5146,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5158,7 +5166,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -5168,7 +5176,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5190,12 +5198,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5220,7 +5228,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5242,12 +5250,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5257,12 +5265,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5272,7 +5280,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
@@ -5294,12 +5302,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5309,12 +5317,12 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -5324,12 +5332,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5346,12 +5354,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5376,12 +5384,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5398,12 +5406,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5428,12 +5436,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5450,12 +5458,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5470,7 +5478,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5480,12 +5488,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5502,12 +5510,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5517,12 +5525,12 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -5532,12 +5540,12 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
@@ -5554,12 +5562,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5569,22 +5577,22 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5597,16 +5605,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K107" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="K107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5662,7 +5662,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L108" s="7" t="inlineStr"/>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -5670,12 +5674,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5690,7 +5694,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5700,7 +5704,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5726,12 +5730,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5741,12 +5745,12 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -5756,7 +5760,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5782,12 +5786,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5797,7 +5801,7 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -5812,7 +5816,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5830,11 +5834,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5890,7 +5890,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L112" s="7" t="inlineStr"/>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -5898,12 +5902,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5918,7 +5922,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5928,7 +5932,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5954,12 +5958,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5969,12 +5973,12 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -5984,7 +5988,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -6010,12 +6014,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6025,22 +6029,22 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -6053,7 +6057,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr"/>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6062,12 +6070,12 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -6082,12 +6090,12 @@
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -6105,11 +6113,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K116" s="7" t="inlineStr"/>
       <c r="L116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
@@ -6118,115 +6122,115 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
+          <t>ФО-89</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к договору залога</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>залогодатель</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 12</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C118" s="7" t="inlineStr">
         <is>
           <t>Письмо по кредиту</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E118" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>по виду письма</t>
         </is>
       </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="G118" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H117" s="7" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr">
+      <c r="I118" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J117" s="7" t="inlineStr">
+      <c r="J118" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K117" s="13" t="inlineStr">
+      <c r="K118" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>Один бланк с видами ниже; у каждого вида свой текст</t>
         </is>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C118" s="11" t="inlineStr">
-        <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
-        </is>
-      </c>
-      <c r="D118" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E118" s="10" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="F118" s="10" t="inlineStr">
-        <is>
-          <t>уполномоченный государственный орган</t>
-        </is>
-      </c>
-      <c r="G118" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H118" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J118" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K118" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="n">
@@ -6239,7 +6243,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6249,12 +6253,12 @@
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6264,7 +6268,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6295,7 +6299,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6310,7 +6314,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6320,7 +6324,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6351,7 +6355,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6366,7 +6370,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6376,7 +6380,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6407,7 +6411,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6417,12 +6421,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6432,7 +6436,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6463,7 +6467,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6473,12 +6477,12 @@
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6488,7 +6492,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6519,7 +6523,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6534,7 +6538,7 @@
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6544,7 +6548,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6575,7 +6579,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -6585,12 +6589,12 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6600,7 +6604,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -6631,106 +6635,106 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E126" s="10" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F126" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 21</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J126" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L126" s="10" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
           <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
-      <c r="D126" s="10" t="inlineStr">
+      <c r="D127" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E126" s="10" t="inlineStr">
+      <c r="E127" s="10" t="inlineStr">
         <is>
           <t>Заявка и комиссия</t>
         </is>
       </c>
-      <c r="F126" s="10" t="inlineStr">
+      <c r="F127" s="10" t="inlineStr">
         <is>
           <t>заявитель</t>
         </is>
       </c>
-      <c r="G126" s="10" t="inlineStr">
+      <c r="G127" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H126" s="10" t="inlineStr">
+      <c r="H127" s="10" t="inlineStr">
         <is>
           <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
-      <c r="I126" s="10" t="inlineStr">
+      <c r="I127" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="J127" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K126" s="13" t="inlineStr">
+      <c r="K127" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L126" s="10" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B127" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-1</t>
-        </is>
-      </c>
-      <c r="C127" s="7" t="inlineStr">
-        <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="inlineStr">
-        <is>
-          <t>Все модули</t>
-        </is>
-      </c>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H127" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
-        </is>
-      </c>
-      <c r="I127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K127" s="7" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
+      <c r="L127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -6738,54 +6742,110 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
           <t>ОТ-2</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>Требование</t>
         </is>
       </c>
-      <c r="E128" s="7" t="inlineStr">
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>Отчётность</t>
         </is>
       </c>
-      <c r="F128" s="7" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G128" s="7" t="inlineStr">
+      <c r="G129" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H128" s="7" t="inlineStr">
+      <c r="H129" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr">
+      <c r="I129" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J128" s="7" t="inlineStr">
+      <c r="J129" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K128" s="7" t="inlineStr"/>
-      <c r="L128" s="7" t="inlineStr"/>
+      <c r="K129" s="7" t="inlineStr"/>
+      <c r="L129" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L128"/>
+  <autoFilter ref="A17:L129"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6841,7 +6901,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6854,7 +6915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7393,16 +7454,17 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Списание задолженности</t>
+          <t>Списание задолженности за период</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма списания по кредиту = сумме списания в карточке кредита (вкладка «Списание»).
-2. «Всего» = основная сумма + проценты + штрафы в каждой строке.
-3. КЗ-08 за сентябрь 2026 показан со списанием всего долга; после списания остаток кредита 0,00.
-4. Подытог и ИТОГО = сумма строк ниже по каждой числовой колонке.
-5. Списание не входит в «Погашения за период» (ФО-04).</t>
+          <t>1. Сентябрь 2026: 1 заёмщик, 1 кредит, 1 списание — КЗ-08 ОсОО «Тянь-Шань Металл», № 20-3/052 от 21.07.2020, списан 17.09.2026 по заключению Постоянно-действующей комиссии № 31 от 10.09.2026: всего 900,500 тыс. сом = основная сумма 750,000 + проценты 112,500 + штрафы 38,000; вид списания — «весь долг».
+2. «Всего списано» каждой строки = по основной сумме + по процентам + по штрафам; строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.
+3. Списано по процентам и штрафам = ФО-07 за тот же период: 112,500 и 38,000. Проценты и штрафы — числившиеся на день списания: проценты 109,167 на начало сентября + начислено по 17.09.2026 3,333; штрафы 36,800 + 1,200.
+4. В ФО-02 на 01.10.2026 остаток КЗ-08 — 0,00; в ФО-04 за сентябрь списание не показано; в ФО-58 — то же событие «Закрытие: списан» 17.09.2026 с тем же основанием.
+5. Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-12), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.
+6. Период 01.01.2026–30.09.2026 — то же одно списание: других списаний в контрольном наборе нет.</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -7417,20 +7479,52 @@
       <c r="J17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>ФО-11</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>вид «Списанная задолженность по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>1. На 01.10.2026: 1 заёмщик, 1 кредит — КЗ-08 № 20-3/052, списан 17.09.2026: списано 900,500 (основная сумма 750,000 + проценты 112,500 + штрафы 38,000), поступило после списания 0,000, не возвращено 900,500; взыскание — «не ведётся»: иска, исполнительного листа и залога в обращении взыскания по кредиту нет.
+2. «Всего списано» по кредиту = основному отчёту ФО-11 за период с первого списания по дату отчёта; у кредита в сомах не возвращено = всего списано − поступило после списания; строка разреза = сумма строк ниже.
+3. Остаток списанного кредита в ФО-02 — 0,00, и в просрочку (ФО-01) он не попадает; поступление после списания в ФО-04 — обычный платёж.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-08</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>ФО-12</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Перевод долга</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
 2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
@@ -7438,32 +7532,32 @@
 4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>КЗ-07</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
-      <c r="J18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ФО-13</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Целевое использование средств</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
 2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
@@ -7472,32 +7566,32 @@
 5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>КЗ-12, КЗ-13</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ФО-14</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7507,32 +7601,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7542,32 +7636,32 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>ФО-16</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
 2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
@@ -7576,32 +7670,32 @@
 5. Все даты снятия попадают в период отчёта.</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7611,32 +7705,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7644,32 +7738,32 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
 2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
@@ -7678,42 +7772,9 @@
 5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>КЗ-02</t>
-        </is>
-      </c>
-      <c r="F25" s="10" t="inlineStr"/>
-      <c r="G25" s="10" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr"/>
-      <c r="I25" s="10" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
@@ -7723,20 +7784,53 @@
       <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+      <c r="H27" s="10" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7745,32 +7839,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7780,32 +7874,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7815,32 +7909,32 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>ФО-24</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
 2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
@@ -7849,32 +7943,32 @@
 5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
 2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
@@ -7883,32 +7977,32 @@
 5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7917,32 +8011,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+      <c r="H33" s="10" t="inlineStr"/>
+      <c r="I33" s="10" t="inlineStr"/>
+      <c r="J33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7951,32 +8045,32 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>ФО-27</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
 2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
@@ -7985,39 +8079,6 @@
 5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>ФО-28</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Доля проблемных кредитов</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
-        </is>
-      </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -8035,15 +8096,48 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
+          <t>ФО-28</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Доля проблемных кредитов</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
           <t>ФО-47</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Реестр имущества на дату</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
 2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
@@ -8052,32 +8146,32 @@
 5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>КЗ-16</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>ФО-53</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
 2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
@@ -8086,32 +8180,32 @@
 5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>КЗ-11</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>ФО-54</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>План-факт погашений</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8121,32 +8215,32 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-02</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>ФО-55</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Заявки по программам и статусам</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
 2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
@@ -8155,42 +8249,9 @@
 5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>КЗ-17, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>ФО-56</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>План и факт выдачи</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -8205,15 +8266,48 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
+          <t>ФО-56</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>План и факт выдачи</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
           <t>ФО-57</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8223,32 +8317,32 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>ФО-58</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
 2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
@@ -8257,32 +8351,32 @@
 5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>ФО-59</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>Кредитный риск портфеля</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8292,41 +8386,9 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>ФО-91</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
@@ -8341,12 +8403,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8373,12 +8435,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8405,12 +8467,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -8437,15 +8499,47 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Состав — по образцу заказчика</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8456,42 +8550,9 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>КЗ-15, КЗ-16</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr"/>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>ФО-29</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Уведомление о наступающем платеже</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
@@ -8506,15 +8567,48 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
           <t>ФО-30</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Первичная претензия</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
 2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
@@ -8523,32 +8617,32 @@
 5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>КЗ-02</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>ФО-31</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Повторная претензия</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
 2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
@@ -8557,32 +8651,32 @@
 5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>ФО-32</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
 2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
@@ -8591,32 +8685,32 @@
 5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>ФО-33</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
 2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
@@ -8625,42 +8719,9 @@
 5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr"/>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
@@ -8670,20 +8731,53 @@
       <c r="J54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="n">
+      <c r="A55" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Акт сверки задолженности на 1 января</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8692,32 +8786,32 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="inlineStr"/>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr"/>
+      <c r="G56" s="10" t="inlineStr"/>
+      <c r="H56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="inlineStr"/>
+      <c r="J56" s="10" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
@@ -8726,32 +8820,32 @@
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>ФО-36</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
 2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
@@ -8760,32 +8854,32 @@
 5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>ФО-37</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
 2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
@@ -8794,32 +8888,32 @@
 5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
-      <c r="J58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>ФО-38</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Исковое заявление</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
 2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
@@ -8828,32 +8922,32 @@
 5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>ФО-39</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
 2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
@@ -8862,32 +8956,32 @@
 5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>ФО-40</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Справка о задолженности</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8897,39 +8991,6 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -8942,20 +9003,53 @@
       <c r="J62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -8964,32 +9058,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr"/>
-      <c r="H63" s="10" t="inlineStr"/>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr"/>
+      <c r="G64" s="10" t="inlineStr"/>
+      <c r="H64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -8997,32 +9091,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -9032,32 +9126,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -9067,32 +9161,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -9102,42 +9196,9 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ФО-46</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Договор поручительства</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9152,25 +9213,25 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
@@ -9185,20 +9246,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9218,20 +9279,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9251,20 +9312,20 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -9284,15 +9345,48 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
+          <t>ФО-51</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Претензия покупателю</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-16</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
           <t>ФО-52</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Справка по заёмщику</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
 2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
@@ -9301,32 +9395,32 @@
 5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>ФО-60</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Опись предметов залога по договору</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
 2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
@@ -9335,32 +9429,32 @@
 5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>ФО-61</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9370,39 +9464,6 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr"/>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>ФО-62</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
-        </is>
-      </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9420,25 +9481,25 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -9453,15 +9514,48 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
+          <t>ФО-63</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по заявкам</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
           <t>ФО-64</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9471,32 +9565,32 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Бланк печатается пустым, данных набора не требует</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr"/>
+      <c r="G79" s="7" t="inlineStr"/>
+      <c r="H79" s="7" t="inlineStr"/>
+      <c r="I79" s="7" t="inlineStr"/>
+      <c r="J79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>ФО-65</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Карточка организации</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
 2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
@@ -9505,42 +9599,9 @@
 5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>Карточка организации из справочника ведомств</t>
-        </is>
-      </c>
-      <c r="F79" s="7" t="inlineStr"/>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="n">
-        <v>76</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>ФО-66</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Журнал регистрации документов за период</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -9555,20 +9616,20 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -9588,15 +9649,48 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
+          <t>ФО-67</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Лист ознакомления</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>ФО-68</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>Опись дела</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9606,39 +9700,6 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr"/>
-      <c r="I82" s="7" t="inlineStr"/>
-      <c r="J82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>ФО-69</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Регистрационно-контрольная карточка документа</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
-        </is>
-      </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9656,15 +9717,48 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
           <t>ФО-70</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
 2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
@@ -9673,32 +9767,32 @@
 5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>ФО-71</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
 2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
@@ -9707,32 +9801,32 @@
 5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
         </is>
       </c>
-      <c r="F85" s="7" t="inlineStr"/>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>ФО-72</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
 2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
@@ -9741,42 +9835,9 @@
 5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>КЗ-09</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr"/>
-      <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr"/>
-      <c r="J86" s="7" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>ФО-73</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Служебная записка об инициировании банкротства</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
-        </is>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
@@ -9791,15 +9852,48 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
+          <t>ФО-73</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании банкротства</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-10</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
           <t>ФО-74</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
 2. Суммы в таблице = справке об обеспеченности на дату записки.
@@ -9808,32 +9902,32 @@
 5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>ФО-75</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9843,39 +9937,6 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr"/>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>ФО-76</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
-        </is>
-      </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9893,25 +9954,25 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -9926,15 +9987,48 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
+          <t>ФО-77</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-13</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr"/>
+      <c r="J92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
           <t>ФО-78</t>
         </is>
       </c>
-      <c r="C92" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
 2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
@@ -9943,42 +10037,9 @@
 5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F92" s="7" t="inlineStr"/>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
-      <c r="J92" s="7" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>ФО-79</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>Внутренний акт сверки платежей</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -9993,15 +10054,48 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
+          <t>ФО-79</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Внутренний акт сверки платежей</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="n">
+        <v>91</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
           <t>ФО-80</t>
         </is>
       </c>
-      <c r="C94" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
-      <c r="D94" s="7" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
 2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
@@ -10010,39 +10104,6 @@
 5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="7" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>ФО-81</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
-        </is>
-      </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
           <t>КЗ-06</t>
@@ -10060,15 +10121,48 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
+          <t>ФО-81</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к кредитному договору</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
           <t>ФО-82</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Соглашение о переводе долга</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
 2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
@@ -10077,32 +10171,32 @@
 5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>КЗ-07</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr"/>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="7" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>ФО-83</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
 2. Сумма строк графика = сумме, присуждённой судебным актом.
@@ -10111,32 +10205,32 @@
 5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr"/>
+      <c r="J98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>ФО-84</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
 2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
@@ -10145,42 +10239,9 @@
 5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>КЗ-18</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr"/>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="7" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B99" s="8" t="inlineStr">
-        <is>
-          <t>ФО-85</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
-        </is>
-      </c>
-      <c r="E99" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
@@ -10195,15 +10256,48 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
+          <t>ФО-85</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт распределения выручки от реализации залога</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-04</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr"/>
+      <c r="J100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
           <t>ФО-86</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
 2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
@@ -10212,42 +10306,9 @@
 5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr"/>
-      <c r="J100" s="7" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t>ФО-87</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10262,25 +10323,25 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
@@ -10295,15 +10356,48 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
+          <t>ФО-88</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Паспорт предмета залога</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr"/>
+      <c r="G103" s="7" t="inlineStr"/>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
           <t>ФО-89</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
 2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
@@ -10312,42 +10406,9 @@
 5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr"/>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
@@ -10357,20 +10418,53 @@
       <c r="J104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="10" t="n">
+      <c r="A105" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Письмо по кредиту</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется по видам</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
+      <c r="I105" s="7" t="inlineStr"/>
+      <c r="J105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10378,42 +10472,9 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
-      <c r="E105" s="10" t="inlineStr">
+      <c r="E106" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F105" s="10" t="inlineStr"/>
-      <c r="G105" s="10" t="inlineStr"/>
-      <c r="H105" s="10" t="inlineStr"/>
-      <c r="I105" s="10" t="inlineStr"/>
-      <c r="J105" s="10" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
-        <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
-        </is>
-      </c>
-      <c r="D106" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
-        </is>
-      </c>
-      <c r="E106" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr"/>
@@ -10433,15 +10494,15 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
+4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
@@ -10466,20 +10527,20 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
-2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
-3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
-4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
+2. Каждый запрос получает отдельный исходящий номер.
+3. Данные умершего заёмщика = карточке субъекта.
+4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
@@ -10499,10 +10560,43 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
+2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
+3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
+4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-10</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
           <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
-      <c r="D109" s="10" t="inlineStr">
+      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
 2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
@@ -10511,32 +10605,32 @@
 5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>КЗ-12</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr"/>
-      <c r="G109" s="10" t="inlineStr"/>
-      <c r="H109" s="10" t="inlineStr"/>
-      <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr"/>
+      <c r="G110" s="10" t="inlineStr"/>
+      <c r="H110" s="10" t="inlineStr"/>
+      <c r="I110" s="10" t="inlineStr"/>
+      <c r="J110" s="10" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>1. Форма доступна, только если по договору освобождены все доли предметов (полное снятие) либо выбрана часть предмета при частичном снятии.
 2. Основание выбрано из классификатора; при полном погашении указан акт сверки о полном погашении (ФО-34).
@@ -10546,41 +10640,9 @@
 6. Зарегистрированное письмо видно в ФО-19.</t>
         </is>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F110" s="10" t="inlineStr"/>
-      <c r="G110" s="10" t="inlineStr"/>
-      <c r="H110" s="10" t="inlineStr"/>
-      <c r="I110" s="10" t="inlineStr"/>
-      <c r="J110" s="10" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
-2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
-3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
-        </is>
-      </c>
-      <c r="E111" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
@@ -10600,20 +10662,19 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
-2. Перечень документов в письме = составу пакета действующей редакции методики.
-3. Установленная дата в письме не раньше даты запроса.
-4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
+          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
+2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
+3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>КЗ-17</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr"/>
@@ -10633,14 +10694,15 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
-2. Перечень недостатков в письме = замечаниям комиссии по заявке.
-3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
+          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
+2. Перечень документов в письме = составу пакета действующей редакции методики.
+3. Установленная дата в письме не раньше даты запроса.
+4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -10655,20 +10717,52 @@
       <c r="J113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="n">
+      <c r="A114" s="10" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
+2. Перечень недостатков в письме = замечаниям комиссии по заявке.
+3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr"/>
+      <c r="G114" s="10" t="inlineStr"/>
+      <c r="H114" s="10" t="inlineStr"/>
+      <c r="I114" s="10" t="inlineStr"/>
+      <c r="J114" s="10" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>ОТ-1</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>Выгрузка любого экранного списка в xlsx</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D115" s="7" t="inlineStr">
         <is>
           <t>1. Файл xlsx содержит те же колонки, в том же порядке и с теми же заголовками, что видны на экране; скрытые колонки не выгружаются.
 2. Число строк в файле = число строк списка с учётом всех фильтров и поиска, а не только текущей страницы.
@@ -10679,32 +10773,32 @@
 7. Список с фильтром, не давшим строк, выгружается как файл с заголовками и без строк.</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Проверяется на списках всех модулей</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr"/>
-      <c r="I114" s="7" t="inlineStr"/>
-      <c r="J114" s="7" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="7" t="inlineStr"/>
+      <c r="J115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>ОТ-2</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C116" s="7" t="inlineStr">
         <is>
           <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D116" s="7" t="inlineStr">
         <is>
           <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
 2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
@@ -10713,33 +10807,33 @@
 5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E116" s="7" t="inlineStr">
         <is>
           <t>Проверяется на каждой строке перечня</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="7" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="7" t="inlineStr"/>
+      <c r="J116" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>Сдал: ____________________ (разработчик)          Принял: ____________________ (заказчик)          Дата: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J115"/>
+  <autoFilter ref="A4:J116"/>
   <mergeCells count="3">
-    <mergeCell ref="A117:J117"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A118:J118"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сдано,сдано с замечанием,не сдано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11388,7 +11482,7 @@
       </c>
       <c r="M13" s="7" t="inlineStr">
         <is>
-          <t>ФО-09, ФО-11, ФО-58</t>
+          <t>ФО-09, ФО-11, ФО-11|Списанная, ФО-58</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 37 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 36 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1532,21 +1532,25 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–377, ¶428–431; старая система</t>
+          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по переводу долга»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-12.xlsx</t>
+          <t>obrazcy/ФО-13.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1554,12 +1558,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1569,7 +1573,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1584,25 +1588,21 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1640,21 +1640,25 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1662,12 +1666,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1692,25 +1696,21 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-16.xlsx</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n">
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1748,77 +1748,77 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="H39" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -1925,56 +1925,60 @@
       <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G40" s="10" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" s="10" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-18.xlsx</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
@@ -1982,12 +1986,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2012,17 +2016,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-18.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2038,12 +2042,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2053,7 +2057,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2068,17 +2072,17 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
@@ -2094,12 +2098,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2109,7 +2113,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2124,25 +2128,21 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -2190,115 +2190,115 @@
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K46" s="10" t="inlineStr"/>
-      <c r="L46" s="10" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-26.xlsx</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-26.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2554,11 +2554,15 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2566,12 +2570,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2581,7 +2585,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2596,7 +2600,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2606,15 +2610,11 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2662,11 +2662,15 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -2674,12 +2678,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2689,12 +2693,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2704,7 +2708,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2714,13 +2718,13 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2734,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2745,12 +2749,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2770,15 +2774,11 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-58.xlsx</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2826,11 +2826,19 @@
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr"/>
-      <c r="L56" s="7" t="inlineStr"/>
+          <t>obrazcy/ФО-59.xlsx</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2838,12 +2846,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2853,12 +2861,12 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2868,7 +2876,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -2876,21 +2884,17 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-59.xlsx</t>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -2898,12 +2902,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2918,7 +2922,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2954,12 +2958,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2974,7 +2978,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3010,12 +3014,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3030,7 +3034,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3066,12 +3070,12 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3081,12 +3085,12 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -3096,24 +3100,20 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3122,51 +3122,59 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Бланк</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>язык интерфейса</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3174,12 +3182,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3204,12 +3212,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3222,11 +3230,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+      <c r="L63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -3234,12 +3238,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3264,12 +3268,12 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
@@ -3290,12 +3294,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3310,7 +3314,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3320,7 +3324,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3346,12 +3350,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3366,7 +3370,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик, залогодатель, орган регистрации</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3376,7 +3380,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -3402,12 +3406,12 @@
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -3422,7 +3426,7 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -3432,141 +3436,137 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
+          <t>старая система «Акт сверки»</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>вид «Акт сверки о полном погашении задолженности»</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 64</t>
+        </is>
+      </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="L68" s="10" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>ФО-35</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Акт сверки»</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>Департамент правового обеспечения</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>рус</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C69" s="11" t="inlineStr">
-        <is>
-          <t>вид «Акт сверки о полном погашении задолженности»</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F69" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 64</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L69" s="10" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-35</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3698,22 +3698,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3721,7 +3721,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr"/>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3730,12 +3734,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3750,22 +3754,22 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -3773,11 +3777,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -3801,22 +3801,22 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -3829,7 +3829,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="7" t="inlineStr"/>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -3838,12 +3842,12 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-41</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Реестр погашений</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -3853,7 +3857,7 @@
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -3868,141 +3872,141 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
+          <t>старая система, распечатка «Реестр погашений»</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>вид «Выписка по кредиту»</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Платежи</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>ФО-42</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>График погашения</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Реестр погашений»</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>старая система, выгрузка графика</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K76" s="13" t="inlineStr">
+      <c r="K77" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>вид «Выписка по кредиту»</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L77" s="10" t="inlineStr">
-        <is>
-          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
-        </is>
-      </c>
+      <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -4010,12 +4014,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-42</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>График погашения</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4025,27 +4029,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>старая система, выгрузка графика</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4053,11 +4057,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K78" s="7" t="inlineStr"/>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4081,27 +4081,27 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4109,7 +4109,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr"/>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
@@ -4118,12 +4122,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4133,12 +4137,12 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4148,12 +4152,12 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J80" s="7" t="inlineStr">
@@ -4174,12 +4178,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4194,7 +4198,7 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4204,7 +4208,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4230,12 +4234,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4245,12 +4249,12 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
@@ -4260,7 +4264,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
@@ -4286,12 +4290,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4342,12 +4346,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4418,7 +4422,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -4428,7 +4432,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4454,12 +4458,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4469,22 +4473,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4497,11 +4501,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4553,7 +4553,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr"/>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4562,12 +4566,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4582,17 +4586,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4605,11 +4609,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K88" s="7" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4661,7 +4661,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="7" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4670,12 +4674,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4685,22 +4689,22 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4713,11 +4717,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K90" s="7" t="inlineStr"/>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4746,17 +4746,17 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4769,7 +4769,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr"/>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4778,12 +4782,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4793,22 +4797,22 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4821,11 +4825,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K92" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K92" s="7" t="inlineStr"/>
       <c r="L92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
@@ -4834,12 +4834,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J106" s="7" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5577,22 +5577,22 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5605,8 +5605,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K107" s="7" t="inlineStr"/>
-      <c r="L107" s="7" t="inlineStr"/>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5614,12 +5622,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5629,12 +5637,12 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5644,7 +5652,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5662,11 +5670,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="L108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -5674,12 +5678,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5694,7 +5698,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5704,7 +5708,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5730,12 +5734,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5745,12 +5749,12 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
@@ -5760,7 +5764,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5786,12 +5790,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5801,7 +5805,7 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
@@ -5816,7 +5820,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5834,7 +5838,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5842,12 +5850,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5857,12 +5865,12 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5872,7 +5880,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5890,11 +5898,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L112" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -5902,12 +5906,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5922,7 +5926,7 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5932,7 +5936,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5958,12 +5962,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5973,12 +5977,12 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
@@ -5988,7 +5992,7 @@
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -6014,12 +6018,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6029,22 +6033,22 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>ТЗ 12</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -6057,11 +6061,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K115" s="7" t="inlineStr"/>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
@@ -6113,7 +6113,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="7" t="inlineStr"/>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
@@ -6122,12 +6126,12 @@
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -6137,12 +6141,12 @@
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>по виду письма</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -6152,7 +6156,7 @@
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
@@ -6170,53 +6174,57 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr"/>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="n">
+      <c r="A118" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
+        <is>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>по виду письма</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
+      <c r="E118" s="10" t="inlineStr">
+        <is>
+          <t>Реструктуризация</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>уполномоченный государственный орган</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
-        </is>
-      </c>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="H118" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
+        </is>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J118" s="7" t="inlineStr">
+      <c r="J118" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6226,11 +6234,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L118" s="7" t="inlineStr">
-        <is>
-          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
-        </is>
-      </c>
+      <c r="L118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="n">
@@ -6243,7 +6247,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6253,12 +6257,12 @@
       </c>
       <c r="E119" s="10" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6268,7 +6272,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6299,7 +6303,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6314,7 +6318,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6324,7 +6328,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6355,7 +6359,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6370,7 +6374,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6380,7 +6384,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6411,7 +6415,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6421,12 +6425,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6436,7 +6440,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6467,7 +6471,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6477,12 +6481,12 @@
       </c>
       <c r="E123" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6492,7 +6496,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6523,7 +6527,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6538,7 +6542,7 @@
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6548,7 +6552,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6579,7 +6583,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -6589,12 +6593,12 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6604,7 +6608,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>ТЗ 21</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -6635,7 +6639,7 @@
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
@@ -6645,12 +6649,12 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr">
@@ -6660,7 +6664,7 @@
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr">
@@ -6681,60 +6685,60 @@
       <c r="L126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="10" t="n">
+      <c r="A127" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>Заявка и комиссия</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t>заявитель</t>
-        </is>
-      </c>
-      <c r="G127" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr">
-        <is>
-          <t>ПКМ №554 пп. 66, 74</t>
-        </is>
-      </c>
-      <c r="I127" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K127" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L127" s="10" t="inlineStr"/>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n">
@@ -6742,12 +6746,12 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>ОТ-1</t>
+          <t>ОТ-2</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -6757,7 +6761,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Все модули</t>
+          <t>Отчётность</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -6772,7 +6776,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
@@ -6786,66 +6790,10 @@
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr"/>
-      <c r="L128" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="7" t="n">
-        <v>112</v>
-      </c>
-      <c r="B129" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>Отчётность</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
-        </is>
-      </c>
-      <c r="I129" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K129" s="7" t="inlineStr"/>
-      <c r="L129" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L129"/>
+  <autoFilter ref="A17:L128"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6901,8 +6849,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6915,7 +6862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7100,7 +7047,7 @@
 5. У КЗ-01 «Ак-Дан» два кредита, у каждого своя строка и свой платёж: № 21-3/117 — п/п 4417 от 15.09.2026 (170,625), № 22-2/031 — п/п 4398 от 11.09.2026 (112,500).
 6. Платёж КЗ-11 по кредиту в долларах США — в сомах, как поступил: 461,035 тыс. сом (основная сумма 437,000, проценты 24,035); строки в валюте нет.
 7. Платёж КЗ-15 от 18.09.2026 (полное погашение, 520,000) в отчёте есть, хотя на 01.10.2026 кредит закрыт.
-8. Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 (ФО-12) и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.
+8. Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.
 9. Остальные заёмщики набора в сентябре 2026 не платили и не показаны; платёж КЗ-24 от 14.08.2026 — в отчёте за август.
 10. Отбор «вид погашения: имущество в счёт погашения» за 01.01.2026–30.09.2026 — только КЗ-16, платёж 20.03.2026 на 4 250,000 тыс. сом.
 11. У г. Бишкек и г. Ош по две строки: область и район.</t>
@@ -7463,7 +7410,7 @@
 2. «Всего списано» каждой строки = по основной сумме + по процентам + по штрафам; строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.
 3. Списано по процентам и штрафам = ФО-07 за тот же период: 112,500 и 38,000. Проценты и штрафы — числившиеся на день списания: проценты 109,167 на начало сентября + начислено по 17.09.2026 3,333; штрафы 36,800 + 1,200.
 4. В ФО-02 на 01.10.2026 остаток КЗ-08 — 0,00; в ФО-04 за сентябрь списание не показано; в ФО-58 — то же событие «Закрытие: списан» 17.09.2026 с тем же основанием.
-5. Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-12), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.
+5. Не попадают: КЗ-15 (погашен 18.09.2026 — ФО-95), КЗ-07 (перевод долга 09.09.2026 — ФО-58), КЗ-16 (погашен имуществом 20.03.2026 — ФО-04), кредиты в группе «4. Безнадёжные долги» без решения о списании.
 6. Период 01.01.2026–30.09.2026 — то же одно списание: других списаний в контрольном наборе нет.</t>
         </is>
       </c>
@@ -7516,25 +7463,26 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-12</t>
+          <t>ФО-13</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Перевод долга</t>
+          <t>Целевое использование средств</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1. Данные перевода = вкладке «Перевод долга» карточки кредита (дата, номер, сумма, валюта, стороны).
-2. У КЗ-07 за сентябрь 2026 один перевод: новый заёмщик — ОсОО «Ысык-Көл Логистик».
-3. Подытог и ИТОГО = сумма строк ниже по числовым колонкам.
-4. Для кредита, выданного деньгами, колонки «Предмет», «Количество», «Цена» пусты.</t>
+          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
+2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
+3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
+4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
+5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-12, КЗ-13</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -7549,49 +7497,15 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
-2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
-3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
-4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
-5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12, КЗ-13</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>ФО-14</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Залоговое обеспечение — предметы</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7601,32 +7515,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7636,9 +7550,43 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
+2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
+3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
+4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
+5. Все даты снятия попадают в период отчёта.</t>
+        </is>
+      </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-15</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
@@ -7653,49 +7601,15 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
-2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
-3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
-4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
-5. Все даты снятия попадают в период отчёта.</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7705,32 +7619,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7738,9 +7652,43 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>вид «Претензии по областям за период»</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
+2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
+3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
+4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
+5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+        </is>
+      </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7760,21 +7708,20 @@
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
-2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
-3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
-4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
-5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr"/>
@@ -7784,53 +7731,20 @@
       <c r="J26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F27" s="10" t="inlineStr"/>
-      <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="10" t="inlineStr"/>
-      <c r="J27" s="10" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7839,32 +7753,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7874,32 +7788,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7909,9 +7823,43 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ФО-24</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Классификация — движение по группам платёжеспособности</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
+2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
+3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
+4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
+5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+        </is>
+      </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -7926,26 +7874,26 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
-2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
-3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
-4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
-5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
+2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
+3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
+4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
+5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-19</t>
+          <t>весь набор</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -7955,54 +7903,20 @@
       <c r="J31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
-2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
-3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
-4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
-5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -8011,32 +7925,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr"/>
-      <c r="I33" s="10" t="inlineStr"/>
-      <c r="J33" s="10" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -8045,6 +7959,40 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>ФО-27</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Средняя просрочка по департаментам</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
+2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
+3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
+4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
+5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+        </is>
+      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -8062,21 +8010,20 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
-2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
-3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
-4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
-5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -8096,25 +8043,26 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
+2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
+3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
+4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
+5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -8129,26 +8077,26 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
-2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
-3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
-4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
-5. Подытог по состоянию и источнику = сумма строк ниже.</t>
+          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
+2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
+3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
+4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
+5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-11</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -8163,49 +8111,15 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
-2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
-3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
-4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
-5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-11</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-54</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>План-факт погашений</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8215,9 +8129,43 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01, КЗ-02</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>ФО-55</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Заявки по программам и статусам</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
+2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
+3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
+4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
+5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+        </is>
+      </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-02</t>
+          <t>КЗ-17, КЗ-18</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8232,26 +8180,25 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
-2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
-3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
-4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
-5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17, КЗ-18</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -8266,48 +8213,15 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>ФО-57</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>Данные для расчёта ОКУ на дату</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8317,9 +8231,43 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>ФО-58</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Изменения статусов кредитов за период</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
+2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
+3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
+4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
+5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
+        </is>
+      </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -8334,49 +8282,15 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
-2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
-3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
-4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
-5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>ФО-59</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный риск портфеля</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8386,9 +8300,41 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>ФО-91</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
@@ -8403,12 +8349,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8435,12 +8381,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8467,12 +8413,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -8499,47 +8445,15 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr"/>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8550,9 +8464,42 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-15, КЗ-16</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>КЗ-15, КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
@@ -8567,25 +8514,26 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
+2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
+4. Для КЗ-01 (без просрочки) бланк недоступен.
+5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
@@ -8600,26 +8548,26 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
-2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
-4. Для КЗ-01 (без просрочки) бланк недоступен.
-5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
+          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
+2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
+3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
+5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
@@ -8634,21 +8582,21 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
-2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
-3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
-5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
+          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
+2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
+3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
+5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -8668,26 +8616,26 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
-2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
-3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
-5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
+          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
+2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
+3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
+4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
+5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -8702,26 +8650,25 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
-2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
-3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
-4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
-5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
@@ -8731,53 +8678,20 @@
       <c r="J54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8786,32 +8700,32 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F56" s="10" t="inlineStr"/>
-      <c r="G56" s="10" t="inlineStr"/>
-      <c r="H56" s="10" t="inlineStr"/>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="10" t="inlineStr"/>
+      <c r="H55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
@@ -8820,6 +8734,40 @@
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
         </is>
       </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>ФО-36</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
+2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
+3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
+4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
+5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
+        </is>
+      </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
@@ -8837,21 +8785,21 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
-2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
-3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
-4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
-5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
+          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
+2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
+3. Меры в тексте = записям ФО-17 по КЗ-05.
+4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
+5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -8871,21 +8819,21 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
-2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
-3. Меры в тексте = записям ФО-17 по КЗ-05.
-4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
-5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
+          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
+2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
+3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
+4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
+5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -8905,21 +8853,21 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
-2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
-3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
-4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
-5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
+          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
+2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
+3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
+4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
+5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -8939,49 +8887,15 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
-2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
-3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
-4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
-5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>ФО-40</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Справка о задолженности</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8991,6 +8905,39 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -9003,53 +8950,20 @@
       <c r="J62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="10" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -9058,32 +8972,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr"/>
-      <c r="G64" s="10" t="inlineStr"/>
-      <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="10" t="inlineStr"/>
-      <c r="J64" s="10" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -9091,32 +9005,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -9126,32 +9040,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -9161,32 +9075,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -9196,9 +9110,42 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>ФО-46</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Договор поручительства</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+        </is>
+      </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9213,25 +9160,25 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
@@ -9246,20 +9193,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9279,20 +9226,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9312,20 +9259,20 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -9345,25 +9292,26 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
+2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
+3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
+4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
+5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -9378,26 +9326,26 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
-2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
-3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
-4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
-5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
+          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
+2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
+3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
+4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
+5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
@@ -9412,49 +9360,15 @@
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
-2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
-3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
-4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
-5. Договор без отнесённых предметов опись не формирует.</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr"/>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>ФО-61</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Справка об обеспеченности кредита</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9464,6 +9378,39 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>ФО-62</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+        </is>
+      </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9481,25 +9428,25 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
@@ -9514,48 +9461,15 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>ФО-64</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9565,9 +9479,43 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Бланк печатается пустым, данных набора не требует</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>ФО-65</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Карточка организации</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
+2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
+3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
+4. Дата формирования = дате печати.
+5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+        </is>
+      </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Бланк печатается пустым, данных набора не требует</t>
+          <t>Карточка организации из справочника ведомств</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -9582,26 +9530,25 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
-2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
-3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
-4. Дата формирования = дате печати.
-5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации из справочника ведомств</t>
+          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
@@ -9616,20 +9563,20 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -9649,48 +9596,15 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr"/>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="7" t="inlineStr"/>
-      <c r="I82" s="7" t="inlineStr"/>
-      <c r="J82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>79</v>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>ФО-68</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Опись дела</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9700,6 +9614,39 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9717,25 +9664,26 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
+2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
+3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
+4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
+5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
@@ -9750,26 +9698,26 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
-2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
-3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
-4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
-5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
+          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
+2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
+3. Задолженность = расчёту кредита на дату бланка.
+4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
+5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
@@ -9784,26 +9732,26 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
-2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
-3. Задолженность = расчёту кредита на дату бланка.
-4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
-5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
+          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
+2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
+3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
+4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
+5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -9818,26 +9766,25 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
-2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
-3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
-4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
-5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
@@ -9852,25 +9799,26 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
+2. Суммы в таблице = справке об обеспеченности на дату записки.
+3. Не хватает = требуется − имеется по каждому кредиту.
+4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
+5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
@@ -9885,49 +9833,15 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
-2. Суммы в таблице = справке об обеспеченности на дату записки.
-3. Не хватает = требуется − имеется по каждому кредиту.
-4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
-5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr"/>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>ФО-75</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9937,6 +9851,39 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-12</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr"/>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>ФО-76</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+        </is>
+      </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9954,25 +9901,25 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-13</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -9987,25 +9934,26 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
+2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
+3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
+4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
+5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -10020,26 +9968,25 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
-2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
-3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
-4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
-5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -10054,25 +10001,26 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
+          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
+2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
+3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
+4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
+5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-06</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
@@ -10087,21 +10035,20 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
-2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
-3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
-4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
-5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -10121,25 +10068,26 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
+2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
+3. В соглашении указано основание — реквизиты согласия кредитора.
+4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
+5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
@@ -10154,26 +10102,26 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
-2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
-3. В соглашении указано основание — реквизиты согласия кредитора.
-4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
-5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
+          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
+2. Сумма строк графика = сумме, присуждённой судебным актом.
+3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
+4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
+5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
@@ -10188,26 +10136,26 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
-2. Сумма строк графика = сумме, присуждённой судебным актом.
-3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
-4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
-5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
+          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
+2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
+3. Номер, дата и сумма договора = карточке кредита.
+4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
+5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-18</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -10222,26 +10170,25 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
-2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
-3. Номер, дата и сумма договора = карточке кредита.
-4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
-5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>КЗ-18</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
@@ -10256,25 +10203,26 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
+2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
+3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
+4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
+5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -10289,26 +10237,25 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
-2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
-3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
-4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
-5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10323,25 +10270,25 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
@@ -10356,20 +10303,21 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
+2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
+3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
+4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
+5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -10389,26 +10337,25 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
-2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
-3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
-4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
-5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
@@ -10418,53 +10365,20 @@
       <c r="J104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="10" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E105" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
-      <c r="I105" s="7" t="inlineStr"/>
-      <c r="J105" s="7" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="B106" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr">
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10472,9 +10386,42 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr"/>
+      <c r="G105" s="10" t="inlineStr"/>
+      <c r="H105" s="10" t="inlineStr"/>
+      <c r="I105" s="10" t="inlineStr"/>
+      <c r="J105" s="10" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
+4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+        </is>
+      </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr"/>
@@ -10494,15 +10441,15 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
+2. Каждый запрос получает отдельный исходящий номер.
+3. Данные умершего заёмщика = карточке субъекта.
+4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
@@ -10527,20 +10474,20 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
+2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
+3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
+4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
@@ -10560,20 +10507,21 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
-2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
-3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
-4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
+2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
+3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
+4. Срок устранения нарушений не раньше даты регистрации письма.
+5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
         </is>
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr"/>
@@ -10593,44 +10541,10 @@
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
-2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
-3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
-4. Срок устранения нарушений не раньше даты регистрации письма.
-5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F110" s="10" t="inlineStr"/>
-      <c r="G110" s="10" t="inlineStr"/>
-      <c r="H110" s="10" t="inlineStr"/>
-      <c r="I110" s="10" t="inlineStr"/>
-      <c r="J110" s="10" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="10" t="n">
-        <v>107</v>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
         <is>
           <t>1. Форма доступна, только если по договору освобождены все доли предметов (полное снятие) либо выбрана часть предмета при частичном снятии.
 2. Основание выбрано из классификатора; при полном погашении указан акт сверки о полном погашении (ФО-34).
@@ -10640,9 +10554,41 @@
 6. Зарегистрированное письмо видно в ФО-19.</t>
         </is>
       </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-15</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr"/>
+      <c r="G110" s="10" t="inlineStr"/>
+      <c r="H110" s="10" t="inlineStr"/>
+      <c r="I110" s="10" t="inlineStr"/>
+      <c r="J110" s="10" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
+2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
+3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+        </is>
+      </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>КЗ-15</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
@@ -10662,19 +10608,20 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
-2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
-3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
+2. Перечень документов в письме = составу пакета действующей редакции методики.
+3. Установленная дата в письме не раньше даты запроса.
+4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr"/>
@@ -10694,15 +10641,14 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
-2. Перечень документов в письме = составу пакета действующей редакции методики.
-3. Установленная дата в письме не раньше даты запроса.
-4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
+          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
+2. Перечень недостатков в письме = замечаниям комиссии по заявке.
+3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
         </is>
       </c>
       <c r="E113" s="10" t="inlineStr">
@@ -10717,52 +10663,20 @@
       <c r="J113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="n">
+      <c r="A114" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C114" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
-2. Перечень недостатков в письме = замечаниям комиссии по заявке.
-3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
-        </is>
-      </c>
-      <c r="E114" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F114" s="10" t="inlineStr"/>
-      <c r="G114" s="10" t="inlineStr"/>
-      <c r="H114" s="10" t="inlineStr"/>
-      <c r="I114" s="10" t="inlineStr"/>
-      <c r="J114" s="10" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>ОТ-1</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>Выгрузка любого экранного списка в xlsx</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>1. Файл xlsx содержит те же колонки, в том же порядке и с теми же заголовками, что видны на экране; скрытые колонки не выгружаются.
 2. Число строк в файле = число строк списка с учётом всех фильтров и поиска, а не только текущей страницы.
@@ -10773,9 +10687,43 @@
 7. Список с фильтром, не давшим строк, выгружается как файл с заголовками и без строк.</t>
         </is>
       </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется на списках всех модулей</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="7" t="inlineStr"/>
+      <c r="J114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-2</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
+2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
+3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
+4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
+5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
+        </is>
+      </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>Проверяется на списках всех модулей</t>
+          <t>Проверяется на каждой строке перечня</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr"/>
@@ -10784,56 +10732,22 @@
       <c r="I115" s="7" t="inlineStr"/>
       <c r="J115" s="7" t="inlineStr"/>
     </row>
-    <row r="116">
-      <c r="A116" s="7" t="n">
-        <v>112</v>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
-2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
-3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
-4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
-5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется на каждой строке перечня</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr"/>
-      <c r="H116" s="7" t="inlineStr"/>
-      <c r="I116" s="7" t="inlineStr"/>
-      <c r="J116" s="7" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Сдал: ____________________ (разработчик)          Принял: ____________________ (заказчик)          Дата: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J116"/>
+  <autoFilter ref="A4:J115"/>
   <mergeCells count="3">
+    <mergeCell ref="A117:J117"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A118:J118"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сдано,сдано с замечанием,не сдано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11419,7 +11333,7 @@
       </c>
       <c r="M12" s="7" t="inlineStr">
         <is>
-          <t>ФО-12, ФО-58, ФО-82</t>
+          <t>ФО-58, ФО-82</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12995,6 +12909,26 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>ФО-12 «Перевод долга»</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт не нужен: перевод долга виден в ФО-58 «Изменения статусов кредитов за период» (событие «Перевод долга» с соглашением), соглашение — бланк ФО-82; номер не используется</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>решение владельца 30.10.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$127</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$114</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 36 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1532,25 +1532,21 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶444–445, ¶869; Порядок №41 п. 6 пп. 3; Методика №16 пп. 4, 6, 7, 11; ПКМ №554 Типовое положение пп. 78, 80</t>
+          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Отчет по залогу»</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-13.xlsx</t>
+          <t>obrazcy/ФО-14.xlsx</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>Бланки Методики №16 — ФО-75…ФО-78</t>
-        </is>
-      </c>
+      <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n">
@@ -1558,12 +1554,12 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>ФО-14</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -1588,21 +1584,25 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶357, ¶361, ¶475, ¶511, ¶671–682; Порядок №41 п. 10; Положение №12 п. 4.1, прил. 2 п. 2.5; ТЗ 12; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по залогу»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-14.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-15</t>
+          <t>ФО-16</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Акты обследования залога</t>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1640,25 +1640,21 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по актам обследования»</t>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-15.xlsx</t>
+          <t>obrazcy/ФО-16.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
-        </is>
-      </c>
+      <c r="L34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1666,12 +1662,12 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -1681,7 +1677,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1696,77 +1692,77 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по взысканию»</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶582–583; старая система</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>старая система «Отчет ОИП»</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
-        <is>
-          <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
-        </is>
-      </c>
+      <c r="K36" s="10" t="inlineStr"/>
+      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -1779,7 +1775,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1804,12 +1800,12 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>старая система «Отчет ОИП»</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1831,7 +1827,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1856,12 +1852,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶627</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1873,56 +1869,60 @@
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>ФО-18</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Оформление</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶627</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="inlineStr"/>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по оформлению»</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-18.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-18</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Оформление</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по оформлению»</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-18.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -1986,12 +1986,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2072,25 +2072,21 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2098,12 +2094,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2113,7 +2109,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Кураторство</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2128,7 +2124,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2138,115 +2134,115 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>образцы практики</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr"/>
+      <c r="L44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>ФО-26</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Портфель — оперативный срез</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K44" s="7" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C45" s="11" t="inlineStr">
-        <is>
-          <t>вид «Погашенные заёмщики: месяц × куратор»</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>Кураторство</t>
-        </is>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>образцы практики</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>«Result_3.xlsx», «Result_6.xlsx»</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-25.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-26.xlsx</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2254,12 +2250,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-26</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Портфель — оперативный срез</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2284,7 +2280,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2294,7 +2290,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-26.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -2306,12 +2302,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2336,7 +2332,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2346,7 +2342,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2358,12 +2354,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2373,7 +2369,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Портфель</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2388,7 +2384,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2398,7 +2394,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2410,12 +2406,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2425,7 +2421,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2440,7 +2436,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2450,7 +2446,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2462,12 +2458,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2477,7 +2473,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2502,11 +2498,15 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2554,15 +2554,11 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2570,12 +2566,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2585,7 +2581,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2600,7 +2596,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2610,11 +2606,15 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>Плановые показатели выдачи — справочник</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2662,13 +2662,13 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>Плановые показатели выдачи — справочник</t>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2718,15 +2718,11 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-58.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
-        </is>
-      </c>
+      <c r="L54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -2734,12 +2730,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2749,12 +2745,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2764,7 +2760,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2774,11 +2770,19 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr"/>
-      <c r="L55" s="7" t="inlineStr"/>
+          <t>obrazcy/ФО-59.xlsx</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2786,12 +2790,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2801,12 +2805,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2816,7 +2820,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2824,21 +2828,17 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J56" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-59.xlsx</t>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3044,24 +3044,20 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K60" s="13" t="inlineStr">
-        <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3070,51 +3066,59 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Отчёт</t>
+          <t>Бланк</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>язык интерфейса</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr"/>
-      <c r="L61" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3122,12 +3126,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3152,12 +3156,12 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -3170,11 +3174,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+      <c r="L62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик, залогодатель, орган регистрации</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
@@ -3380,141 +3380,137 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
+          <t>старая система «Акт сверки»</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>вид «Акт сверки о полном погашении задолженности»</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 64</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J66" s="7" t="inlineStr">
+      <c r="J67" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="L67" s="10" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>ФО-35</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H67" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
-        </is>
-      </c>
-      <c r="I67" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Акт сверки»</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Департамент правового обеспечения</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>рус</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="inlineStr">
-        <is>
-          <t>вид «Акт сверки о полном погашении задолженности»</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 64</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J68" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr"/>
+      <c r="K68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -3522,12 +3518,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-35</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3552,12 +3548,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -3574,12 +3570,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3594,7 +3590,7 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3604,7 +3600,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -3626,12 +3622,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3646,22 +3642,22 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
@@ -3669,7 +3665,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K71" s="7" t="inlineStr"/>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3698,22 +3698,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3721,11 +3721,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3734,12 +3730,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3749,22 +3745,22 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -3777,7 +3773,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="7" t="inlineStr"/>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-41</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Реестр погашений</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -3816,141 +3816,141 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
+          <t>старая система, распечатка «Реестр погашений»</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>вид «Выписка по кредиту»</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>Платежи</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 14</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J75" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>ФО-42</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>График погашения</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>График</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I75" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Реестр погашений»</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>старая система, выгрузка графика</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="7" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>вид «Выписка по кредиту»</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>Платежи</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>ТЗ 14</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
-        </is>
-      </c>
+      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-42</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>График погашения</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -3973,27 +3973,27 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>График</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>старая система, выгрузка графика</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -4001,11 +4001,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
@@ -4014,12 +4010,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4029,27 +4025,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4057,7 +4053,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="7" t="inlineStr"/>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4346,12 +4346,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4417,22 +4417,22 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4445,11 +4445,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K85" s="7" t="inlineStr"/>
       <c r="L85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4458,12 +4454,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4473,22 +4469,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4501,7 +4497,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr"/>
+      <c r="K86" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4530,17 +4530,17 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4553,11 +4553,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K87" s="7" t="inlineStr"/>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4566,12 +4562,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4586,17 +4582,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4609,7 +4605,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="7" t="inlineStr"/>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4633,22 +4633,22 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4661,11 +4661,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K89" s="7" t="inlineStr"/>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4674,12 +4670,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4694,17 +4690,17 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4717,7 +4713,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr"/>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4741,22 +4741,22 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4769,11 +4769,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K91" s="7" t="inlineStr"/>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4782,12 +4778,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4797,7 +4793,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4812,7 +4808,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4834,12 +4830,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4864,7 +4860,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4886,12 +4882,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4938,12 +4934,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4990,12 +4986,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -5005,7 +5001,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5020,7 +5016,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -5042,12 +5038,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5072,7 +5068,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5094,12 +5090,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5114,7 +5110,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -5124,7 +5120,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5146,12 +5142,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5176,7 +5172,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5198,12 +5194,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5213,12 +5209,12 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -5228,7 +5224,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5250,12 +5246,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5265,12 +5261,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5280,12 +5276,12 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -5302,12 +5298,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5332,12 +5328,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5354,12 +5350,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5384,12 +5380,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5406,12 +5402,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5426,7 +5422,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -5436,12 +5432,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5458,12 +5454,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5473,12 +5469,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5488,12 +5484,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5510,12 +5506,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5525,22 +5521,22 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -5553,8 +5549,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K106" s="7" t="inlineStr"/>
-      <c r="L106" s="7" t="inlineStr"/>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -5562,12 +5566,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5577,12 +5581,12 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -5592,7 +5596,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5610,11 +5614,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="L107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5782,7 +5782,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr"/>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -5790,12 +5794,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5805,12 +5809,12 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -5820,7 +5824,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5838,11 +5842,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5850,12 +5850,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5977,22 +5977,22 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>ТЗ 12</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -6005,11 +6005,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K114" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K114" s="7" t="inlineStr"/>
       <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -6018,12 +6014,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6038,12 +6034,12 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6061,7 +6057,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="7" t="inlineStr"/>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>по виду письма</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -6118,53 +6118,57 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L116" s="7" t="inlineStr"/>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Кредит</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>по виду письма</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
+      <c r="E117" s="10" t="inlineStr">
+        <is>
+          <t>Реструктуризация</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>уполномоченный государственный орган</t>
+        </is>
+      </c>
+      <c r="G117" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
-        </is>
-      </c>
-      <c r="I117" s="7" t="inlineStr">
+      <c r="H117" s="10" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
+        </is>
+      </c>
+      <c r="I117" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J117" s="7" t="inlineStr">
+      <c r="J117" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6174,11 +6178,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>Один бланк с видами ниже; у каждого вида свой текст</t>
-        </is>
-      </c>
+      <c r="L117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>ТЗ 21</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr">
@@ -6629,60 +6629,60 @@
       <c r="L125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="A126" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E126" s="10" t="inlineStr">
-        <is>
-          <t>Заявка и комиссия</t>
-        </is>
-      </c>
-      <c r="F126" s="10" t="inlineStr">
-        <is>
-          <t>заявитель</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H126" s="10" t="inlineStr">
-        <is>
-          <t>ПКМ №554 пп. 66, 74</t>
-        </is>
-      </c>
-      <c r="I126" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K126" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L126" s="10" t="inlineStr"/>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr"/>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>ОТ-1</t>
+          <t>ОТ-2</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>Все модули</t>
+          <t>Отчётность</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -6734,66 +6734,10 @@
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>Отчётность</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
-        </is>
-      </c>
-      <c r="I128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K128" s="7" t="inlineStr"/>
-      <c r="L128" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L128"/>
+  <autoFilter ref="A17:L127"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6848,8 +6792,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6862,7 +6805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7463,49 +7406,15 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>ФО-13</t>
+          <t>ФО-14</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование средств</t>
+          <t>Залоговое обеспечение — предметы</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>1. „Освоено“ по кредиту = сумма освоений кредита в карточке кредита (КЗ-12 — 2 500 000,00, КЗ-13 — 4 500 000,00).
-2. „Не подтверждено“ = „Освоено“ − „Подтверждено“; „в том числе нецелевое“ не больше „Не подтверждено“; подытоги и ИТОГО равны сумме строк.
-3. КЗ-12: нецелевое использование 400 000,00 сом, выявленное выездным мониторингом 15.09.2026, входит в неподтверждённую часть и совпадает с актом о нецелевом использовании.
-4. КЗ-13 (кредит АПК): подтверждено 100,0 %, неподтверждённой части нет, проверку проводит региональное представительство; форма ФО-13 добавляется к КЗ-13 в наборе.
-5. Срок очередной документальной проверки у КЗ-12 (освоение не завершено, неосвоенный остаток 1 500 000,00) заполнен, у КЗ-13 (освоено полностью) пуст.</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12, КЗ-13</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>ФО-14</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Залоговое обеспечение — предметы</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
 2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
@@ -7515,32 +7424,32 @@
 6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-14</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7550,9 +7459,43 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="7" t="inlineStr"/>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
+2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
+3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
+4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
+5. Все даты снятия попадают в период отчёта.</t>
+        </is>
+      </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-15</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
@@ -7567,49 +7510,15 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-17</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
-2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
-3. Заёмщик с непогашенным кредитом без снятия запрета в периоде (например, КЗ-01) в отчёте не показан.
-4. «Залоговая стоимость» предмета = значение в карточке предмета; подытог по договору, заёмщику, району и области = сумма предметов под ним.
-5. Все даты снятия попадают в период отчёта.</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-15</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7619,32 +7528,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7652,9 +7561,43 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="10" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>вид «Претензии по областям за период»</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
+2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
+3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
+4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
+5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+        </is>
+      </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr"/>
@@ -7674,21 +7617,20 @@
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «События фазы по датам и времени»</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
-2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
-3. «Всего погашено» = платежи по кредиту после даты претензии до даты отчёта (по КЗ-02 и КЗ-03 их нет); «Всего остаток» = «Сумма» минус «Всего погашено».
-4. Лист «ИТОГО» в xlsx: число заёмщиков по области = число заёмщиков в подытоге области на листе области.
-5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
         </is>
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7698,53 +7640,20 @@
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr"/>
-      <c r="G26" s="10" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr"/>
-      <c r="I26" s="10" t="inlineStr"/>
-      <c r="J26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7753,32 +7662,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7788,32 +7697,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7823,9 +7732,43 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>ФО-24</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Классификация — движение по группам платёжеспособности</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
+2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
+3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
+4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
+5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+        </is>
+      </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -7840,26 +7783,26 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-25</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
-2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
-3. КЗ-19: переход «2.1 → 3.1» (группа понижена решением от 22.09.2026).
-4. КЗ-15: переход «→ 5», остаток на дату 2 равен 0,00 (погашен 18.09.2026). КЗ-08: переход «→ 4», остаток 0,00 (списан 17.09.2026).
-5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
+          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
+2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
+3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
+4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
+5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>весь набор; особо: КЗ-19</t>
+          <t>весь набор</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -7869,54 +7812,20 @@
       <c r="J30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Кураторство — нагрузка и закрепление</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
-2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
-3. ИТОГО по „Просроченная задолженность“ = ИТОГО ФО-01 на ту же дату (4 560 750,00); ИТОГО по „Портфель“ = ИТОГО ФО-26 (39 482 500,00), кредитов 17.
-4. Кураторы набора: Асанов А. К. — КЗ-01, 02, 03, 06; Осмонов Б. Т. — КЗ-04, 12, 14, 17; Жумабаев Р. С. — КЗ-05, 07, 09, 10; Токтогулова Г. А. — КЗ-13, 19, 20; Бекова Н. С. — КЗ-11. КЗ-02: куратор Асанов А. К., просроченная задолженность 180 850,00, 20 дней.
-5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>ФО-25</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7925,32 +7834,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr"/>
-      <c r="G32" s="10" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr"/>
-      <c r="I32" s="10" t="inlineStr"/>
-      <c r="J32" s="10" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+      <c r="H31" s="10" t="inlineStr"/>
+      <c r="I31" s="10" t="inlineStr"/>
+      <c r="J31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7959,6 +7868,40 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>ФО-27</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Средняя просрочка по департаментам</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
+2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
+3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
+4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
+5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+        </is>
+      </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -7976,21 +7919,20 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
-2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
-3. На наборе: РП «Ош» — 212,0 (КЗ-04); ОДП — (409 + 260 + 190 + 95) / 4 = 238,5; ДАК — (75 + 20) / 2 = 47,5; ИТОГО — 1 261 / 7 = 180,1.
-4. „Просроченная задолженность“ в ИТОГО = ИТОГО ФО-01 на ту же дату (4 560 750,00); кредиты без просрочки (КЗ-01, КЗ-06 и др.) в отчёт не входят.
-5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -8010,25 +7952,26 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
+2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
+3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
+4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
+5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -8043,26 +7986,26 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
-2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
-3. «Дней на учёте» = дата среза минус дата перехода права (20.03.2026): на 01.10.2026 — 195.
-4. Позиции предложений: «Принято» + «Отказано» + «Отозвано» + «Не состоялось» = число позиций предложения.
-5. Подытог по состоянию и источнику = сумма строк ниже.</t>
+          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
+2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
+3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
+4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
+5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-11</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -8077,49 +8020,15 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
-2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
-3. Курсовая разница = остаток в сомах на конец − (остаток в сомах на начало + движение за период).
-4. КЗ-11 за сентябрь 2026: 60 000,00 USD на начало, погашено 5 000,00 USD, на конец 55 000,00 USD; курсовая разница 17 500,00 сом.
-5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-11</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>ФО-54</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>План-факт погашений</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8129,9 +8038,43 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01, КЗ-02</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>ФО-55</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Заявки по программам и статусам</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
+2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
+3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
+4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
+5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+        </is>
+      </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01, КЗ-02</t>
+          <t>КЗ-17, КЗ-18</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -8146,26 +8089,25 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
-2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
-3. КЗ-17: заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026), решение комиссии — протокол № 7 от 20.08.2026; статус „Оформлена“, запрошено и одобрено 1 500 000,00, дней в рассмотрении 69.
-4. КЗ-18: заявка одобрена, договор № 26-1/012 расторгнут 10.09.2026; одобрено 900 000,00 сом.
-5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17, КЗ-18</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8180,48 +8122,15 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>ФО-57</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Данные для расчёта ОКУ на дату</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8231,9 +8140,43 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>ФО-58</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Изменения статусов кредитов за период</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
+2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
+3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
+4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
+5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -8248,49 +8191,15 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
-2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
-3. КЗ-06 показан с изменением условий по реструктуризации, КЗ-07 — с переводом долга, КЗ-17 — с регистрацией кредитного договора.
-4. У каждой строки заполнено основание; дата изменения внутри периода. Основание списания — заключение Постоянно-действующей комиссии (Порядок №41 п. 63), как в ФО-11.
-5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>ФО-59</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Кредитный риск портфеля</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8300,9 +8209,41 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>ФО-91</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>весь набор</t>
+          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -8317,12 +8258,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -8349,12 +8290,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8381,12 +8322,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8413,47 +8354,15 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>ФО-95</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Погашенные кредиты за период</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8464,9 +8373,42 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-15, КЗ-16</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>КЗ-15, КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -8481,25 +8423,26 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
+2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
+4. Для КЗ-01 (без просрочки) бланк недоступен.
+5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-02</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
@@ -8514,26 +8457,26 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
-2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-3. Просроченная основная сумма, проценты и штрафы = просроченной задолженности карточки кредита КЗ-02 № 22-1/045 на дату бланка; на 01.10.2026 просрочка 20 дней: 150 000,00, 28 500,00 и 2 350,00.
-4. Для КЗ-01 (без просрочки) бланк недоступен.
-5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
+          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
+2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
+3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
+5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>КЗ-02</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
@@ -8548,21 +8491,21 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
-2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
-3. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 № 23-4/008 на дату бланка; на 01.10.2026 просрочка 75 дней: 90 000,00, 41 000,00 и 18 400,00.
-5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
+          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
+2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
+3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
+4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
+5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -8582,26 +8525,26 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-33</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
-2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
-3. Договор поручительства в тексте = договору из закладки «Обеспечение» карточки кредита.
-4. Суммы задолженности = просроченной задолженности карточки кредита КЗ-03 на дату бланка.
-5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
+          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
+2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
+3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
+4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
+5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
@@ -8616,26 +8559,25 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-34</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
-2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
-3. Суммы задолженности = расчёту кредита КЗ-04 № 21-5/203 на дату бланка; основная сумма в извещении — весь остаток 3 600 000,00, в том числе просроченная 800 000,00.
-4. После регистрации извещения в карточке кредита появляется фаза взыскания «Извещение» с суммой, датой и реквизитами договоров.
-5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -8645,53 +8587,20 @@
       <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="8" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr"/>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8700,32 +8609,32 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E55" s="10" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="inlineStr"/>
-      <c r="I55" s="10" t="inlineStr"/>
-      <c r="J55" s="10" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="10" t="inlineStr"/>
+      <c r="H54" s="10" t="inlineStr"/>
+      <c r="I54" s="10" t="inlineStr"/>
+      <c r="J54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
@@ -8734,6 +8643,40 @@
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
         </is>
       </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>ФО-36</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
+2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
+3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
+4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
+5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
+        </is>
+      </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
@@ -8751,21 +8694,21 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
-2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
-3. Реквизиты претензий в тексте = записям ФО-17, вид «Претензии», по КЗ-05.
-4. Если в деле нет акта сверки, претензии или расчёта, система предупреждает до регистрации.
-5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
+          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
+2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
+3. Меры в тексте = записям ФО-17 по КЗ-05.
+4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
+5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -8785,21 +8728,21 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
-2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
-3. Меры в тексте = записям ФО-17 по КЗ-05.
-4. Адресат — должность «Председатель Правления»; при смене лица на должности бланк не меняется.
-5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
+          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
+2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
+3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
+4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
+5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -8819,21 +8762,21 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
-2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
-3. Перечень приложений совпадает с документами кредитно-залогового дела КЗ-05; отсутствующий документ система показывает до регистрации.
-4. После регистрации иска у КЗ-05 появляется фаза «Иск» с датой подачи 16.03.2026 и суммой; группа платёжеспособности меняется на «2.1. Работа с судебными органами».
-5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
+          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
+2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
+3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
+4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
+5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -8853,49 +8796,15 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-40</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Справка о задолженности</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
-2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
-3. Адресат = подразделению, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.
-4. Каждое замечание имеет причину из перечня и рекомендацию; пустая строка не сохраняется.
-5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>ФО-40</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Справка о задолженности</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8905,6 +8814,39 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -8917,53 +8859,20 @@
       <c r="J61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -8972,32 +8881,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr"/>
-      <c r="H63" s="10" t="inlineStr"/>
-      <c r="I63" s="10" t="inlineStr"/>
-      <c r="J63" s="10" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr"/>
+      <c r="G62" s="10" t="inlineStr"/>
+      <c r="H62" s="10" t="inlineStr"/>
+      <c r="I62" s="10" t="inlineStr"/>
+      <c r="J62" s="10" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -9005,32 +8914,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -9040,32 +8949,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -9075,32 +8984,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -9110,9 +9019,42 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>ФО-46</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Договор поручительства</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+        </is>
+      </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -9127,25 +9069,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-16</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9160,20 +9102,20 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -9193,20 +9135,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9226,20 +9168,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9259,25 +9201,26 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
+2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
+3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
+4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
+5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
@@ -9292,26 +9235,26 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
-2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
-3. Раздел «Реквизиты» для юридического лица показывает руководителя, для физического лица и ИП — документ.
-4. Раздел 5 КЗ-01: два договора залога (№ 21-3/117-З1, № 22-2/031-З1) и один договор поручительства (№ 21-3/117-П1); разделы 6 и 7 — «нет».
-5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
+          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
+2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
+3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
+4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
+5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
@@ -9326,49 +9269,15 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
-2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
-3. Итого по валюте = сумме залоговой стоимости строк этой валюты.
-4. КЗ-14: договор № 24-6/019-З1 — две строки (здание склада 3 010 000,00; трактор — утрачен, 0,00), итого по KGS 3 010 000,00 на 01.10.2026.
-5. Договор без отнесённых предметов опись не формирует.</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-61</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Справка об обеспеченности кредита</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9378,6 +9287,39 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>ФО-62</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+        </is>
+      </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9395,25 +9337,25 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -9428,48 +9370,15 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr"/>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>ФО-64</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9479,9 +9388,43 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Бланк печатается пустым, данных набора не требует</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>ФО-65</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Карточка организации</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
+2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
+3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
+4. Дата формирования = дате печати.
+5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+        </is>
+      </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Бланк печатается пустым, данных набора не требует</t>
+          <t>Карточка организации из справочника ведомств</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
@@ -9496,26 +9439,25 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
-2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
-3. Реквизиты счёта (банк, БИК, номер, валюта) = реквизитам организации на дату формирования.
-4. Дата формирования = дате печати.
-5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации из справочника ведомств</t>
+          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -9530,20 +9472,20 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -9563,48 +9505,15 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>ФО-68</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Опись дела</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9614,6 +9523,39 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9631,25 +9573,26 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
+2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
+3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
+4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
+5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>КЗ-20</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
@@ -9664,26 +9607,26 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
-2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
-3. Даты и суммы исполнения = записям реестра платежей КЗ-05; последняя дата — дата последнего платежа.
-4. После регистрации фаза получает статус «Полное погашение», процедура — «Передан в отраслевые отделы»; подтверждение статуса отраслевым департаментом — в течение 3 рабочих дней (записка от 11.03.2027 — до 16.03.2027).
-5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
+          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
+2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
+3. Задолженность = расчёту кредита на дату бланка.
+4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
+5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
@@ -9698,26 +9641,26 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
-2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
-3. Задолженность = расчёту кредита на дату бланка.
-4. Основание выбирается из перечня п. 40–41; без основания бланк не сохраняется.
-5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
+          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
+2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
+3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
+4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
+5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
@@ -9732,26 +9675,25 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
-2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
-3. Перечень писем (родственникам, нотариусу, регистрационной службе) = записям ФО-90 по КЗ-09; отсутствующее письмо система показывает до регистрации.
-4. Задолженность = расчёту кредита КЗ-09 № 24-2/077 на дату бланка: на 01.10.2026 просрочка 95 дней — основная сумма 40 000,00, проценты 10 500,00, штрафы 1 200,00.
-5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -9766,25 +9708,26 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
+2. Суммы в таблице = справке об обеспеченности на дату записки.
+3. Не хватает = требуется − имеется по каждому кредиту.
+4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
+5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
@@ -9799,49 +9742,15 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
-2. Суммы в таблице = справке об обеспеченности на дату записки.
-3. Не хватает = требуется − имеется по каждому кредиту.
-4. КЗ-14: кредит № 24-6/019 — требуется 4 425 000,00, имеется 3 910 000,00, не хватает 515 000,00, индекс 88,4 %.
-5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>ФО-75</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9851,6 +9760,39 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-12</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>ФО-76</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+        </is>
+      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9868,25 +9810,25 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-13</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -9901,25 +9843,26 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
+2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
+3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
+4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
+5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -9934,26 +9877,25 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
-2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
-3. Реквизиты заёмщика (адрес, руководитель, ИНН, контакты) = карточке субъекта; фраза «Мы, нижеподписавшиеся» — один раз.
-4. Сумма нецелевого использования в описательной части = 400 000,00 = сумме по подтверждающему документу, указанному в тексте (договор № 12 от 18.03.2024), и выводу ФО-76.
-5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -9968,25 +9910,26 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
+          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
+2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
+3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
+4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
+5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>КЗ-01</t>
+          <t>КЗ-06</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
@@ -10001,21 +9944,20 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
-2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
-3. Ставка «После» (5,00 %) не ниже половины первоначальной ставки 10,00 % (ПКМ №14 п. 92).
-4. Основной долг «После» = число платежей × платёж по основному долгу: 15 × 120 000,00 = 1 800 000,00; «До»: 18 × 100 000,00.
-5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -10035,25 +9977,26 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
+2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
+3. В соглашении указано основание — реквизиты согласия кредитора.
+4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
+5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-07</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
@@ -10068,26 +10011,26 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
-2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
-3. В соглашении указано основание — реквизиты согласия кредитора.
-4. После регистрации перевода в кредите заёмщик заменён, бланк находится в карточке кредита.
-5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
+          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
+2. Сумма строк графика = сумме, присуждённой судебным актом.
+3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
+4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
+5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>КЗ-07</t>
+          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
@@ -10102,26 +10045,26 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
-2. Сумма строк графика = сумме, присуждённой судебным актом.
-3. Судебный акт и кредитный договор в тексте = данным фазы «Иск» и карточки кредита КЗ-05.
-4. Поступления по соглашению отражаются в реестре платежей КЗ-05 и учитываются в ФО-70 при полном погашении.
-5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
+          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
+2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
+3. Номер, дата и сумма договора = карточке кредита.
+4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
+5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>КЗ-05</t>
+          <t>КЗ-18</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
@@ -10136,26 +10079,25 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
-2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
-3. Номер, дата и сумма договора = карточке кредита.
-4. После подписания в карточке кредита записана операция «Расторжение» с реквизитами соглашения, а запрос на снятие запрета на отчуждение доступен.
-5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>КЗ-18</t>
+          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -10170,25 +10112,26 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
+2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
+3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
+4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
+5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>КЗ-04</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
@@ -10203,26 +10146,25 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
-2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
-3. Для КЗ-03 создаётся по экземпляру на каждый банк, где у заёмщика есть счёт; в каждом экземпляре указана полная сумма «в пределах остатка на счёте».
-4. Сумма списания = просроченной задолженности кредита на дату бланка: на 01.10.2026 просрочка 75 дней — 90 000,00, 41 000,00 и 18 400,00, всего 149 400,00.
-5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>КЗ-03</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -10237,25 +10179,25 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>КЗ-12</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10270,20 +10212,21 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-89</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
+2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
+3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
+4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
+5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
@@ -10303,26 +10246,25 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-90</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Письмо по кредиту</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
-2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
-3. Индекс после = расчёт по новому составу; замена ликвидного залога менее ликвидным и замена при просрочке не проходят.
-4. КЗ-14: соглашение № 1 от 09.09.2026 к договору № 24-6/019-З1 уточняет общую площадь предмета П-071 с 540,0 до 548,6 кв.м; индекс обеспеченности кредита не меняется (104,2 %).
-5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -10332,53 +10274,20 @@
       <c r="J103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr"/>
-      <c r="J104" s="7" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
+      <c r="C104" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D104" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10386,9 +10295,42 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr"/>
+      <c r="G104" s="10" t="inlineStr"/>
+      <c r="H104" s="10" t="inlineStr"/>
+      <c r="I104" s="10" t="inlineStr"/>
+      <c r="J104" s="10" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
+4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+        </is>
+      </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>КЗ-06</t>
+          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
@@ -10408,15 +10350,15 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
+          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
+2. Каждый запрос получает отдельный исходящий номер.
+3. Данные умершего заёмщика = карточке субъекта.
+4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
         </is>
       </c>
       <c r="E106" s="10" t="inlineStr">
@@ -10441,20 +10383,20 @@
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
+2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
+3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
+4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
         </is>
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>КЗ-09</t>
+          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr"/>
@@ -10474,20 +10416,21 @@
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-10 письмо доступно при наличии зарегистрированной фазы «Иск»; для КЗ-01 недоступно.
-2. Размер обязательств по статьям = задолженности по кредиту на дату письма (15.06.2026, просрочка 152 дня); «Итого» = сумма строк.
-3. В тексте есть предупреждение об обращении в суд для установления процедуры банкротства.
-4. Дата письма и срок исполнения (15.07.2026) попадают в карточку взыскания заёмщика.</t>
+          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
+2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
+3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
+4. Срок устранения нарушений не раньше даты регистрации письма.
+5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
         </is>
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>КЗ-10</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr"/>
@@ -10507,44 +10450,10 @@
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 вид доступен по кредиту с выявленным нарушением: предписание от 28.09.2026 ссылается на акт ФО-78 от 25.09.2026 и называет сумму 400 000,00.
-2. Для КЗ-12 есть запрос документов от 28.07.2026 № 12-04/0861 со сроком представления 11.08.2026 — раньше отчёта ФО-75 от 15.08.2026.
-3. Номер и дата договора (№ 24-2/088 от 12.03.2024), сумма кредита 4 000 000,00 в тексте = карточке кредита.
-4. Срок устранения нарушений не раньше даты регистрации письма.
-5. Зарегистрированное предписание получает исходящий номер (12-04/1173), виден в журнале исходящих ФО-66 и в ФО-19; адресат — заёмщик, копия — отраслевой орган.</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F109" s="10" t="inlineStr"/>
-      <c r="G109" s="10" t="inlineStr"/>
-      <c r="H109" s="10" t="inlineStr"/>
-      <c r="I109" s="10" t="inlineStr"/>
-      <c r="J109" s="10" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="n">
-        <v>106</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr">
-        <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
         <is>
           <t>1. Форма доступна, только если по договору освобождены все доли предметов (полное снятие) либо выбрана часть предмета при частичном снятии.
 2. Основание выбрано из классификатора; при полном погашении указан акт сверки о полном погашении (ФО-34).
@@ -10554,9 +10463,41 @@
 6. Зарегистрированное письмо видно в ФО-19.</t>
         </is>
       </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-15</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr"/>
+      <c r="G109" s="10" t="inlineStr"/>
+      <c r="H109" s="10" t="inlineStr"/>
+      <c r="I109" s="10" t="inlineStr"/>
+      <c r="J109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
+2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
+3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+        </is>
+      </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>КЗ-15</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr"/>
@@ -10576,19 +10517,20 @@
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>1. В бланке указано решение уполномоченных лиц с номером и датой; без него форма не формируется.
-2. Предмет, договор о залоге и запрет в тексте = карточке предмета; текст сохраняет запрет в силе.
-3. КЗ-14: согласие по зданию склада на передачу в аренду по заявлению от 10.09.2026, решение № 14 от 15.09.2026.</t>
+          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
+2. Перечень документов в письме = составу пакета действующей редакции методики.
+3. Установленная дата в письме не раньше даты запроса.
+4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
         </is>
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr"/>
@@ -10608,15 +10550,14 @@
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 письмо (заявитель на дату письма) создаёт запрос в анализе: дата запроса = 15.07.2026, установленная дата = 14.08.2026 = дате в тексте.
-2. Перечень документов в письме = составу пакета действующей редакции методики.
-3. Установленная дата в письме не раньше даты запроса.
-4. Запрос без даты получения остаётся незакрытым; письмо видно в журнале исходящих.</t>
+          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
+2. Перечень недостатков в письме = замечаниям комиссии по заявке.
+3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
         </is>
       </c>
       <c r="E112" s="10" t="inlineStr">
@@ -10631,52 +10572,20 @@
       <c r="J112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="n">
+      <c r="A113" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="inlineStr">
-        <is>
-          <t>вид «Возврат проекта на доработку — заявителю»</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-17 письмо доступно по заявке № 14 с замечаниями; срок исправления = дата письма (26.06.2026) + один месяц = 26.07.2026.
-2. Перечень недостатков в письме = замечаниям комиссии по заявке.
-3. Письмо фиксируется в журнале заявки датой и номером; по истечении срока без устранения заявка предлагается к отклонению.</t>
-        </is>
-      </c>
-      <c r="E113" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr"/>
-      <c r="G113" s="10" t="inlineStr"/>
-      <c r="H113" s="10" t="inlineStr"/>
-      <c r="I113" s="10" t="inlineStr"/>
-      <c r="J113" s="10" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>ОТ-1</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>Выгрузка любого экранного списка в xlsx</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D113" s="7" t="inlineStr">
         <is>
           <t>1. Файл xlsx содержит те же колонки, в том же порядке и с теми же заголовками, что видны на экране; скрытые колонки не выгружаются.
 2. Число строк в файле = число строк списка с учётом всех фильтров и поиска, а не только текущей страницы.
@@ -10687,9 +10596,43 @@
 7. Список с фильтром, не давшим строк, выгружается как файл с заголовками и без строк.</t>
         </is>
       </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется на списках всех модулей</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="7" t="inlineStr"/>
+      <c r="J113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>ОТ-2</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
+2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
+3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
+4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
+5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
+        </is>
+      </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Проверяется на списках всех модулей</t>
+          <t>Проверяется на каждой строке перечня</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr"/>
@@ -10698,56 +10641,22 @@
       <c r="I114" s="7" t="inlineStr"/>
       <c r="J114" s="7" t="inlineStr"/>
     </row>
-    <row r="115">
-      <c r="A115" s="7" t="n">
-        <v>111</v>
-      </c>
-      <c r="B115" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-2</t>
-        </is>
-      </c>
-      <c r="C115" s="7" t="inlineStr">
-        <is>
-          <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>1. У каждого отчёта перечня есть выгрузка в xlsx и pdf; у каждого бланка — в docx и pdf.
-2. Состав строк, колонки, подытоги и ИТОГО отчёта в xlsx и pdf совпадают с экраном для тех же параметров; при смене параметров файл меняется.
-3. Текст и подставленные значения бланка в docx и pdf совпадают с экраном.
-4. Кириллица и буквы кыргызского алфавита (ү, ө, ң) читаются в xlsx, docx и pdf без замен символов.
-5. Числа в xlsx выгружаются числами, даты — датами; в pdf числа выглядят как на экране: суммы с двумя знаками, проценты и средние — с одним.</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется на каждой строке перечня</t>
-        </is>
-      </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="7" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Сдал: ____________________ (разработчик)          Принял: ____________________ (заказчик)          Дата: ____________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J115"/>
+  <autoFilter ref="A4:J114"/>
   <mergeCells count="3">
-    <mergeCell ref="A117:J117"/>
+    <mergeCell ref="A116:J116"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"сдано,сдано с замечанием,не сдано"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11648,7 +11557,7 @@
       </c>
       <c r="M17" s="7" t="inlineStr">
         <is>
-          <t>ФО-08, ФО-09, ФО-13, ФО-75, ФО-76, ФО-78, ФО-87, ФО-90|По целевому</t>
+          <t>ФО-08, ФО-09, ФО-75, ФО-76, ФО-78, ФО-87, ФО-90|По целевому</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11620,7 @@
       </c>
       <c r="M18" s="7" t="inlineStr">
         <is>
-          <t>ФО-06, ФО-10, ФО-13, ФО-77</t>
+          <t>ФО-06, ФО-10, ФО-77</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12929,6 +12838,26 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ФО-13 «Целевое использование средств»</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт не нужен: проверки целевого использования оформляются бланками ФО-75–ФО-78 и письмом ФО-90 «По целевому использованию» (Методика №16); номер не используется</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>решение владельца 30.10.2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/perechen-otchetov/Перечень.xlsx
+++ b/docs/perechen-otchetov/Перечень.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вне перечня" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Перечень'!$A$17:$L$128</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Перечень'!$17:$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Приёмка'!$A$4:$J$115</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Приёмка'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Контрольный набор'!$4:$4</definedName>
   </definedNames>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 8. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
+          <t>Отчётов: 35 (из них заготовок внешних форм: 4), видов отчётов: 9. Бланков: 54, видов бланков: 11. Общих требований: 2. Строк с ⚠: 46 (кыргызский текст: 41).</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Предметы залога по состоянию на дату</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -1546,61 +1546,65 @@
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>Прежнее название — «Залоговое обеспечение — предметы»; в старой системе — «Отчет по залогу» («Информация по залогу»). Обеспеченность кредитов — вид отчёта</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>ФО-15</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>Акты обследования залога</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>ФО-14</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>вид «Обеспеченность кредитов залогом по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Залог</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по актам обследования»</t>
-        </is>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-15.xlsx</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr"/>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Положение №12 прил. 1 пп. 2.3–2.4, прил. 2 п. 2.5; ТЗ 12</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-14.xlsx</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Строка — кредит: сумма под риском, залоговая стоимость, порог, индекс обеспеченности, недостаёт залога. Справка по одному договору — бланк ФО-61</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1614,12 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>ФО-16</t>
+          <t>ФО-15</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Снятие с ареста (запрета на отчуждение)</t>
+          <t>Акты обследования залога</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -1640,21 +1644,25 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+          <t>оф. ТЗ ¶68, ¶356, ¶513–519, ¶859; Положение №12 п. 5.3; старая система</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+          <t>старая система «Отчет по актам обследования»</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-16.xlsx</t>
+          <t>obrazcy/ФО-15.xlsx</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик. Бланк акта — ФО-43</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -1662,107 +1670,107 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>ФО-16</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Снятие с ареста (запрета на отчуждение)</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶514, ¶520–524, ¶863–864; Положение №12 прил. 3; старая система</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>старая система «Отчет по снятию с ареста»; «снятие залога по погашенным кредитам с 10 сент 2025.xls»</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-16.xlsx</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶93, ¶96, ¶557–593, ¶621–622; Порядок №41 пп. 20, 21, 25, 27–29, 37, 53, 58, 59, 61; ТЗ 13; старая система</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>старая система «Отчет по взысканию»</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>obrazcy/ФО-17.xlsx</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr"/>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>Отбор по виду документа взыскания, включая документы, которые система только учитывает (оф. ТЗ ¶557–585)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶582–583; старая система</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>старая система «Отчет ОИП»</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-17.xlsx</t>
-        </is>
-      </c>
-      <c r="K36" s="10" t="inlineStr"/>
-      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -1775,7 +1783,7 @@
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>вид «Претензии по областям за период»</t>
+          <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1800,12 +1808,12 @@
       </c>
       <c r="H37" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶553–556; образец практики</t>
+          <t>оф. ТЗ ¶582–583; старая система</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>«Претензии по 7 областям.xls»</t>
+          <t>старая система «Отчет ОИП»</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
@@ -1827,7 +1835,7 @@
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>вид «События фазы по датам и времени»</t>
+          <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1852,12 +1860,12 @@
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶627</t>
+          <t>оф. ТЗ ¶553–556; образец практики</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>«Претензии по 7 областям.xls»</t>
         </is>
       </c>
       <c r="J38" s="12" t="inlineStr">
@@ -1869,60 +1877,56 @@
       <c r="L38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-18</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Оформление — комплектность кредитно-залогового дела</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Оформление</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>старая система «Отчет по оформлению»</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-18.xlsx</t>
-        </is>
-      </c>
-      <c r="K39" s="7" t="inlineStr"/>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>Данные для формы обеспечивает разработчик</t>
-        </is>
-      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶627</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-17.xlsx</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n">
@@ -1930,12 +1934,12 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>ФО-19</t>
+          <t>ФО-18</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Документооборот — входящие и исходящие</t>
+          <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
@@ -1945,7 +1949,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Оформление</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
+          <t>оф. ТЗ ¶346–347; Порядок №41 п. 13, п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>старая система «Отчет по документообороту»</t>
+          <t>старая система «Отчет по оформлению»</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-19.xlsx</t>
+          <t>obrazcy/ФО-18.xlsx</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr"/>
@@ -1986,12 +1990,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>ФО-20</t>
+          <t>ФО-19</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Задания и их исполнение</t>
+          <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
@@ -2001,7 +2005,7 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Задания</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2016,17 +2020,17 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
+          <t>оф. ТЗ ¶696–706, ¶926, ¶930–935, ¶953–959; Порядок №41 пп. 26, 28; ТЗ 23; старая система</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>старая система «Контроль исполнения» (частично)</t>
+          <t>старая система «Отчет по документообороту»</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-20.xlsx</t>
+          <t>obrazcy/ФО-19.xlsx</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr"/>
@@ -2042,12 +2046,12 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>ФО-24</t>
+          <t>ФО-20</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Классификация — движение по группам платёжеспособности</t>
+          <t>Задания и их исполнение</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -2057,7 +2061,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Классификация</t>
+          <t>Задания</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2072,21 +2076,25 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
+          <t>оф. ТЗ ¶707–716, ¶1022–1033</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Контроль исполнения» (частично)</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-24.xlsx</t>
+          <t>obrazcy/ФО-20.xlsx</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>Данные для формы обеспечивает разработчик</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -2094,12 +2102,12 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>ФО-25</t>
+          <t>ФО-24</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Кураторство — нагрузка и закрепление</t>
+          <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -2109,7 +2117,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Кураторство</t>
+          <t>Классификация</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2124,7 +2132,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+          <t>оф. ТЗ ¶743–752; Инструкция №14 пп. 5–6; ТЗ 17</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2134,115 +2142,115 @@
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-25.xlsx</t>
+          <t>obrazcy/ФО-24.xlsx</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство — нагрузка и закрепление</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Кураторство</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>внутренний</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>язык интерфейса</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶277–282; ТЗ 16</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-25.xlsx</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>ФО-25</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D45" s="10" t="inlineStr">
         <is>
           <t>Отчёт</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Кураторство</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>внутренний</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
+      <c r="G45" s="10" t="inlineStr">
         <is>
           <t>язык интерфейса</t>
         </is>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>образцы практики</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>«Result_3.xlsx», «Result_6.xlsx»</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>obrazcy/ФО-25.xlsx</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr"/>
-      <c r="L44" s="10" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>ФО-26</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>Портфель — оперативный срез</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Портфель</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>внутренний</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>язык интерфейса</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
-        </is>
-      </c>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-26.xlsx</t>
-        </is>
-      </c>
-      <c r="K45" s="7" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr"/>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -2250,12 +2258,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-27</t>
+          <t>ФО-26</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Средняя просрочка по департаментам</t>
+          <t>Портфель — оперативный срез</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -2280,7 +2288,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶646; ТЗ 24</t>
+          <t>оф. ТЗ ¶117–118, ¶644–670; Порядок №41 п. 6 пп. 7; Политика №28 п. 4.1.1</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -2290,7 +2298,7 @@
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-27.xlsx</t>
+          <t>obrazcy/ФО-26.xlsx</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr"/>
@@ -2302,12 +2310,12 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>ФО-28</t>
+          <t>ФО-27</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Доля проблемных кредитов</t>
+          <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -2332,7 +2340,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
+          <t>оф. ТЗ ¶646; ТЗ 24</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -2342,7 +2350,7 @@
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-28.xlsx</t>
+          <t>obrazcy/ФО-27.xlsx</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr"/>
@@ -2354,12 +2362,12 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>ФО-47</t>
+          <t>ФО-28</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Реестр имущества на дату</t>
+          <t>Доля проблемных кредитов</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2369,7 +2377,7 @@
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Портфель</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
+          <t>Порядок №41 п. 6 пп. 7; ТЗ 24</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-47.xlsx</t>
+          <t>obrazcy/ФО-28.xlsx</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr"/>
@@ -2406,12 +2414,12 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>ФО-53</t>
+          <t>ФО-47</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Расчёт в валюте и курсовая разница за период</t>
+          <t>Реестр имущества на дату</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -2421,7 +2429,7 @@
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>Расчёты</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -2436,7 +2444,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶740</t>
+          <t>оф. ТЗ ¶531–537; ТЗ 22</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -2446,7 +2454,7 @@
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-53.xlsx</t>
+          <t>obrazcy/ФО-47.xlsx</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
@@ -2458,12 +2466,12 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>ФО-54</t>
+          <t>ФО-53</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>План-факт погашений</t>
+          <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -2473,7 +2481,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Расчёты</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
+          <t>оф. ТЗ ¶740</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -2498,15 +2506,11 @@
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-54.xlsx</t>
+          <t>obrazcy/ФО-53.xlsx</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr">
-        <is>
-          <t>Факт погашений против графика и плановых показателей</t>
-        </is>
-      </c>
+      <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -2514,12 +2518,12 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ФО-55</t>
+          <t>ФО-54</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Заявки по программам и статусам</t>
+          <t>План-факт погашений</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -2529,7 +2533,7 @@
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2544,7 +2548,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>оф. ТЗ ¶75, ¶489, ¶660–663</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -2554,11 +2558,15 @@
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-55.xlsx</t>
+          <t>obrazcy/ФО-54.xlsx</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
-      <c r="L51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>Факт погашений против графика и плановых показателей</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n">
@@ -2566,12 +2574,12 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>ФО-56</t>
+          <t>ФО-55</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>План и факт выдачи</t>
+          <t>Заявки по программам и статусам</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -2581,7 +2589,7 @@
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Кредитная программа</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2596,7 +2604,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -2606,15 +2614,11 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-56.xlsx</t>
+          <t>obrazcy/ФО-55.xlsx</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>Плановые показатели выдачи — справочник</t>
-        </is>
-      </c>
+      <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -2622,12 +2626,12 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>ФО-57</t>
+          <t>ФО-56</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Данные для расчёта ОКУ на дату</t>
+          <t>План и факт выдачи</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -2637,12 +2641,12 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредитная программа</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>служба рисков</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -2652,7 +2656,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
+          <t>оф. ТЗ ¶648–650; ТЗ 02; ТЗ 06</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -2662,13 +2666,13 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-57.xlsx</t>
+          <t>obrazcy/ФО-56.xlsx</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+          <t>Плановые показатели выдачи — справочник</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2682,12 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>ФО-58</t>
+          <t>ФО-57</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Изменения статусов кредитов за период</t>
+          <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2693,12 +2697,12 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба рисков</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
@@ -2708,7 +2712,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶59</t>
+          <t>Методика №15 гл. 3–5; Политика №28 п. 4.1.1 пп. 11; Учётная политика №27</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -2718,11 +2722,15 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-58.xlsx</t>
+          <t>obrazcy/ФО-57.xlsx</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>По кредиту: остаток ОД, процентов и штрафа в сомах, дни просрочки, группа платёжеспособности, оценка залога, признак реструктуризации. Сам расчёт ОКУ — у службы рисков, вне системы</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -2730,12 +2738,12 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>ФО-59</t>
+          <t>ФО-58</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Кредитный риск портфеля</t>
+          <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2745,12 +2753,12 @@
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Риски</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Правление</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
+          <t>оф. ТЗ ¶59</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -2770,19 +2778,11 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>obrazcy/ФО-59.xlsx</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>Состав показателей — от службы рисков</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr">
-        <is>
-          <t>Раз в квартал</t>
-        </is>
-      </c>
+          <t>obrazcy/ФО-58.xlsx</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>ФО-91</t>
+          <t>ФО-59</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
+          <t>Кредитный риск портфеля</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Внешняя отчётность</t>
+          <t>Риски</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов</t>
+          <t>Правление</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 20 п. 13.7</t>
+          <t>Политика №28 п. 5.4.4, п. 4.1.1 пп. 10</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -2828,17 +2828,21 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="J56" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-59.xlsx</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Образец формы. Без образца к заморозке строка снимается</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr"/>
+          <t>Состав показателей — от службы рисков</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>Раз в квартал</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -2846,12 +2850,12 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2866,7 +2870,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Кабинет Министров</t>
+          <t>Министерство финансов</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -2902,12 +2906,12 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2922,7 +2926,7 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Нацстатком</t>
+          <t>Кабинет Министров</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
@@ -2958,12 +2962,12 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2978,7 +2982,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>банк-агент</t>
+          <t>Нацстатком</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3014,12 +3018,12 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>ФО-95</t>
+          <t>ФО-94</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>Погашенные кредиты за период</t>
+          <t>Отчёт для банка-агента (заготовка)</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -3029,12 +3033,12 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Внешняя отчётность</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>банк-агент</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
@@ -3044,20 +3048,24 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
+          <t>ТЗ 20 п. 13.7</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>нет — новая форма</t>
-        </is>
-      </c>
-      <c r="J60" s="9" t="inlineStr">
-        <is>
-          <t>obrazcy/ФО-95.xlsx</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr"/>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>Образец формы. Без образца к заморозке строка снимается</t>
+        </is>
+      </c>
       <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
@@ -3066,59 +3074,51 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>ФО-29</t>
+          <t>ФО-95</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о наступающем платеже</t>
+          <t>Погашенные кредиты за период</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Бланк</t>
+          <t>Отчёт</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>язык интерфейса</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
+          <t>решение владельца 29.10.2026: выделен из вида ФО-02; закрытие кредитно-залоговых дел и снятие обременений после погашения</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>За 30 дней до платежа по графику</t>
-        </is>
-      </c>
+          <t>нет — новая форма</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>obrazcy/ФО-95.xlsx</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
+      <c r="L61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>ФО-30</t>
+          <t>ФО-29</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Первичная претензия</t>
+          <t>Уведомление о наступающем платеже</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
+          <t>Порядок №41 п. 15 пп. 2; оф. ТЗ ¶553–556; ТЗ 13</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>старая система «Претензия»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -3174,7 +3174,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>За 30 дней до платежа по графику</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -3182,12 +3186,12 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>ФО-31</t>
+          <t>ФО-30</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Повторная претензия</t>
+          <t>Первичная претензия</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3212,12 +3216,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
+          <t>Порядок №41 п. 16 пп. 2; оф. ТЗ ¶553–556; старая система</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Претензия»</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>ФО-32</t>
+          <t>ФО-31</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Требование поручителю, гаранту, госоргану</t>
+          <t>Повторная претензия</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -3258,7 +3262,7 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>поручитель, гарант, госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
@@ -3268,7 +3272,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 4</t>
+          <t>Порядок №41 п. 16 пп. 3; оф. ТЗ ¶553–556</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -3294,12 +3298,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>ФО-33</t>
+          <t>ФО-32</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Извещение о начале обращения взыскания на предмет залога</t>
+          <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, залогодатель, орган регистрации</t>
+          <t>поручитель, гарант, госорган</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -3324,7 +3328,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+          <t>Порядок №41 п. 16 пп. 4</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -3350,167 +3354,171 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
+          <t>ФО-33</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>Извещение о начале обращения взыскания на предмет залога</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Взыскание</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик, залогодатель, орган регистрации</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Порядок №41 п. 20 пп. 1, п. 32, п. 45; оф. ТЗ ¶962</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Акт сверки задолженности на 1 января</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H66" s="7" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Порядок №41 п. 9, п. 11 пп. 1; оф. ТЗ ¶961; старая система</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>старая система «Акт сверки»</t>
         </is>
       </c>
-      <c r="J66" s="7" t="inlineStr">
+      <c r="J67" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr">
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>Подписывается со всеми действующими заёмщиками до 1 сентября</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D67" s="10" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>Взыскание</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Порядок №41 п. 64</t>
         </is>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J67" s="10" t="inlineStr">
+      <c r="J68" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K67" s="13" t="inlineStr">
+      <c r="K68" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L67" s="10" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>ФО-35</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Взыскание</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>Департамент правового обеспечения</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>рус</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 19 пп. 2; старая система</t>
-        </is>
-      </c>
-      <c r="I68" s="7" t="inlineStr">
-        <is>
-          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr"/>
-      <c r="L68" s="7" t="inlineStr"/>
+      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n">
@@ -3518,12 +3526,12 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-36</t>
+          <t>ФО-35</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании принудительного взыскания</t>
+          <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -3548,12 +3556,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 19 пп. 2</t>
+          <t>Порядок №41 п. 19 пп. 2; старая система</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система, распечатка «Расчет» («На исковое заявление»); «1.pdf», «chakanges/*.pdf»</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -3570,12 +3578,12 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-37</t>
+          <t>ФО-36</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о судебном взыскании</t>
+          <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
@@ -3590,7 +3598,7 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Председатель Правления</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
@@ -3600,7 +3608,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21</t>
+          <t>Порядок №41 п. 19 пп. 2</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -3622,12 +3630,12 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-38</t>
+          <t>ФО-37</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Исковое заявление</t>
+          <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -3642,22 +3650,22 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>суд</t>
+          <t>Председатель Правления</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
+          <t>Порядок №41 п. 21</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>старая система «Доо талап»</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
@@ -3665,11 +3673,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
@@ -3678,12 +3682,12 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>ФО-39</t>
+          <t>ФО-38</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о возврате материалов на доработку</t>
+          <t>Исковое заявление</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -3698,22 +3702,22 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>суд</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 20 пп. 1, 2</t>
+          <t>Порядок №41 п. 21; оф. ТЗ ¶558; старая система</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Доо талап»</t>
         </is>
       </c>
       <c r="J72" s="7" t="inlineStr">
@@ -3721,7 +3725,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="7" t="inlineStr"/>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
@@ -3730,12 +3738,12 @@
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>ФО-40</t>
+          <t>ФО-39</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Справка о задолженности</t>
+          <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -3745,22 +3753,22 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 05; ТЗ 14; старая система</t>
+          <t>Порядок №41 п. 20 пп. 1, 2</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
@@ -3773,11 +3781,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K73" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
@@ -3786,171 +3790,171 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
+          <t>ФО-40</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Справка о задолженности</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 05; ТЗ 14; старая система</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Реестр погашений</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
+      <c r="H75" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶490–495; Порядок №41 п. 64; ТЗ 05; старая система</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>старая система, распечатка «Реестр погашений»</t>
         </is>
       </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C75" s="11" t="inlineStr">
+      <c r="C76" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D75" s="10" t="inlineStr">
+      <c r="D76" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E75" s="10" t="inlineStr">
+      <c r="E76" s="10" t="inlineStr">
         <is>
           <t>Платежи</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F76" s="10" t="inlineStr">
         <is>
           <t>заёмщик</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
+      <c r="G76" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>ТЗ 14</t>
         </is>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J75" s="10" t="inlineStr">
+      <c r="J76" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>С оговоркой «не подтверждено казначейством» для таких платежей</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>ФО-42</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>График погашения</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>График</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>заёмщик</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>старая система, выгрузка графика</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -3958,12 +3962,12 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>ФО-43</t>
+          <t>ФО-42</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>Акт обследования залога</t>
+          <t>График погашения</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -3973,27 +3977,27 @@
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>График</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>подразделение, ведущее кредит</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
+          <t>оф. ТЗ ¶61, ¶418, ¶872–874; ТЗ 05; старая система</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Положение №12, прил. 1 к прил. 2</t>
+          <t>старая система, выгрузка графика</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
@@ -4001,7 +4005,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K77" s="7" t="inlineStr"/>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
@@ -4010,12 +4018,12 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>ФО-44</t>
+          <t>ФО-43</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>Кредитный договор</t>
+          <t>Акт обследования залога</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -4025,27 +4033,27 @@
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>подразделение, ведущее кредит</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
+          <t>оф. ТЗ ¶356, ¶513–519, ¶859; Порядок №41 п. 10; Положение №12 п. 5.3, прил. 2 пп. 2.3–2.4; ТЗ 12</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
+          <t>Положение №12, прил. 1 к прил. 2</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr">
@@ -4053,11 +4061,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K78" s="7" t="inlineStr"/>
       <c r="L78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -4066,12 +4070,12 @@
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>ФО-45</t>
+          <t>ФО-44</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Договор залога</t>
+          <t>Кредитный договор</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4081,12 +4085,12 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -4096,12 +4100,12 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
+          <t>оф. ТЗ ¶345, ¶375–376; ТЗ 02; старая система</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>старая система «Шаблон договора (200 т.с.)», «Шаблон договора (50 т.с.)»</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
@@ -4122,12 +4126,12 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-46</t>
+          <t>ФО-45</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Договор поручительства</t>
+          <t>Договор залога</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -4142,7 +4146,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>поручитель</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -4152,7 +4156,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
+          <t>оф. ТЗ ¶352, ¶855; Положение №12 п. 4.1, прил. 1; ТЗ 12</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -4178,12 +4182,12 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
@@ -4193,12 +4197,12 @@
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>Имущество</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>источник предложения</t>
+          <t>поручитель</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -4208,7 +4212,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 22</t>
+          <t>оф. ТЗ ¶849, ¶851–852; Положение №12 прил. 1 п. 9; ТЗ 12</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
@@ -4234,12 +4238,12 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -4290,12 +4294,12 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -4346,12 +4350,12 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
@@ -4366,7 +4370,7 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>покупатель</t>
+          <t>источник предложения</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶965; ТЗ 22</t>
+          <t>ТЗ 22</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -4402,12 +4406,12 @@
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>ФО-52</t>
+          <t>ФО-51</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Справка по заёмщику</t>
+          <t>Претензия покупателю</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -4417,22 +4421,22 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>Заёмщик</t>
+          <t>Имущество</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>заказавший сотрудник</t>
+          <t>покупатель</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶403; ТЗ 04</t>
+          <t>оф. ТЗ ¶965; ТЗ 22</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
@@ -4445,7 +4449,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr"/>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
@@ -4454,12 +4462,12 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>ФО-60</t>
+          <t>ФО-52</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>Опись предметов залога по договору</t>
+          <t>Справка по заёмщику</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -4469,22 +4477,22 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Заёмщик</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заказавший сотрудник</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 10; ТЗ 12</t>
+          <t>оф. ТЗ ¶403; ТЗ 04</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -4497,11 +4505,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K86" s="7" t="inlineStr"/>
       <c r="L86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
@@ -4510,12 +4514,12 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>ФО-61</t>
+          <t>ФО-60</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>Справка об обеспеченности кредита</t>
+          <t>Опись предметов залога по договору</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -4530,17 +4534,17 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>Порядок №41 п. 10; ТЗ 12</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
@@ -4553,7 +4557,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr"/>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
@@ -4562,12 +4570,12 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>ФО-62</t>
+          <t>ФО-61</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
+          <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -4582,17 +4590,17 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
+          <t>оф. ТЗ ¶671–682; Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -4605,11 +4613,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K88" s="7" t="inlineStr"/>
       <c r="L88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
@@ -4618,12 +4622,12 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -4633,22 +4637,22 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>Заявка и комиссия</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 03</t>
+          <t>Положение №12 прил. 2 п. 2.5; ТЗ 12</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -4661,7 +4665,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="7" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
@@ -4670,12 +4678,12 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-64</t>
+          <t>ФО-63</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
+          <t>Протокол заседания комиссии по заявкам</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -4690,17 +4698,17 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>заявитель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 02; ТЗ 03</t>
+          <t>ТЗ 03</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -4713,11 +4721,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K90" s="7" t="inlineStr"/>
       <c r="L90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
@@ -4726,12 +4730,12 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>ФО-65</t>
+          <t>ФО-64</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>Карточка организации</t>
+          <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
@@ -4741,22 +4745,22 @@
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>Ведомство</t>
+          <t>Заявка и комиссия</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>заявитель</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 09</t>
+          <t>ТЗ 02; ТЗ 03</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
@@ -4769,7 +4773,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr"/>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
@@ -4778,12 +4786,12 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>ФО-66</t>
+          <t>ФО-65</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Журнал регистрации документов за период</t>
+          <t>Карточка организации</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -4793,7 +4801,7 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>Документооборот</t>
+          <t>Ведомство</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -4808,7 +4816,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
+          <t>ТЗ 09</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -4830,12 +4838,12 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -4860,7 +4868,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 23</t>
+          <t>оф. ТЗ ¶926, ¶930–935; ТЗ 23</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
@@ -4882,12 +4890,12 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>ФО-68</t>
+          <t>ФО-67</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>Опись дела</t>
+          <t>Лист ознакомления</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
@@ -4934,12 +4942,12 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t>ФО-69</t>
+          <t>ФО-68</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>Регистрационно-контрольная карточка документа</t>
+          <t>Опись дела</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -4986,12 +4994,12 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>ФО-70</t>
+          <t>ФО-69</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
+          <t>Регистрационно-контрольная карточка документа</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
@@ -5001,7 +5009,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Документооборот</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 37</t>
+          <t>ТЗ 23</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
@@ -5038,12 +5046,12 @@
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t>ФО-71</t>
+          <t>ФО-70</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
+          <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -5068,7 +5076,7 @@
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 42</t>
+          <t>Порядок №41 п. 37</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -5090,12 +5098,12 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>ФО-72</t>
+          <t>ФО-71</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об установлении правопреемника</t>
+          <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -5110,7 +5118,7 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
@@ -5120,7 +5128,7 @@
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
+          <t>Порядок №41 п. 42</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -5142,12 +5150,12 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>ФО-73</t>
+          <t>ФО-72</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об инициировании банкротства</t>
+          <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
@@ -5172,7 +5180,7 @@
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
+          <t>Порядок №41 п. 53; оф. ТЗ ¶562–567</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -5194,12 +5202,12 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>ФО-74</t>
+          <t>ФО-73</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Служебная записка об отказе в дополнительном залоге</t>
+          <t>Служебная записка об инициировании банкротства</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -5209,12 +5217,12 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Департамент правового обеспечения, отраслевые департаменты</t>
+          <t>Департамент правового обеспечения</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
@@ -5224,7 +5232,7 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 2 п. 2.5</t>
+          <t>Порядок №41 п. 58; оф. ТЗ ¶568</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -5246,12 +5254,12 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-75</t>
+          <t>ФО-74</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Отчёт документального мониторинга целевого использования</t>
+          <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -5261,12 +5269,12 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Департамент правового обеспечения, отраслевые департаменты</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -5276,12 +5284,12 @@
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
+          <t>Положение №12 прил. 2 п. 2.5</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 1</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -5298,12 +5306,12 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>ФО-76</t>
+          <t>ФО-75</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
+          <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -5328,12 +5336,12 @@
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 8, 9, прил. 2</t>
+          <t>Методика №16 пп. 4, 6, 7, прил. 1</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 2</t>
+          <t>Методика №16, прил. 1</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -5350,12 +5358,12 @@
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -5380,12 +5388,12 @@
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 пп. 6, 9, прил. 3</t>
+          <t>Методика №16 пп. 8, 9, прил. 2</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 3</t>
+          <t>Методика №16, прил. 2</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -5402,12 +5410,12 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>ФО-78</t>
+          <t>ФО-77</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -5422,7 +5430,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>служба риск-менеджмента</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
@@ -5432,12 +5440,12 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16 п. 13, прил. 4</t>
+          <t>Методика №16 пп. 6, 9, прил. 3</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Методика №16, прил. 4</t>
+          <t>Методика №16, прил. 3</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
@@ -5454,12 +5462,12 @@
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>ФО-79</t>
+          <t>ФО-78</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>Внутренний акт сверки платежей</t>
+          <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
@@ -5469,12 +5477,12 @@
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>Платежи</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>служба риск-менеджмента</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -5484,12 +5492,12 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
+          <t>Методика №16 п. 13, прил. 4</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Методика №16, прил. 4</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
@@ -5506,12 +5514,12 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>ФО-80</t>
+          <t>ФО-79</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Расчёт реструктуризации: условия и график до и после</t>
+          <t>Внутренний акт сверки платежей</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -5521,22 +5529,22 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Реструктуризация</t>
+          <t>Платежи</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>уполномоченный государственный орган</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
+          <t>оф. ТЗ ¶541–543; ТЗ 14</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -5549,16 +5557,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K106" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L106" s="7" t="inlineStr">
-        <is>
-          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
-        </is>
-      </c>
+      <c r="K106" s="7" t="inlineStr"/>
+      <c r="L106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>ФО-81</t>
+          <t>ФО-80</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
+          <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №14 п. 96; ТЗ 15</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
@@ -5614,7 +5614,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L107" s="7" t="inlineStr"/>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>По одному кредиту, прилагается к письму по реструктуризации (ФО-90). Свод по кредитам — ФО-10, вид «Влияние реструктуризации»</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n">
@@ -5622,12 +5626,12 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>ФО-82</t>
+          <t>ФО-81</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о переводе долга</t>
+          <t>Дополнительное соглашение к кредитному договору</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -5642,7 +5646,7 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>заёмщик, новый заёмщик</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
@@ -5652,7 +5656,7 @@
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>оф. ТЗ ¶375–376, ¶380</t>
+          <t>ПКМ №14 п. 96; ТЗ 15</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
@@ -5678,12 +5682,12 @@
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>ФО-83</t>
+          <t>ФО-82</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о добровольном исполнении судебного акта</t>
+          <t>Соглашение о переводе долга</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -5693,12 +5697,12 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>заёмщик, новый заёмщик</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -5708,7 +5712,7 @@
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 38</t>
+          <t>оф. ТЗ ¶375–376, ¶380</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -5734,12 +5738,12 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>ФО-84</t>
+          <t>ФО-83</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Соглашение о расторжении кредитного договора</t>
+          <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
@@ -5749,7 +5753,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -5764,7 +5768,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 п. 3.4</t>
+          <t>Порядок №41 п. 38</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -5782,11 +5786,7 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>Когда заёмщик не получил средства кредита</t>
-        </is>
-      </c>
+      <c r="L110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t>ФО-85</t>
+          <t>ФО-84</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
+          <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 48</t>
+          <t>Положение №12 прил. 3 п. 3.4</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -5842,7 +5842,11 @@
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L111" s="7" t="inlineStr"/>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>Когда заёмщик не получил средства кредита</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n">
@@ -5850,12 +5854,12 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>ФО-86</t>
+          <t>ФО-85</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>Платёжное требование в банк заёмщика</t>
+          <t>Расчёт распределения выручки от реализации залога</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -5870,7 +5874,7 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>банк заёмщика</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
@@ -5880,7 +5884,7 @@
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
+          <t>Порядок №41 п. 48</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
@@ -5906,12 +5910,12 @@
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t>ФО-87</t>
+          <t>ФО-86</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
+          <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
@@ -5921,12 +5925,12 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Министерство финансов (казначейство)</t>
+          <t>банк заёмщика</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -5936,7 +5940,7 @@
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>ПКМ №554 Типовое положение п. 76</t>
+          <t>Порядок №41 п. 16 пп. 5; ТЗ 13</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -5962,12 +5966,12 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -5977,22 +5981,22 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Кредит</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>внутренний</t>
+          <t>Министерство финансов (казначейство)</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>рус</t>
+          <t>рус, кырг</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>ТЗ 12</t>
+          <t>ПКМ №554 Типовое положение п. 76</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -6005,7 +6009,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K114" s="7" t="inlineStr"/>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
       <c r="L114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
@@ -6014,12 +6022,12 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>ФО-89</t>
+          <t>ФО-88</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>Дополнительное соглашение к договору залога</t>
+          <t>Паспорт предмета залога</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -6034,12 +6042,12 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>внутренний</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>рус, кырг</t>
+          <t>рус</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
@@ -6057,11 +6065,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
+      <c r="K115" s="7" t="inlineStr"/>
       <c r="L115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6070,115 +6074,115 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
+          <t>ФО-89</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к договору залога</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Залог</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>залогодатель</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>ТЗ 12</t>
+        </is>
+      </c>
+      <c r="I116" s="7" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr">
         <is>
           <t>Письмо по кредиту</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>Кредит</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>по виду письма</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>Порядок №41; Положение №12; Методика №16; ПКМ №554; ТЗ 21</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
+      <c r="I117" s="7" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J116" s="7" t="inlineStr">
+      <c r="J117" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="13" t="inlineStr">
+      <c r="K117" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L116" s="7" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>Один бланк с видами ниже; у каждого вида свой текст</t>
         </is>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr">
-        <is>
-          <t>вид «По реструктуризации — уполномоченному органу»</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="inlineStr">
-        <is>
-          <t>Бланк</t>
-        </is>
-      </c>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>Реструктуризация</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t>уполномоченный государственный орган</t>
-        </is>
-      </c>
-      <c r="G117" s="10" t="inlineStr">
-        <is>
-          <t>рус, кырг</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>Порядок №41 п. 18; ТЗ 15</t>
-        </is>
-      </c>
-      <c r="I117" s="10" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="J117" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K117" s="13" t="inlineStr">
-        <is>
-          <t>Кыргызский текст</t>
-        </is>
-      </c>
-      <c r="L117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="10" t="n">
@@ -6191,7 +6195,7 @@
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
+          <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
@@ -6201,12 +6205,12 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>Взыскание</t>
+          <t>Реструктуризация</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
-          <t>родственники заёмщика</t>
+          <t>уполномоченный государственный орган</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
@@ -6216,7 +6220,7 @@
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 51 пп. 3</t>
+          <t>Порядок №41 п. 18; ТЗ 15</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr">
@@ -6247,7 +6251,7 @@
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
@@ -6262,7 +6266,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>нотариат, ЦОН, орган регистрации</t>
+          <t>родственники заёмщика</t>
         </is>
       </c>
       <c r="G119" s="10" t="inlineStr">
@@ -6272,7 +6276,7 @@
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 пп. 51–52</t>
+          <t>Порядок №41 п. 51 пп. 3</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr">
@@ -6303,7 +6307,7 @@
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
+          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
@@ -6318,7 +6322,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>нотариат, ЦОН, орган регистрации</t>
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr">
@@ -6328,7 +6332,7 @@
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>Порядок №41 п. 55</t>
+          <t>Порядок №41 пп. 51–52</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr">
@@ -6359,7 +6363,7 @@
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
+          <t>вид «О намерении инициировать банкротство — заёмщику»</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
@@ -6369,12 +6373,12 @@
       </c>
       <c r="E121" s="10" t="inlineStr">
         <is>
-          <t>Целевое использование</t>
+          <t>Взыскание</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>заёмщик, отраслевой госорган</t>
+          <t>заёмщик</t>
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr">
@@ -6384,7 +6388,7 @@
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
+          <t>Порядок №41 п. 55</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr">
@@ -6415,7 +6419,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
+          <t>вид «По целевому использованию — запрос документов, предписание об устранении нарушений»</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
@@ -6425,12 +6429,12 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>Залог</t>
+          <t>Целевое использование</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>нотариус, регистрирующий орган</t>
+          <t>заёмщик, отраслевой госорган</t>
         </is>
       </c>
       <c r="G122" s="10" t="inlineStr">
@@ -6440,7 +6444,7 @@
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
+          <t>Методика №16 п. 6 пп. 1, пп. 14–15</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr">
@@ -6471,7 +6475,7 @@
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
+          <t>вид «О снятии запрета на отчуждение — нотариусу, регистрирующему органу»</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
@@ -6486,7 +6490,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>залогодатель</t>
+          <t>нотариус, регистрирующий орган</t>
         </is>
       </c>
       <c r="G123" s="10" t="inlineStr">
@@ -6496,7 +6500,7 @@
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Положение №12 п. 8</t>
+          <t>Положение №12 прил. 3 пп. 3.2–3.7; оф. ТЗ ¶520–524</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr">
@@ -6527,7 +6531,7 @@
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>вид «Запрос финансового пакета — заёмщику»</t>
+          <t>вид «Согласие на действия с заложенным имуществом без снятия запрета»</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
@@ -6537,12 +6541,12 @@
       </c>
       <c r="E124" s="10" t="inlineStr">
         <is>
-          <t>Кредит</t>
+          <t>Залог</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>заёмщик</t>
+          <t>залогодатель</t>
         </is>
       </c>
       <c r="G124" s="10" t="inlineStr">
@@ -6552,7 +6556,7 @@
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>ТЗ 21</t>
+          <t>Положение №12 п. 8</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr">
@@ -6583,106 +6587,106 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
+          <t>вид «Запрос финансового пакета — заёмщику»</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Бланк</t>
+        </is>
+      </c>
+      <c r="E125" s="10" t="inlineStr">
+        <is>
+          <t>Кредит</t>
+        </is>
+      </c>
+      <c r="F125" s="10" t="inlineStr">
+        <is>
+          <t>заёмщик</t>
+        </is>
+      </c>
+      <c r="G125" s="10" t="inlineStr">
+        <is>
+          <t>рус, кырг</t>
+        </is>
+      </c>
+      <c r="H125" s="10" t="inlineStr">
+        <is>
+          <t>ТЗ 21</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="J125" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>Кыргызский текст</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
           <t>вид «Возврат проекта на доработку — заявителю»</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>Бланк</t>
         </is>
       </c>
-      <c r="E125" s="10" t="inlineStr">
+      <c r="E126" s="10" t="inlineStr">
         <is>
           <t>Заявка и комиссия</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F126" s="10" t="inlineStr">
         <is>
           <t>заявитель</t>
         </is>
       </c>
-      <c r="G125" s="10" t="inlineStr">
+      <c r="G126" s="10" t="inlineStr">
         <is>
           <t>рус, кырг</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>ПКМ №554 пп. 66, 74</t>
         </is>
       </c>
-      <c r="I125" s="10" t="inlineStr">
+      <c r="I126" s="10" t="inlineStr">
         <is>
           <t>нет</t>
         </is>
       </c>
-      <c r="J125" s="10" t="inlineStr">
+      <c r="J126" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K125" s="13" t="inlineStr">
+      <c r="K126" s="13" t="inlineStr">
         <is>
           <t>Кыргызский текст</t>
         </is>
       </c>
-      <c r="L125" s="10" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>ОТ-1</t>
-        </is>
-      </c>
-      <c r="C126" s="7" t="inlineStr">
-        <is>
-          <t>Выгрузка любого экранного списка в xlsx</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Требование</t>
-        </is>
-      </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>Все модули</t>
-        </is>
-      </c>
-      <c r="F126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="7" t="inlineStr">
-        <is>
-          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
-        </is>
-      </c>
-      <c r="I126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K126" s="7" t="inlineStr"/>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>Видимые колонки списка с учётом фильтров экрана</t>
-        </is>
-      </c>
+      <c r="L126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n">
@@ -6690,54 +6694,110 @@
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
+          <t>ОТ-1</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>Выгрузка любого экранного списка в xlsx</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Требование</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Все модули</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>оф. ТЗ ¶799; старая система (выгрузка списков в Excel)</t>
+        </is>
+      </c>
+      <c r="I127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr"/>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>Видимые колонки списка с учётом фильтров экрана</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
           <t>ОТ-2</t>
         </is>
       </c>
-      <c r="C127" s="7" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>Форматы выгрузки: отчёт — xlsx и pdf, бланк — docx и pdf</t>
         </is>
       </c>
-      <c r="D127" s="7" t="inlineStr">
+      <c r="D128" s="7" t="inlineStr">
         <is>
           <t>Требование</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>Отчётность</t>
         </is>
       </c>
-      <c r="F127" s="7" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H127" s="7" t="inlineStr">
+      <c r="H128" s="7" t="inlineStr">
         <is>
           <t>оф. ТЗ ¶146, ¶150–151, ¶799, ¶812–817</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J127" s="7" t="inlineStr">
+      <c r="J128" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K127" s="7" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr"/>
+      <c r="K128" s="7" t="inlineStr"/>
+      <c r="L128" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A17:L127"/>
+  <autoFilter ref="A17:L128"/>
   <mergeCells count="13">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
@@ -6792,7 +6852,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6805,7 +6866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7411,17 +7472,18 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Залоговое обеспечение — предметы</t>
+          <t>Предметы залога по состоянию на дату</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1. ИТОГО по «Оценочной стоимости» и «Залоговой стоимости» = сумма стоимостей предметов залога набора на дату отчёта, каждый предмет один раз.
-2. «Остаток задолженности» и «Просрочка» по кредиту КЗ-04 (№ 21-5/203 от 09.09.2021) = значения в карточке кредита на дату отчёта; ИТОГО = сумма по кредитам набора, каждый кредит один раз.
-3. КЗ-14 показан двумя договорами залога (№ 24-6/019-З1 — здание и трактор, № 24-6/019-З2 — производственная линия); кредит № 24-6/019 выведен один раз, под договором № 24-6/019-З1. Предмет «Трактор» имеет отметку «утрачен», «Производственная линия» — «в наличии, хорошее».
-4. «Дата обследования» предмета = дата последнего акта по нему в ФО-15.
-5. Подытог по договору, заёмщику, району и области = сумма строк ниже по каждой числовой колонке.
-6. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
+          <t>1. На 01.10.2026: 2 заёмщика, 3 договора залога, 5 предметов; оценочная стоимость 17 100,000 тыс. сом, залоговая 11 610,000.
+2. КЗ-04 ОсОО «Ош-Текстиль», договор № 21-5/203-З1 от 09.09.2021: нежилое здание (цех) — 8 000,000 / 5 600,000, земельный участок — 3 000,000 / 2 100,000; статус залога «реализуется» — внесудебное обращение взыскания начато решением комитета (протокол № 6 от 02.06.2026, ФО-33).
+3. КЗ-14 ОсОО «Ак-Булак»: договор № 24-6/019-З1 — здание склада 4 300,000 / 3 010,000 и трактор МТЗ-82.1, утрачен (акт обследования 18.09.2026, ФО-43), 0,00 / 0,00; договор № 24-6/019-З2 — линия фасовки 1 800,000 / 900,000. Залоговая стоимость по заёмщику 3 910,000 — та же, что в справке ФО-61.
+4. Залоговая = оценочная × коэффициент вида: недвижимость 0,7 (4 300,000 × 0,7 = 3 010,000), оборудование 0,5 (1 800,000 × 0,5 = 900,000).
+5. «Дата обследования» и «Состояние» предмета = дата и исход его последнего акта в ФО-15.
+6. Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику. Предметов КЗ-15 в отчёте нет: запрет снят в сентябре 2026 (ФО-16).
+7. При единице «сом» все суммы в 1000 раз больше, чем при «тыс. сом».</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -7436,20 +7498,53 @@
       <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>ФО-14</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>вид «Обеспеченность кредитов залогом по состоянию на дату»</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>1. На 01.10.2026: 2 заёмщика, 2 кредита; сумма под риском 6 550,000 тыс. сом; залоговая стоимость 11 610,000 — та же, что ИТОГО основного отчёта (каждый предмет отнесён к одному кредиту целиком); недостаёт 515,000.
+2. КЗ-14 № 24-6/019: сумма под риском 2 950,000; залоговая 3 910,000 (здание склада 3 010,000 + линия фасовки 900,000, трактор утрачен — 0,00); порог 150 % (в залоге оборудование); требуется 4 425,000; индекс 88,4 %; доля ликвидного 102,0 %; недостаёт 515,000 — «не обеспечен». Те же числа в справке ФО-61.
+3. КЗ-04 № 21-5/203: сумма под риском 3 600,000; залоговая 7 700,000; порог 120 % (только недвижимость); требуется 4 320,000; индекс 178,2 %; доля ликвидного не применяется — «обеспечен».
+4. Строка разреза = сумма строк на уровень ниже по суммам и счётчикам.</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-04, КЗ-14</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>ФО-15</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Акты обследования залога</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>1. Число строк актов = число актов обследования в карточках предметов залога набора за период; ИТОГО «Кол-во актов» им равно.
 2. КЗ-14: два договора залога, три предмета и четыре акта; у «Трактора» результат «Залог утрачен» от 10.08.2026 и пустая дата следующего обследования.
@@ -7459,32 +7554,32 @@
 6. С отбором «Только предметы без акта в периоде» в отчёте нет предметов, у которых в периоде есть акт.</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>ФО-16</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Снятие с ареста (запрета на отчуждение)</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>1. Число строк снятий = число записей о снятии запрета в карточках предметов залога набора за период; ИТОГО «Кол-во снятий» им равно.
 2. КЗ-15 показан: кредит погашен в сентябре 2026, запрет снят с двух предметов полностью; в колонке «Вид снятия» нет пустых значений.
@@ -7493,32 +7588,32 @@
 5. Все даты снятия попадают в период отчёта.</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Взыскание — реестр принятых мер (процедуры, фазы, события)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>1. Число фаз в строке ИТОГО = число фаз взыскания в карточках процедур отобранных заёмщиков на дату снимка; в образце — 6 (КЗ-04, КЗ-05, КЗ-16).
 2. КЗ-05: три фазы (иск от 16.03.2026, заявление о выдаче исполнительного листа, письмо в ПССИ от 10.07.2026), статус «Передана в ОИП», соглашение о добровольном исполнении № 3 от 10.09.2026; «Всего остаток» 1 434 810,42 = сумма требования по иску, погашений по судебному акту на 01.10.2026 нет; платежи по соглашению — шесть по 239 135,07 с 10.10.2026 по 10.03.2027.
@@ -7528,32 +7623,32 @@
 6. Подытог процедуры, заёмщика, района, области и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>КЗ-04, КЗ-05, КЗ-16</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>вид «ОИП — исполнительные листы в органе исполнительного производства»</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только фазы с исполнительным листом на исполнении в ОИП в периоде или закрытые в периоде; для набора — КЗ-05.
 2. КЗ-05: «Всего погашено» 0,00, «Всего остаток» 1 434 810,42, «Погашено в период» за сентябрь 2026 — 0,00: платежей по соглашению о добровольном исполнении № 3 от 10.09.2026 в сентябре нет.
@@ -7561,32 +7656,32 @@
 4. Подытоги и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="inlineStr"/>
+      <c r="J24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ФО-17</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>вид «Претензии по областям за период»</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>1. В отчёте только заёмщики с претензией, направленной в периоде: КЗ-02 (первичная от 25.09.2026) и КЗ-03 (повторная от 15.09.2026); первичная претензия КЗ-03 вне периода не повторяется.
 2. «Сумма» претензии = просроченная задолженность на дату претензии (Порядок №41 п. 16 пп. 2–3): КЗ-02 — 180 850,00 (основная сумма 150 000,00, проценты 28 500,00, штрафы 2 350,00), КЗ-03 — 149 400,00 (90 000,00 + 41 000,00 + 18 400,00), как в ФО-01.
@@ -7595,42 +7690,9 @@
 5. Подытоги области, района и ИТОГО = сумма строк ниже по каждой числовой колонке.</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>КЗ-02</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="10" t="inlineStr"/>
-      <c r="J24" s="10" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>ФО-17</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>вид «События фазы по датам и времени»</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
-2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
-3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
-4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-05</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr"/>
@@ -7640,20 +7702,53 @@
       <c r="J25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="8" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>ФО-17</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>вид «События фазы по датам и времени»</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>1. Число строк событий = число событий журнала мер у отобранных заёмщиков за период; ИТОГО «Событий» им равно.
+2. КЗ-05: 9 событий в четырёх фазах (служебные записки и расчёт, возврат на доработку и доработанные материалы; иск и решение суда; заявление и исполнительный лист; письмо в ПССИ и соглашение № 3 от 10.09.2026); в каждой фазе события идут по возрастанию даты и времени.
+3. Подытог «Событий» по фазе, процедуре и заёмщику = число строк событий под ним.
+4. «Сумма требования» и «Поступление» в подытогах = сумма значений событий под ними; событие без суммы в сумму не входит.</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>КЗ-05</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ФО-18</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Оформление — комплектность кредитно-залогового дела</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>1. «Кол-во документов» пакета = число документов в перечне дела по кредиту; сумма «укомплектовано» и «не укомплектовано» равна ему, как и сумма «проверено» и «не проверено».
 2. КЗ-20: дело не укомплектовано — не хватает «Страхового полиса на залог»; статус пакета «Не укомплектовано».
@@ -7662,32 +7757,32 @@
 5. Подытоги и ИТОГО = сумма строк ниже по числовым колонкам.</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>ФО-19</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Документооборот — входящие и исходящие</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>1. Число строк документов = число зарегистрированных в периоде документов журналов входящих и исходящих; ИТОГО им равно.
 2. КЗ-20: входящее письмо от 14.09.2026 и два исходящих (25.09.2026 и 30.09.2026); номера и даты равны номерам и датам в журналах регистрации.
@@ -7697,32 +7792,32 @@
 6. «На контроле» = признак в карточке документа; с отбором «На контроле — да» остаются только отмеченные документы (в образце — входящее письмо).</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>ФО-20</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Задания и их исполнение</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>1. «Назначено» в ИТОГО = число заданий, назначенных в периоде, в модуле «Задания».
 2. Назначено = в работе + исполнено + отказано; исполнено = в срок + с опозданием.
@@ -7732,32 +7827,32 @@
 6. «Сумма по заданию» = платёж по графику кредита КЗ-20 (№ 25-3/014 от 05.03.2025) на 01.11.2026: основная сумма 100 000,00 + проценты 9 166,67 (1 100 000,00 × 10 % / 12).</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>ФО-24</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Классификация — движение по группам платёжеспособности</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>1. Число заёмщиков и остаток в разделе «Состав групп» на каждую дату = группы в карточках заёмщиков (поле «Группа платёжеспособности») на эту дату и остатки их кредитов.
 2. Сумма раздела «Состав групп» = сумма раздела «Переходы между группами» = ИТОГО по обеим датам; остаток на дату 2 в ИТОГО = ИТОГО ФО-26 (39 482 500,00).
@@ -7766,32 +7861,32 @@
 5. КЗ-17: переход «не было → 1.1» (кредит № 26-5/090 от 08.09.2026); КЗ-18 (договор расторгнут, средства не получены) в отчёте не показан ни на одну из дат.</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>весь набор; особо: КЗ-19</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Кураторство — нагрузка и закрепление</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>1. Число кредитов и портфель куратора = число и остаток кредитов, закреплённых за ним на дату по журналу закреплений.
 2. Подытоги подразделения и куратора и ИТОГО равны сумме строк ниже по колонкам „Кредитов“, „Портфель“ и „Просроченная задолженность“.
@@ -7800,32 +7895,32 @@
 5. Кредит, закрытый до даты отчёта (КЗ-08, 15, 16, 18), в отчёте не показан; закрепление закрытого кредита остаётся в журнале.</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>ФО-25</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>вид «Погашенные заёмщики: месяц × куратор»</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>1. Заёмщик попадает в месяц по дате, когда его кредит стал погашенным; дата погашения находится внутри месяца.
 2. „Погашено кредитов“ не больше „Всего кредитов у заёмщика“; подытоги и ИТОГО равны сумме строк ниже.
@@ -7834,32 +7929,32 @@
 5. КЗ-07 (долг переведён на ОсОО «Ысык-Көл Логистик» 09.09.2026, кредит № 21-6/144 действует), КЗ-08 (списан) и КЗ-18 (расторгнут) в отчёте не показаны — их кредиты не погашены.</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr"/>
-      <c r="G31" s="10" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr"/>
-      <c r="I31" s="10" t="inlineStr"/>
-      <c r="J31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="inlineStr"/>
+      <c r="J32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>ФО-26</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Портфель — оперативный срез</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы“ в ИТОГО = сумма остатков основной суммы по карточкам кредитов в состояниях «Зарегистрирован» и «Действует»: на контрольном наборе 17 кредитов, 39 482 500,00 сом.
 2. „Из них с просрочкой“ = число кредитов с „Дней просрочки“ больше нуля (на наборе 7: КЗ-02, 03, 04, 05, 09, 10, 19); подытоги и ИТОГО равны сумме строк.
@@ -7868,32 +7963,32 @@
 5. КЗ-11: остаток 4 812 500,00 сом (55 000,00 USD × 87,50); погашенные, списанные и расторгнутые кредиты (КЗ-15, КЗ-16, КЗ-08, КЗ-18) в отчёте не показаны.</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>ФО-27</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Средняя просрочка по департаментам</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>1. „Средние дни просрочки“ подразделения = сумма дней просрочки его кредитов с просрочкой, делённая на их число.
 2. „Средние дни просрочки“ в ИТОГО считаются по всем кредитам с просрочкой, а не как среднее по подразделениям.
@@ -7902,39 +7997,6 @@
 5. При дате в прошлом значения берутся из состояния на конец этого дня.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>ФО-28</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Доля проблемных кредитов</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
-2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
-3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
-4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
-        </is>
-      </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
@@ -7952,15 +8014,48 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
+          <t>ФО-28</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Доля проблемных кредитов</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>1. „Остаток всего“ в ИТОГО = остаток основной суммы по всем кредитам портфеля на дату (совпадает с ИТОГО ФО-26): 39 482 500,00.
+2. Кредит проблемный ровно тогда, когда группа его заёмщика на дату не «1.1»; группа совпадает с ФО-24.
+3. „Доля проблемных“ подразделения и ИТОГО = „Остаток проблемных“ / „Остаток всего“ × 100, не среднее долей по строкам.
+4. На наборе проблемных 8 кредитов на 14 970 000,00: КЗ-02, 03, 04, 06, 09 (группа 1.2), КЗ-05 (2.1), КЗ-10 (2.3), КЗ-19 (3.1); доля 37,9 %. КЗ-06 после реструктуризации остаётся в группе 1.2 и считается проблемным; КЗ-01 и КЗ-07 — нет.</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>весь набор</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
           <t>ФО-47</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Реестр имущества на дату</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>1. ИТОГО «Количество» и «Учётная стоимость» = число и сумма учётных стоимостей объектов реестра имущества на дату среза; учётная стоимость = стоимость принятия (КЗ-16 — 4 800 000,00).
 2. КЗ-16: на 01.10.2026 объект в состоянии «Продан» (договор купли-продажи № КП-4/26 от 04.05.2026 в рассрочку; расторжения нет); на 30.04.2026 тот же объект показан как «На учёте».
@@ -7969,32 +8064,32 @@
 5. Подытог по состоянию и источнику = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>КЗ-16</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>ФО-53</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Расчёт в валюте и курсовая разница за период</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>1. Остаток на конец периода в валюте = остатку основного долга по карточке кредита на дату окончания периода.
 2. Курсы = официальным курсам валюты на даты начала и окончания периода из справочника курсов.
@@ -8003,32 +8098,32 @@
 5. Подытог и ИТОГО по колонкам в сомах = сумма строк ниже.</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>КЗ-11</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>ФО-54</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>План-факт погашений</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>1. «По графику за период» по кредиту = сумма платежей графика кредита с датой в периоде (карточка кредита, вкладка «График»).
 2. «Погашено за период» по кредиту = сумма платежей кредита с датой в периоде в реестре платежей.
@@ -8038,32 +8133,32 @@
 6. Кредиты без графика и плана в периоде не показываются (КЗ-15, погашен 18.09.2026): ИТОГО «Погашено» меньше ИТОГО ФО-04 за тот же месяц на их платежи и на платежи кредитов, не включённых в образец.</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-02</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>ФО-55</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Заявки по программам и статусам</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>1. Число заявок в ИТОГО = число заявок с датой подачи в периоде в списке заявок.
 2. „Одобрено“ по заявке = сумма, указанная в решении комиссии; „Доля одобренного“ в итоговых строках считается из сумм, не как среднее долей.
@@ -8072,42 +8167,9 @@
 5. Статусы „На рассмотрении“ и „Отклонена“ проверяются на заявках, которые будут добавлены в набор (см. вопрос ниже).</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>КЗ-17, КЗ-18</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>ФО-56</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>План и факт выдачи</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
-2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
-3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
-4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-17</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -8122,15 +8184,48 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
+          <t>ФО-56</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>План и факт выдачи</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>1. „План выдачи на год“ = значение справочника «Плановые показатели» для подразделения на год отчёта.
+2. „Выдано с начала года“ = сумма освоений подразделения с 01.01 по дату отчёта; подытог и ИТОГО равны сумме строк ниже.
+3. КЗ-17: выдача 1 500 000,00 сом от 15.09.2026 по кредиту № 26-5/090 (договор от 08.09.2026) учтена в РП «Ош»; итог выдачи — 1 500 000,00.
+4. КЗ-12: освоений в 2026 году нет (транши 20.03.2024 и 25.06.2024), в „Выдано“ не входит; КЗ-18 (одобрен, средства не получены) не входит.</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr"/>
+      <c r="J40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
           <t>ФО-57</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Данные для расчёта ОКУ на дату</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>1. „Основная сумма“, „Проценты“, „Штраф“ по кредиту = остатки по карточке кредита на ту же дату, вкладка «Расчёты»; „Всего“ = их сумма.
 2. „Из них просроченная“ по кредиту = просроченная задолженность из ФО-01; ИТОГО = ИТОГО ФО-01 (4 560 750,00). Остаток основной суммы в ИТОГО = ИТОГО ФО-26 (39 482 500,00), строк 17.
@@ -8140,32 +8235,32 @@
 6. Подытог подразделения и ИТОГО равны сумме строк ниже по колонкам остатков; колонки с оценкой залога не суммируются.</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>ФО-58</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Изменения статусов кредитов за период</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>1. Число изменений в ИТОГО = числу событий смены состояния кредитов набора за период по журналу изменений кредитов (6).
 2. КЗ-15, КЗ-08, КЗ-18 показаны с закрытием и причиной: погашен, списан, расторгнут.
@@ -8174,32 +8269,32 @@
 5. Подытог подразделения и заёмщика и ИТОГО = числу строк-событий ниже.</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>КЗ-06, КЗ-07, КЗ-08, КЗ-15, КЗ-18</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>ФО-59</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Кредитный риск портфеля</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>1. „Остаток основной суммы портфеля“ на конец квартала = ИТОГО ФО-26 на ту же дату (39 482 500,00); „Просроченная задолженность“ = ИТОГО ФО-01 (4 560 750,00); кредитов 17.
 2. „Доля проблемных кредитов“ = итог ФО-28 (37,9 %), „Средняя просрочка“ = итог ФО-27 (180,1) на ту же дату.
@@ -8209,41 +8304,9 @@
 6. Значение „на начало“ равно значению „на конец“ отчёта за предыдущий квартал.</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>весь набор</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>ФО-91</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт для Министерства финансов (заготовка)</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>1. Состав и колонки — по образцу заказчика.
-2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
-3. Форма выгружается в xlsx и pdf.</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Состав — по образцу заказчика</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -8258,12 +8321,12 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>ФО-92</t>
+          <t>ФО-91</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Кабинета Министров (заготовка)</t>
+          <t>Отчёт для Министерства финансов (заготовка)</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -8290,12 +8353,12 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>ФО-93</t>
+          <t>ФО-92</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для Национального статистического комитета (заготовка)</t>
+          <t>Отчёт для Кабинета Министров (заготовка)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
@@ -8322,12 +8385,12 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>ФО-94</t>
+          <t>ФО-93</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Отчёт для банка-агента (заготовка)</t>
+          <t>Отчёт для Национального статистического комитета (заготовка)</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -8354,15 +8417,47 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
+          <t>ФО-94</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Отчёт для банка-агента (заготовка)</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>1. Состав и колонки — по образцу заказчика.
+2. Каждый показатель формы получен из данных кредитов набора; источник показателя указан в описании формы.
+3. Форма выгружается в xlsx и pdf.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Состав — по образцу заказчика</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
           <t>ФО-95</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Погашенные кредиты за период</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>1. За 01.01.2026–30.09.2026: КЗ-16 (имуществом, 20.03.2026) и КЗ-15 (деньгами, 18.09.2026); ИТОГО — 2 заёмщика, 2 кредита, сумма по договору 6 500,000, получено 6 500,000, погашено 8 500,000 тыс. сом.
 2. За сентябрь 2026 (по умолчанию на 01.10.2026): только КЗ-15.
@@ -8373,42 +8468,9 @@
 7. У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>КЗ-15, КЗ-16</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>ФО-29</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>Уведомление о наступающем платеже</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
-2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
-3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
-4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
@@ -8423,15 +8485,48 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
+          <t>ФО-29</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Уведомление о наступающем платеже</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01, кредит № 21-3/117: платёж по графику 15-го числа; бланк доступен с 15.09.2026 (за 30 календарных дней до платежа 15.10.2026).
+2. Дата и суммы платежа в тексте = строке действующего графика кредита на эту дату: 15.10.2026, основная сумма 325 000,00, проценты 40 625,00, всего 365 625,00.
+3. Остаток основного долга в бланке от 02.10.2026 = остатку по карточке кредита КЗ-01 № 21-3/117 на эту дату — 3 900 000,00.
+4. Зарегистрированный бланк получает исходящий номер и виден в ФО-19.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
           <t>ФО-30</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Первичная претензия</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-02 бланк доступен с 1-го дня просрочки (12.09.2026); если за 10 рабочих дней он не зарегистрирован, система показывает куратору нарушение срока.
 2. Срок погашения в тексте = дата направления + 14 календарных дней (в образце дата направления совпадает с датой бланка).
@@ -8440,32 +8535,32 @@
 5. Зарегистрированная претензия КЗ-02 видна в ФО-17, вид «Претензии», и в ФО-19.</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>КЗ-02</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr"/>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>ФО-31</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Повторная претензия</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-03 бланк недоступен, пока по кредиту не зарегистрирована первичная претензия; срок 10 рабочих дней отсчитывается от даты окончания её срока.
 2. Номер и дата первичной претензии в тексте = записи ФО-17, вид «Претензии»; в образце — исх. № 12-04/0985 от 28.07.2026, срок истёк 11.08.2026.
@@ -8474,32 +8569,32 @@
 5. Бланк формируется в тот же день, что и требование поручителю КЗ-03 (ФО-32).</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>ФО-32</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Требование поручителю, гаранту, госоргану</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>1. КЗ-03: один поручитель — ОсОО «Кербен-Агро» (договор № 23-4/008-П1 от 20.06.2023) — один экземпляр.
 2. Дата бланка = дате повторной претензии КЗ-03 (ФО-31) — 24.08.2026.
@@ -8508,32 +8603,32 @@
 5. Зарегистрированные экземпляры видны в ФО-17 по КЗ-03.</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>ФО-33</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>Извещение о начале обращения взыскания на предмет залога</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 система создаёт два экземпляра: заёмщику-залогодателю ОсОО «Ош-Текстиль» (одно лицо — один экземпляр) и органу регистрации.
 2. Сведения о предмете залога в тексте = карточке предмета залога КЗ-04; договор о залоге № 21-5/203-З1 от 09.09.2021.
@@ -8542,42 +8637,9 @@
 5. При внесудебном порядке бланк недоступен, пока по кредиту нет решения комитета.</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
-        </is>
-      </c>
-      <c r="F52" s="7" t="inlineStr"/>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>ФО-34</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>Акт сверки задолженности на 1 января</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
-2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
-3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
-4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
@@ -8587,20 +8649,53 @@
       <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="n">
+      <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>ФО-34</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Акт сверки задолженности на 1 января</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>1. КЗ-01: на 01.01.2026 действовали два кредита — № 21-3/117 и № 22-2/031 — формируются два акта.
+2. Платежи за год в акте по кредиту № 22-2/031 = платежам кредита с 01.01.2025 по 31.12.2025 в реестре платежей; сумма строк = итогу погашений за год.
+3. Остаток основного долга (2 100 000,00) и дни просрочки (0) = состоянию кредита на 01.01.2026, а не сегодняшнему (на 01.10.2026 остаток по кредиту № 22-2/031 — 1 200 000,00).
+4. КЗ-01: акт по кредиту № 21-3/117 подписан сторонами 20.03.2026 — отмечен в карточке кредита и виден в журнале мер взыскания (ФО-17); акт по кредиту № 22-2/031 не подписан — на 01.10.2026 показан куратору как просроченный по сроку 01.09.2026.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>ФО-34</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>вид «Акт сверки о полном погашении задолженности»</t>
         </is>
       </c>
-      <c r="D54" s="10" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>1. Бланк доступен только по кредиту с нулевым остатком основной суммы, процентов и штрафов (КЗ-15 — да; КЗ-01 — нет).
 2. Погашенные суммы в акте = итогам реестра погашений КЗ-15 по каждому виду.
@@ -8609,32 +8704,32 @@
 5. Подписанный акт отмечается в карточке КЗ-15 и виден в журнале мер взыскания (ФО-17) и в ФО-19.</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>КЗ-15</t>
         </is>
       </c>
-      <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="10" t="inlineStr"/>
-      <c r="H54" s="10" t="inlineStr"/>
-      <c r="I54" s="10" t="inlineStr"/>
-      <c r="J54" s="10" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr"/>
+      <c r="G55" s="10" t="inlineStr"/>
+      <c r="H55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="inlineStr"/>
+      <c r="J55" s="10" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>ФО-35</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Расчёт задолженности, подписанный отраслевым отделом</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>1. Строки таблицы КЗ-05 = событиям кредита по датам (выдача, платежи графика, поступления) в карточке кредита и совпадают со строками расчёта на вкладке «Расчёт» карточки кредита на ту же дату.
 2. Итоговая строка таблицы = сумме строк по каждой числовой колонке; остаток основной суммы в итоговом блоке (2 100 000,00) = остатку в карточке кредита на дату расчёта.
@@ -8643,32 +8738,32 @@
 5. Для кредитов, не переведённых в категорию «высокий кредитный риск» (КЗ-01), бланк формируется только по явному запросу куратора.</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr"/>
+      <c r="J56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>ФО-36</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об инициировании принудительного взыскания</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-05 бланк доступен после перехода в категорию «высокий кредитный риск» (15.02.2026); срок 10 рабочих дней отсчитывается от даты перехода.
 2. Задолженность в записке = расчёту ФО-35 на ту же дату (25.02.2026).
@@ -8677,32 +8772,32 @@
 5. После регистрации записка видна в ФО-19 и в фазе взыскания кредита.</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="7" t="inlineStr"/>
+      <c r="I57" s="7" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>ФО-37</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о судебном взыскании</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>1. Бланк доступен по КЗ-05 только после проверки пакета отделом по работе с проблемными кредитами и истечения срока претензии (06.10.2025).
 2. Задолженность в записке = расчёту на дату записки; цена иска в ФО-38 = расчёту на дату, указанную в иске.
@@ -8711,32 +8806,32 @@
 5. После резолюции «согласовано» по кредиту создаётся срок 5 рабочих дней на подготовку иска.</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>ФО-38</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Исковое заявление</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>1. Цена иска КЗ-05 = сумме основной суммы, процентов и штрафов в приложенном расчёте (ФО-35) на дату расчёта, указанную в иске (16.03.2026).
 2. Номер и дата договора, реквизиты сторон = карточке кредита и карточкам субъектов.
@@ -8745,32 +8840,32 @@
 5. Иск не формируется без записи о согласовании служебной записки ФО-37.</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
-      <c r="J58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>ФО-39</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о возврате материалов на доработку</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен только при зарегистрированной служебной записке ФО-36 по этому кредиту.
 2. Номер и дата служебной записки в тексте = записи в журнале внутренних документов (№ 12-02/0418 от 25.02.2026).
@@ -8779,32 +8874,32 @@
 5. После регистрации возврата срок 10 рабочих дней по записке закрыт, а в карточке кредита стоит отметка «возвращено на доработку» с датой 05.03.2026.</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr"/>
+      <c r="J60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>ФО-40</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Справка о задолженности</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) основной долг в справке на 01.10.2026 = 3 900 000,00 = остатку основного долга в карточке кредита на эту дату.
 2. Для КЗ-01 срочные проценты на 01.10.2026 = 21 666,67 (остаток 3 900 000,00 × 12,5 % × 16 дней с 15.09.2026 / 360).
@@ -8814,39 +8909,6 @@
 6. Для КЗ-11 (кредит в долларах) остаток дан в USD и в сомах по курсу НБ КР на дату справки.</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr"/>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>ФО-41</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Реестр погашений</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
-2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
-3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
-4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
-        </is>
-      </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
@@ -8859,20 +8921,53 @@
       <c r="J61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>ФО-41</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Реестр погашений</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в реестре два платежа — 15.07.2026 и 15.08.2026; строки совпадают с платежами кредита в реестре платежей.
+2. В каждой строке «всего» = основной долг + проценты + штрафы; «Итого» = сумма строк.
+3. Остаток основного долга после последнего платежа (15.08.2026) = 4 225 000,00 = остатку в карточке кредита на эту дату.
+4. Платёж, не подтверждённый казначейством, в реестр не попадает (он виден в виде «Выписка по кредиту»).</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="7" t="inlineStr"/>
+      <c r="I62" s="7" t="inlineStr"/>
+      <c r="J62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>ФО-41</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>вид «Выписка по кредиту»</t>
         </is>
       </c>
-      <c r="D62" s="10" t="inlineStr">
+      <c r="D63" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–30.09.2026 в выписке три платежа — 15.07, 15.08 и 15.09.2026; платёж от 15.09.2026 помечен «не подтверждён казначейством».
 2. Строка «в т. ч. не подтверждено казначейством» = сумма строк с этой пометкой по каждой колонке сумм; если таких нет, строка стоит с нулями.
@@ -8881,32 +8976,32 @@
 5. Тот же период в реестре погашений показывает только два подтверждённых платежа.</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr"/>
-      <c r="G62" s="10" t="inlineStr"/>
-      <c r="H62" s="10" t="inlineStr"/>
-      <c r="I62" s="10" t="inlineStr"/>
-      <c r="J62" s="10" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr"/>
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr"/>
+      <c r="J63" s="10" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>ФО-42</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>График погашения</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>1. Строки графика совпадают со вкладкой «График» карточки кредита: те же даты и суммы (таблица начинается с первого платежа по основному долгу, льготный период в неё не входит).
 2. «Основной долг» в строке «Итого» = сумме кредита (транша), если график охватывает весь срок; «Всего» = основной долг + проценты в каждой строке.
@@ -8914,32 +9009,32 @@
 4. Для КЗ-01 в графике кредита № 22-2/031 24 платежа, первый — 11.10.2025, последний — 11.09.2027; на 01.10.2026 оплачено 12, ближайший — 11.10.2026.</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="7" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>ФО-43</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Акт обследования залога</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>1. Заёмщик, залогодатель и предмет в акте = данным карточки предмета и договора залога.
 2. Для техники в акте есть все строки формы Положения №12 прил. 2 (приложение 1); для остальных видов — все пять данных п. 2.4.
@@ -8949,32 +9044,32 @@
 6. Дата последнего обследования в карточке предмета = дате акта (для трактора 18.09.2026).</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr"/>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>ФО-44</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>Кредитный договор</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-17 номер (26-5/090), дата (08.09.2026), сумма (1 500 000,00) и условия в договоре = карточке кредита на вкладке «Условия».
 2. Разделы договора идут в порядке приложения 5: 1–9, реквизиты сторон — последним.
@@ -8984,32 +9079,32 @@
 6. Договор формируется только для кредита в состоянии «Проект»; для действующего кредита печатается сохранённый экземпляр без изменений.</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>КЗ-01, КЗ-17</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr"/>
+      <c r="J66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>ФО-45</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>Договор залога</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
         <is>
           <t>1. Реквизиты залогодателя, кредитов и предметов в договоре = карточкам субъекта, кредитов и предметов.
 2. Строка «Итого залоговая стоимость» = сумме залоговой стоимости предметов в таблице = сумме по карточкам предметов договора; валюта каждого предмета = валюте его карточки.
@@ -9019,42 +9114,9 @@
 6. Проект печатается без номера и нотариальных реквизитов; зарегистрированный договор — с номером, нотариусом и свидетельством.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr"/>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>ФО-46</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Договор поручительства</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
-2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
-3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
-4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
@@ -9069,25 +9131,25 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>ФО-48</t>
+          <t>ФО-46</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Ответ источнику предложения</t>
+          <t>Договор поручительства</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
-2. Основание отказа указано для каждой отказанной позиции.
-3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
-4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
+          <t>1. Заёмщик, кредитный договор, сумма и срок в договоре = карточке кредита.
+2. В карточке субъекта поручителя возраст на дату договора от 18 до 70 лет; бланк с иным возрастом не формируется; для юридического лица проверка возраста не применяется.
+3. КЗ-03: договор поручительства № 23-4/008-П1 по кредиту № 23-4/008 от 20.06.2023 содержит срок поручительства, вид и объём ответственности.
+4. Вид «солидарная» и объём «полностью» дают типовой текст; иное сочетание помечает договор как индивидуальную форму.</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>КЗ-16</t>
+          <t>КЗ-03</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
@@ -9102,20 +9164,20 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>ФО-49</t>
+          <t>ФО-48</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Промежуточное письмо по предложению</t>
+          <t>Ответ источнику предложения</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1. Дата письма не позже срока ответа предложения.
-2. Реквизиты предложения и позиции в письме = карточке предложения.
-3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
-4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
+          <t>1. Позиции, стоимость и итоги в письме = позициям и решению карточки предложения.
+2. Основание отказа указано для каждой отказанной позиции.
+3. Зарегистрированное письмо появляется в карточке предложения как ответ; срок ответа предложения закрыт.
+4. КЗ-16: письмо должнику ОАО «Бишкексүт» от 26.02.2026 — позиция 1 принята (4 800 000,00), позиция 2 отказана.</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -9135,20 +9197,20 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>ФО-50</t>
+          <t>ФО-49</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Уведомление о доплате</t>
+          <t>Промежуточное письмо по предложению</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
-2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
-3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
-4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
+          <t>1. Дата письма не позже срока ответа предложения.
+2. Реквизиты предложения и позиции в письме = карточке предложения.
+3. Зарегистрированное письмо вводится в карточку предложения как ответ; повод «срок ответа истёк» по предложению не возникает.
+4. КЗ-16: письмо от 10.02.2026 при сроке ответа 13.02.2026; решение органа позднее — 24.02.2026.</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -9168,20 +9230,20 @@
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>ФО-51</t>
+          <t>ФО-50</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Претензия покупателю</t>
+          <t>Уведомление о доплате</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
-2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
-3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
-4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+          <t>1. Сумма доплаты в бланке = стоимость принятия − сумма, распределённая по кредитам.
+2. Адресат доплаты = отчуждателю, депозиту ПССИ или конкурсной массе по источнику.
+3. Строка «Всего (стоимость принятия)» = задолженности, погашенной принятием, плюс доплата.
+4. КЗ-16: стоимость 4 800 000,00, долг на 20.03.2026 — 4 250 000,00, доплата 550 000,00 сом, срок до 19.04.2026.</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -9201,15 +9263,48 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
+          <t>ФО-51</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>Претензия покупателю</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>1. Просроченные суммы и дни = графику договора и поступлениям на дату претензии.
+2. Неустойка = просроченная сумма × ставка договора × число дней просрочки.
+3. Зарегистрированная претензия видна в карточке договора купли-продажи с датой и документом.
+4. КЗ-16: платёж № 4 от 05.09.2026 на 400 000,00, просрочка 26 дней на 01.10.2026, неустойка 0,1 % в день = 10 400,00; всего к уплате 410 400,00.</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-16</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
           <t>ФО-52</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>Справка по заёмщику</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>1. «Остаток всего» в сводке = сумма остатков основного долга по строкам раздела 4 = 5 100 000,00 для КЗ-01.
 2. Для КЗ-01 в разделе 4 два кредита (№ 21-3/117 и № 22-2/031); для КЗ-15 — ни одного действующего и строка «погашено кредитов: 1».
@@ -9218,32 +9313,32 @@
 5. Справка не получает регистрационного номера и не попадает в журнал исходящих документов.</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>КЗ-01</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr"/>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr"/>
-      <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>ФО-60</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>Опись предметов залога по договору</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>1. Список предметов = предметам с долей отнесения по договору; число строк = числу таких предметов.
 2. Залоговая стоимость каждого предмета = значению в карточке предмета на дату формирования; у утраченного — 0,00.
@@ -9252,32 +9347,32 @@
 5. Договор без отнесённых предметов опись не формирует.</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>ФО-61</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>Справка об обеспеченности кредита</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>1. Сумма под риском и дата снимка = остатку и неосвоенной части по карточке кредита на дату справки.
 2. Индекс залога = залоговая стоимость отнесённых предметов ÷ (сумма под риском × порог); индекс гарантии считается так же от суммы гарантии.
@@ -9287,39 +9382,6 @@
 6. Недостающая сумма по № 24-6/019 = 2 950 000,00 × 1,5 − 3 910 000,00 = 4 425 000,00 − 3 910 000,00 = 515 000,00.</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="7" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>ФО-62</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr">
-        <is>
-          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
-2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
-3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
-4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
-        </is>
-      </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
@@ -9337,25 +9399,25 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>ФО-63</t>
+          <t>ФО-62</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Протокол заседания комиссии по заявкам</t>
+          <t>Извещение о восполнении (восстановлении, замене) предмета залога</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
-2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
-3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
-4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+          <t>1. Форма доступна при исходах «утраченное», «повреждённое», «требует ремонта», «аварийное»; при исходах «хорошее» и «удовлетворительное» не открывается.
+2. Предмет, договор залога и акт в тексте = карточке предмета и журналу обследований.
+3. Срок восполнения в тексте = сроку в карточке извещения (дата извещения + 30 календарных дней).
+4. КЗ-14: извещение по трактору МТЗ-82.1 (акт от 18.09.2026) от 24.09.2026, срок до 24.10.2026; соответствующая часть кредита № 24-6/019 = 2 950 000,00 − 3 910 000,00 ÷ 1,5 = 343 333,33.</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>КЗ-17</t>
+          <t>КЗ-14</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
@@ -9370,15 +9432,48 @@
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
+          <t>ФО-63</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по заявкам</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-17 протокол доступен только при набранном кворуме и заполненных номере протокола и дате заседания.
+2. Строка «Кворум» = число проголосовавших членов и порог ⌊M/2⌋+1 по составу комиссии.
+3. Итог голосования по каждому типу голоса = число строк таблицы с этим голосом; сумма всех типов = число членов комиссии.
+4. Решение в протоколе = типу решения в карточке комиссии КЗ-17; протокол № 7 от 20.08.2026; заявка № 14 от 12.06.2026 (возвращена на доработку 26.06.2026) и сумма 1 500 000,00 = карточке заявки; дата заседания раньше даты кредитного договора № 26-5/090 от 08.09.2026.</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-17</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr"/>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr"/>
+      <c r="J77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
           <t>ФО-64</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>Бланки заявки (пустые, для заполнения заявителем)</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>1. Бланк «Заявление-анкета заёмщика» печатается без единого подставленного значения: все строки полей пустые.
 2. Бланк «Согласие на обработку персональных данных»: заголовок и текст согласия постоянные, поля Ф. И. О., ИНН, дата, подпись — пустые.
@@ -9388,32 +9483,32 @@
 6. Заполненный и подписанный скан загружается в тот же документ комплекта (документ принимает статус «Загружен»).</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>Бланк печатается пустым, данных набора не требует</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr"/>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr"/>
+      <c r="H78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr"/>
+      <c r="J78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>ФО-65</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Карточка организации</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>1. Карточка занимает одну страницу А4 при полном заполнении данных организации.
 2. В списке счетов только счета без даты закрытия; закрытый счёт в карточке не показан.
@@ -9422,42 +9517,9 @@
 5. Логотип в шапке = файлу логотипа из карточки организации; без файла строка логотипа не печатается.</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>Карточка организации из справочника ведомств</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr"/>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="7" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>ФО-66</t>
-        </is>
-      </c>
-      <c r="C79" s="7" t="inlineStr">
-        <is>
-          <t>Журнал регистрации документов за период</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
-2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
-3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
-4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
@@ -9472,20 +9534,20 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>ФО-67</t>
+          <t>ФО-66</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Лист ознакомления</t>
+          <t>Журнал регистрации документов за период</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
-2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
-3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
-4. У не ознакомившегося строка присутствует с пустой датой.</t>
+          <t>1. Число строк журнала исходящих за сентябрь 2026 = числу зарегистрированных исходящих документов с датой регистрации в сентябре, включая аннулированные; строка «Всего зарегистрировано» = числу строк.
+2. Регистрационные номера идут по возрастанию вместе с датой: аннулированный документ показан в журнале со своим номером и пометкой.
+3. Документы КЗ-20 (исходящие № 12-04/1170 от 25.09.2026 и № 12-04/1176 от 30.09.2026) и КЗ-12 (предписание № 12-04/1173 от 28.09.2026) присутствуют в журнале исходящих с верными номерами и датами; образец показывает исходящие контрольного набора.
+4. Фильтр по виду: в журнале исходящих нет входящих и внутренних документов; фильтр по типу оставляет только документы выбранного типа.</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -9505,15 +9567,48 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
+          <t>ФО-67</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Лист ознакомления</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>1. Список строк = получателям документа «на ознакомление»; сотрудник, получивший документ «на исполнение», в листе не показан.
+2. Дата и время у каждой ознакомившейся строки = отметке «Ознакомлен» в журнале документа.
+3. Итог «ознакомлены N из M» = число строк с датой ознакомления из общего числа строк.
+4. У не ознакомившегося строка присутствует с пустой датой.</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr"/>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
           <t>ФО-68</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Опись дела</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>1. Число строк описи = числу документов со статусом «В деле» и данным делом.
 2. Документ другого дела или не сданный в дело в опись не попадает.
@@ -9523,39 +9618,6 @@
 6. КЗ-20: опись показывает документы дела по кредиту № 25-3/014 от 05.03.2025 — внутренний ВН-7, входящий 12-03/512, исходящие 12-04/1170 и 12-04/1176.</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-20</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>78</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>ФО-69</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Регистрационно-контрольная карточка документа</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
-2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
-3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
-4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
-        </is>
-      </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
           <t>КЗ-20</t>
@@ -9573,15 +9635,48 @@
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
+          <t>ФО-69</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Регистрационно-контрольная карточка документа</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1. Номер и дата регистрации в карточке = полям документа; у документа без регистрации карточка не формируется.
+2. Резолюции в карточке = резолюциям документа, верхнего уровня и вложенные, в порядке каскада.
+3. Исход «исполнено» показан только если исполнены все резолюции верхнего уровня.
+4. Для входящего документа КЗ-20 № 12-03/512 с резолюцией показаны ответственный и срок.</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-20</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
           <t>ФО-70</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об исполнении судебного акта (полное погашение)</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен, когда сумма поступлений по судебному акту не меньше суммы, присуждённой актом; на 01.10.2026 недоступен — платежи по соглашению № 3 начинаются 10.10.2026, последний платёж 10.03.2027.
 2. Сумма по судебному акту и реквизиты акта = данным фазы «Иск» по КЗ-05 (решение суда от 25.05.2026).
@@ -9590,32 +9685,32 @@
 5. Адресат = департаменту, ведущему кредит КЗ-05 — Отраслевому департаменту промышленности.</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr"/>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>ФО-71</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>Служебная записка о внесудебном обращении взыскания на залог</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-04 бланк доступен, если у кредита есть договор залога (№ 21-5/203-З1 от 09.09.2021) и по предмету залога нет признака «только судебный порядок».
 2. Предмет залога и договор залога в тексте = карточке предмета залога КЗ-04.
@@ -9624,32 +9719,32 @@
 5. После регистрации по КЗ-04 открывается вопрос для комитета по правовому обеспечению и управлению активами.</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>КЗ-04</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr"/>
-      <c r="G84" s="7" t="inlineStr"/>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="7" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr"/>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>ФО-72</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об установлении правопреемника</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-09 доступен, когда у субъекта заёмщика отмечена дата смерти (12.06.2026).
 2. Дата смерти и реквизиты свидетельства = карточке субъекта КЗ-09.
@@ -9658,42 +9753,9 @@
 5. После регистрации фаза получает статус «Не погашено», процедура — «Передан в УПО» (названия статусов по Порядку №41 п. 53).</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>КЗ-09</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr"/>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>ФО-73</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>Служебная записка об инициировании банкротства</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
-2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
-3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
-4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
-        </is>
-      </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-10</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
@@ -9708,15 +9770,48 @@
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
+          <t>ФО-73</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Служебная записка об инициировании банкротства</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк по КЗ-10 доступен при наличии судебного акта и постановления судебного исполнителя о возврате листа без исполнения в карточке кредита.
+2. Уведомление о намерении в тексте = письму ФО-90, вид «О намерении», по КЗ-10 (исх. № 12-04/0771 от 15.06.2026); срок в уведомлении (15.07.2026) истёк.
+3. Задолженность = расчёту кредита КЗ-10 № 23-4/021 на дату бланка: на 01.10.2026 просрочка 260 дней — основная сумма 600 000,00, проценты 215 000,00, штрафы 58 000,00.
+4. После регистрации фаза получает статус «Инициирование банкротства», процедура — «Передан в сектор по работе с активами (процедура банкротства)».</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-10</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
           <t>ФО-74</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>Служебная записка об отказе в дополнительном залоге</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D88" s="7" t="inlineStr">
         <is>
           <t>1. Форма доступна только при исходе извещения «отказ» или при истёкшем сроке восполнения.
 2. Суммы в таблице = справке об обеспеченности на дату записки.
@@ -9725,32 +9820,32 @@
 5. Записка получает номер журнала внутренних документов и видна в ФО-19.</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr"/>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>ФО-75</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>Отчёт документального мониторинга целевого использования</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 бланк формируется по кредиту с освоенными траншами и перечисленными средствами.
 2. «Освоено» в параметрах = сумме перечислений средств по кредиту (1 500 000,00 + 1 000 000,00) = итогу колонки «Платёжное поручение / квитанция, сумма».
@@ -9760,39 +9855,6 @@
 6. Заёмщик, адрес и руководитель = карточке субъекта.</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr"/>
-      <c r="G88" s="7" t="inlineStr"/>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B89" s="8" t="inlineStr">
-        <is>
-          <t>ФО-76</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
-2. Заёмщик и адрес = карточке субъекта заёмщика.
-3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
-4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
-        </is>
-      </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
@@ -9810,25 +9872,25 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>ФО-77</t>
+          <t>ФО-76</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>Форма отчётности целевого использования кредитов АПК</t>
+          <t>Отчёт фактического мониторинга целевого использования (выезд)</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
-2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
-3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
-4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+          <t>1. Для КЗ-12 бланк формируется по кредиту после документального мониторинга и содержит дату выезда (15.09.2026) и трёх исполнителей.
+2. Заёмщик и адрес = карточке субъекта заёмщика.
+3. Каждое фото в «Фотоотчёте» имеет подпись с датой и объектом, приложенные файлы видны в карточке кредита.
+4. Если в «Выводе» указано «нецелевое использование», по тому же кредиту формируется акт ФО-78; для КЗ-12 вывод назван именно так (Методика №16 п. 12 пп. 1), сумма 400 000,00.</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>КЗ-13</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
@@ -9843,15 +9905,48 @@
       </c>
       <c r="B91" s="8" t="inlineStr">
         <is>
+          <t>ФО-77</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Форма отчётности целевого использования кредитов АПК</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>1. Бланк доступен только по кредитам с отраслью «Агропромышленный комплекс»; для КЗ-13 формируется, для кредитов других отраслей — нет.
+2. «Освоенная сумма» (4 500 000,00) − «Погашенная сумма» (600 000,00) = «Текущий остаток» (3 900 000,00) при отсутствии просроченной и капитализированной задолженности; «Погашенная сумма» — погашение основной суммы.
+3. Номер и дата договора (№ 25-4/030 от 10.02.2025), сумма, ставка, срок возврата = карточке кредита.
+4. Строки «Перечня документов» = документам целевого использования, загруженным по кредиту; сумма документов, подтверждающих расход, = освоенной сумме.</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-13</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
           <t>ФО-78</t>
         </is>
       </c>
-      <c r="C91" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>Акт о нецелевом использовании средств бюджетного кредита</t>
         </is>
       </c>
-      <c r="D91" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-12 акт формируется по кредиту, у которого в отчёте фактического мониторинга (ФО-76) вывод — «нецелевое использование».
 2. Сумма кредита 4 000 000,00, дата и номер договора (№ 24-2/088 от 12.03.2024) = карточке кредита.
@@ -9860,42 +9955,9 @@
 5. Число строк подписи = числу исполнителей, указанных в ФО-76.</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>КЗ-12</t>
-        </is>
-      </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="7" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>ФО-79</t>
-        </is>
-      </c>
-      <c r="C92" s="7" t="inlineStr">
-        <is>
-          <t>Внутренний акт сверки платежей</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
-2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
-3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
-4. «Итого» = сумма строк по каждой числовой колонке.</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-01</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
@@ -9910,15 +9972,48 @@
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
+          <t>ФО-79</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Внутренний акт сверки платежей</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-01 (договор № 21-3/117) за 01.07.2026–31.08.2026 в акте два платежа — 15.07.2026 и 15.08.2026; суммы «по учёту» = суммам платежей в реестре платежей.
+2. Сумма «по реестру казначейства» в строке = сумме соответствующей строки реестра ЦК; «расхождение» = учёт − реестр.
+3. Для КЗ-01 за 01.07.2026–30.09.2026 платёж от 15.09.2026 не подтверждён казначейством: акт помечен «предварительно», подписей нет, номер не присваивается.
+4. «Итого» = сумма строк по каждой числовой колонке.</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-01</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
           <t>ФО-80</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>Расчёт реструктуризации: условия и график до и после</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 строки «До» совпадают с долгом по статьям в карточке кредита на дату расчёта, строки «После» — с результатом расчёта реструктуризации.
 2. Итого задолженность «До» = итого «После» + «Прощено»; для КЗ-06 прощено 0,00, итоги равны (1 860 000,00).
@@ -9927,39 +10022,6 @@
 5. Срок возврата продлён не более чем на 7 лет при остатке задолженности от 1 млн до 10 млн сомов (ПКМ №14 п. 90): 15.03.2028 → 15.10.2030 проходит.</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>ФО-81</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>Дополнительное соглашение к кредитному договору</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
-2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
-3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
-4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
-        </is>
-      </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
           <t>КЗ-06</t>
@@ -9977,15 +10039,48 @@
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
+          <t>ФО-81</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Дополнительное соглашение к кредитному договору</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>1. Для КЗ-06 в допсоглашении только те условия, которые изменены расчётом реструктуризации; остальные не перечислены.
+2. Новые значения совпадают с результатом расчёта (ФО-80) по тому же кредиту.
+3. Для КЗ-06 допсоглашение содержит ссылку на решение комитета и на решение уполномоченного государственного органа.
+4. После подписания и внесения условий в кредит график в приложении = действующему графику; КЗ-06: номер допсоглашения — 2.</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-06</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
           <t>ФО-82</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Соглашение о переводе долга</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-07 (договор № 21-6/144) в соглашении № 14 первоначальный заёмщик — ОсОО «Эко-Продукт», новый — ОсОО «Ысык-Көл Логистик», дата перевода — 09.09.2026.
 2. Переводимый долг по статьям = задолженности по кредиту на дату перевода; «Итого» = сумма строк.
@@ -9994,32 +10089,32 @@
 5. В соглашении указано обоснование: надёжность исполнения повышается (обеспечение нового заёмщика не меньше переводимого долга).</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>КЗ-07</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>ФО-83</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Соглашение о добровольном исполнении судебного акта</t>
         </is>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-05 доступен после вступления судебного акта в силу (решение суда от 25.05.2026).
 2. Сумма строк графика = сумме, присуждённой судебным актом.
@@ -10028,32 +10123,32 @@
 5. Подписанное соглашение № 3 от 10.09.2026 видно в ФО-17 по КЗ-05.</t>
         </is>
       </c>
-      <c r="E96" s="7" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>КЗ-05</t>
         </is>
       </c>
-      <c r="F96" s="7" t="inlineStr"/>
-      <c r="G96" s="7" t="inlineStr"/>
-      <c r="H96" s="7" t="inlineStr"/>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="7" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>ФО-84</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>Соглашение о расторжении кредитного договора</t>
         </is>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>1. Для КЗ-18 (кредит № 26-1/012, средства не получены) бланк доступен, для КЗ-01 (средства получены) — нет.
 2. В тексте указано, что средства по договору не перечислялись: сумма освоения по кредиту = 0,00.
@@ -10062,42 +10157,9 @@
 5. Бланк доступен только при освоении 0,00; при частично перечисленных средствах расторжение этим бланком не оформляется.</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>КЗ-18</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>ФО-85</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
-        <is>
-          <t>Расчёт распределения выручки от реализации залога</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
-2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
-3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
-4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-04</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
@@ -10112,15 +10174,48 @@
       </c>
       <c r="B99" s="8" t="inlineStr">
         <is>
+          <t>ФО-85</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Расчёт распределения выручки от реализации залога</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>1. Выручка по КЗ-04 = сумме поступления от реализации предмета залога в реестре платежей (4 700 000,00, поступила 29.09.2026).
+2. Остаток залогодателю = выручка − расходы − требования ОАО (459 500,00); если результат отрицательный, остаток залогодателю 0,00 и показана непокрытая часть требований.
+3. Требования ОАО по видам = задолженности кредита КЗ-04 № 21-5/203 на дату реализации: основная сумма 3 600 000,00, проценты 410 000,00, штрафы 120 500,00.
+4. Остаток выручки в последней строке таблицы равен 0,00; на каждой строке он равен предыдущему остатку минус сумма строки.</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-04</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
           <t>ФО-86</t>
         </is>
       </c>
-      <c r="C99" s="7" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>Платёжное требование в банк заёмщика</t>
         </is>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>1. Бланк по КЗ-03 доступен только при положительном решении комитета по кредиту и признаке «право безакцептного списания» в договоре.
 2. Срок направления — не более 10 рабочих дней со дня решения комитета: решение КЗ-03 от 17.09.2026, срок до 01.10.2026; нарушение показывается куратору.
@@ -10129,42 +10224,9 @@
 5. Зарегистрированное требование видно в ФО-17 и в ФО-19.</t>
         </is>
       </c>
-      <c r="E99" s="7" t="inlineStr">
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>КЗ-03</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr"/>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>ФО-87</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr">
-        <is>
-          <t>Заявка на перечисление средств кредита заёмщику</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
-2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
-3. По кредиту без подписанного договора заявка недоступна.
-4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
@@ -10179,25 +10241,25 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>ФО-88</t>
+          <t>ФО-87</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>Паспорт предмета залога</t>
+          <t>Заявка на перечисление средств кредита заёмщику</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>1. Все значения документа = карточке предмета на дату печати.
-2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
-3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
-4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+          <t>1. Для КЗ-12 заявка формируется по траншу; сумма транша 2 = 1 000 000,00 = сумме транша в карточке кредита.
+2. Реквизиты получателя = реквизитам заёмщика в карточке субъекта.
+3. По кредиту без подписанного договора заявка недоступна.
+4. Зарегистрированная заявка видна в журнале исходящих документов; сумма выдачи после подтверждения казначейства попадает в освоение транша.</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>КЗ-14</t>
+          <t>КЗ-12</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
@@ -10212,15 +10274,48 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
+          <t>ФО-88</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Паспорт предмета залога</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>1. Все значения документа = карточке предмета на дату печати.
+2. Залоговая стоимость = оценочная × коэффициент вида (недвижимость 0,7): 4 300 000,00 × 0,7 = 3 010 000,00.
+3. Список обеспечиваемых кредитов и доли = отнесениям предмета в карточке.
+4. КЗ-14, предмет «Здание склада» (залоговая стоимость 3 010 000,00): общая площадь 548,6 кв.м — после дополнительного соглашения от 09.09.2026.</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>КЗ-14</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
           <t>ФО-89</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>Дополнительное соглашение к договору залога</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>1. Сторона, номер и дата договора в соглашении = карточке договора.
 2. Таблица «было → стало» = изменениям записи соглашения; «было» = состоянию договора до пакета.
@@ -10229,42 +10324,9 @@
 5. Подписанное соглашение хранится в карточке договора; номер соглашения = числу соглашений договора на эту дату.</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>КЗ-14</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr"/>
-      <c r="G102" s="7" t="inlineStr"/>
-      <c r="H102" s="7" t="inlineStr"/>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B103" s="8" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr">
-        <is>
-          <t>Письмо по кредиту</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
-2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
-3. Шапка, номер и подпись во всех видах одинаковы по расположению.
-4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>Проверяется по видам</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
@@ -10274,20 +10336,53 @@
       <c r="J103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="10" t="n">
+      <c r="A104" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>ФО-90</t>
         </is>
       </c>
-      <c r="C104" s="11" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>Письмо по кредиту</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>1. Письмо получает исходящий номер при регистрации и появляется в журнале исходящих документов.
+2. Вид письма определяет получателя, текст и приложения; у каждого вида в шапке совпадает набор реквизитов с рамкой.
+3. Шапка, номер и подпись во всех видах одинаковы по расположению.
+4. В шапке рамки и в каждом виде одинаковые реквизиты: исходящий номер, дата, получатель, подпись.</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>Проверяется по видам</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>ФО-90</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
         <is>
           <t>вид «По реструктуризации — уполномоченному органу»</t>
         </is>
       </c>
-      <c r="D104" s="10" t="inlineStr">
+      <c r="D105" s="10" t="inlineStr">
         <is>
           <t>1. Для КЗ-06 письмо доступно после решения комитета (10.08.2026) и создаётся не позднее 5 рабочих дней с его даты: письмо от 14.08.2026.
 2. Номер и дата решения комитета в письме = записи в журнале актов заявки.
@@ -10295,42 +10390,9 @@
 4. Отправка письма фиксируется датой и номером; на период решения уполномоченного органа, но не более 70 календарных дней, ранее запущенные меры взыскания приостановлены (Порядок №41 п. 18).</t>
         </is>
       </c>
-      <c r="E104" s="10" t="inlineStr">
+      <c r="E105" s="10" t="inlineStr">
         <is>
           <t>КЗ-06</t>
-        </is>
-      </c>
-      <c r="F104" s="10" t="inlineStr"/>
-      <c r="G104" s="10" t="inlineStr"/>
-      <c r="H104" s="10" t="inlineStr"/>
-      <c r="I104" s="10" t="inlineStr"/>
-      <c r="J104" s="10" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="n">
-        <v>101</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>ФО-90</t>
-        </is>
-      </c>
-      <c r="C105" s="11" t="inlineStr">
-        <is>
-          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
-        </is>
-      </c>
-      <c r="D105" s="10" t="inlineStr">
-        <is>
-          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
-2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
-3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящими номерами.
-4. Срок ответа в тексте = значению, введённому куратором (по умолчанию 30 календарных дней со дня письма).</t>
-        </is>
-      </c>
-      <c r="E105" s="10" t="inlineStr">
-        <is>
-          <t>КЗ-09</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr"/>
@@ -10350,15 +10412,15 @@
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>вид «Запросы по умершему заёмщику — нотариату, ЦОН, органу регистрации имущества»</t>
+          <t>вид «Родственникам умершего заёмщика — о добровольном принятии задолженности»</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>1. Для КЗ-09 доступны три адресата; запрос в ЦОН — при заполненной дате смерти (12.06.2026), запросы нотариусу и регистрирующему органу — после записи об отказе родственников от добровольного погашения (в контрольном наборе — 20.08.2026).
-2. Каждый запрос получает отдельный исходящий номер.
-3. Данные умершего заёмщика = карточке субъекта.
-4. В тексте каждого запроса указаны только сведения, которые запрашивает данный адресат.</t>
+          <t>1. Для КЗ-09 письмо доступно после внесения в дело даты смерти (12.06.2026) и справки о составе семьи.
+2. Долг по статьям = задолженности по кредиту на дату письма; «Итого» = сумма строк.
+3. КЗ-09: в справке о составе семьи сын и дочь — два письма с разными исходящи